--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -220,12 +220,56 @@
         </r>
       </text>
     </comment>
+    <comment ref="L7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表的ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
   <si>
     <t>序列ID</t>
   </si>
@@ -345,6 +389,9 @@
   </si>
   <si>
     <t>商业-刮刮卡-常驻</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_101_102_103_104</t>
   </si>
   <si>
     <t>12001_100000</t>
@@ -599,12 +646,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1492,7 +1539,7 @@
     <col min="9" max="9" width="14.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="17.375" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
     <col min="13" max="13" width="16.375" style="5" customWidth="1"/>
     <col min="14" max="14" width="16.375" style="1" customWidth="1"/>
     <col min="15" max="15" width="26.75" style="1" customWidth="1"/>
@@ -1707,7 +1754,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>57004</v>
       </c>
@@ -1734,6 +1781,9 @@
       <c r="K7" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L7" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1">
@@ -1762,11 +1812,14 @@
       <c r="K8" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L8" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="M8" s="5">
         <v>100011</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1780,7 +1833,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>36</v>
@@ -1808,7 +1861,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>33</v>
@@ -1836,7 +1889,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>33</v>
@@ -1868,7 +1921,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>33</v>
@@ -1900,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1928,7 +1981,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>33</v>
@@ -1956,7 +2009,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>33</v>
@@ -1984,7 +2037,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>33</v>
@@ -2016,7 +2069,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>33</v>
@@ -2048,7 +2101,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>33</v>
@@ -2077,7 +2130,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>36</v>
@@ -2097,10 +2150,10 @@
         <v>1</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2136,10 +2189,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2147,7 +2200,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2155,7 +2208,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2163,7 +2216,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2195,7 +2248,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2203,7 +2256,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2211,7 +2264,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2219,7 +2272,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2227,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2235,7 +2288,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2243,7 +2296,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2251,7 +2304,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2259,7 +2312,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2267,7 +2320,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2275,7 +2328,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -176,6 +176,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+填写 condition.xlsx  ID</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="L5" authorId="0">
       <text>
         <r>
@@ -269,7 +291,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="64">
   <si>
     <t>序列ID</t>
   </si>
@@ -313,6 +335,9 @@
     <t>掉落条件</t>
   </si>
   <si>
+    <t>进度触发类型</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -367,6 +392,9 @@
     <t>dropcondition</t>
   </si>
   <si>
+    <t>triggerType</t>
+  </si>
+  <si>
     <t>功能-每日奖金(原月卡)</t>
   </si>
   <si>
@@ -407,6 +435,9 @@
   </si>
   <si>
     <t>商业-官方派奖</t>
+  </si>
+  <si>
+    <t>10001_1000</t>
   </si>
   <si>
     <t>活跃-每日签到</t>
@@ -1525,14 +1556,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.375" style="1" customWidth="1"/>
@@ -1542,13 +1573,13 @@
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
     <col min="13" max="13" width="16.375" style="5" customWidth="1"/>
     <col min="14" max="14" width="16.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="26.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="1" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" spans="1:14">
+    <row r="1" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1591,92 +1622,101 @@
       <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:14">
+      <c r="O1" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" s="8" customFormat="1" ht="15" spans="1:14">
+    </row>
+    <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A3" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" s="8" customFormat="1" ht="15" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1691,6 +1731,7 @@
       <c r="L4" s="10"/>
       <c r="M4" s="11"/>
       <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
@@ -1703,10 +1744,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1720,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1734,10 +1775,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1751,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1765,10 +1806,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1782,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1796,10 +1837,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1813,13 +1854,13 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M8" s="5">
         <v>100011</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1833,10 +1874,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1861,10 +1902,10 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1889,10 +1930,10 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11" s="5">
         <v>46104</v>
@@ -1910,7 +1951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
         <v>57009</v>
       </c>
@@ -1921,10 +1962,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F12" s="5">
         <v>46105</v>
@@ -1940,6 +1981,9 @@
       </c>
       <c r="K12" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1953,10 +1997,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1981,10 +2025,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2009,10 +2053,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -2037,10 +2081,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16" s="5">
         <v>46101</v>
@@ -2069,10 +2113,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F17" s="5">
         <v>46102</v>
@@ -2101,10 +2145,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
@@ -2130,10 +2174,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F19" s="5">
         <v>46103</v>
@@ -2150,10 +2194,10 @@
         <v>1</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2189,10 +2233,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2200,7 +2244,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2208,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2216,7 +2260,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2224,7 +2268,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2232,7 +2276,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2240,7 +2284,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2248,7 +2292,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2256,7 +2300,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2264,7 +2308,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2272,7 +2316,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2280,7 +2324,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2288,7 +2332,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2296,7 +2340,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2304,7 +2348,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2312,7 +2356,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2320,7 +2364,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2328,7 +2372,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -291,7 +291,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="62">
   <si>
     <t>序列ID</t>
   </si>
@@ -398,7 +398,7 @@
     <t>功能-每日奖金(原月卡)</t>
   </si>
   <si>
-    <t>1_10</t>
+    <t>1_1</t>
   </si>
   <si>
     <t>1_2_3</t>
@@ -407,9 +407,6 @@
     <t>商业-摇钱树-常驻</t>
   </si>
   <si>
-    <t>1_1</t>
-  </si>
-  <si>
     <t>1_2_3_4_5_6_7_8</t>
   </si>
   <si>
@@ -441,9 +438,6 @@
   </si>
   <si>
     <t>活跃-每日签到</t>
-  </si>
-  <si>
-    <t>1_5</t>
   </si>
   <si>
     <t>商业-首充</t>
@@ -1778,7 +1772,7 @@
         <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1792,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1806,10 +1800,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1837,10 +1831,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1854,13 +1848,13 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M8" s="5">
         <v>100011</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1874,10 +1868,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1902,7 +1896,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>35</v>
@@ -1930,7 +1924,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -1962,7 +1956,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
@@ -1983,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1997,10 +1991,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2025,7 +2019,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>35</v>
@@ -2053,7 +2047,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
@@ -2081,7 +2075,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>35</v>
@@ -2113,7 +2107,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
@@ -2145,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>35</v>
@@ -2174,10 +2168,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F19" s="5">
         <v>46103</v>
@@ -2194,10 +2188,10 @@
         <v>1</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2233,10 +2227,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2244,7 +2238,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2252,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2260,7 +2254,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2276,7 +2270,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2284,7 +2278,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2292,7 +2286,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2300,7 +2294,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2308,7 +2302,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2316,7 +2310,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2324,7 +2318,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2332,7 +2326,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2340,7 +2334,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2348,7 +2342,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2356,7 +2350,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2364,7 +2358,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2372,7 +2366,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -286,12 +286,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="L9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表的ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="63">
   <si>
     <t>序列ID</t>
   </si>
@@ -425,58 +447,61 @@
     <t>活跃-推广分享功能</t>
   </si>
   <si>
+    <t>1_2_3_4_5_6_7_8_9_10_101_102_103_104_105_106_107_108</t>
+  </si>
+  <si>
+    <t>活跃-积分大奖</t>
+  </si>
+  <si>
+    <t>商业-官方派奖</t>
+  </si>
+  <si>
+    <t>10001_1000</t>
+  </si>
+  <si>
+    <t>活跃-每日签到</t>
+  </si>
+  <si>
+    <t>商业-首充</t>
+  </si>
+  <si>
+    <t>商业-每日首充</t>
+  </si>
+  <si>
+    <t>商业-特惠礼包</t>
+  </si>
+  <si>
+    <t>商业-阶梯集合礼包</t>
+  </si>
+  <si>
+    <t>商业-金币投资</t>
+  </si>
+  <si>
+    <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>100006_100007_100008_100009_100010</t>
+  </si>
+  <si>
+    <t>12001_10000</t>
+  </si>
+  <si>
+    <t>#备注1</t>
+  </si>
+  <si>
+    <t>#备注2</t>
+  </si>
+  <si>
+    <t>功能名称</t>
+  </si>
+  <si>
+    <t>功能-道具掉落</t>
+  </si>
+  <si>
+    <t>功能-周卡\月卡\永久卡</t>
+  </si>
+  <si>
     <t>功能-商城</t>
-  </si>
-  <si>
-    <t>活跃-积分大奖</t>
-  </si>
-  <si>
-    <t>商业-官方派奖</t>
-  </si>
-  <si>
-    <t>10001_1000</t>
-  </si>
-  <si>
-    <t>活跃-每日签到</t>
-  </si>
-  <si>
-    <t>商业-首充</t>
-  </si>
-  <si>
-    <t>商业-每日首充</t>
-  </si>
-  <si>
-    <t>商业-特惠礼包</t>
-  </si>
-  <si>
-    <t>商业-阶梯集合礼包</t>
-  </si>
-  <si>
-    <t>商业-金币投资</t>
-  </si>
-  <si>
-    <t>活跃-收集拼图</t>
-  </si>
-  <si>
-    <t>100006_100007_100008_100009_100010</t>
-  </si>
-  <si>
-    <t>12001_10000</t>
-  </si>
-  <si>
-    <t>#备注1</t>
-  </si>
-  <si>
-    <t>#备注2</t>
-  </si>
-  <si>
-    <t>功能名称</t>
-  </si>
-  <si>
-    <t>功能-道具掉落</t>
-  </si>
-  <si>
-    <t>功能-周卡\月卡\永久卡</t>
   </si>
 </sst>
 </file>
@@ -671,12 +696,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1550,7 +1575,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
@@ -1857,7 +1882,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <v>57006</v>
       </c>
@@ -1884,53 +1909,60 @@
       <c r="K9" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L9" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>57007</v>
+        <v>57008</v>
       </c>
       <c r="B10" s="1">
-        <v>57007</v>
+        <v>57008</v>
       </c>
       <c r="C10" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="F10" s="5">
+        <v>46104</v>
+      </c>
       <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="I10" s="14">
+        <v>45901</v>
+      </c>
+      <c r="J10" s="14">
+        <v>45961.9999884259</v>
+      </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>57008</v>
+        <v>57009</v>
       </c>
       <c r="B11" s="1">
-        <v>57008</v>
+        <v>57009</v>
       </c>
       <c r="C11" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F11" s="5">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
@@ -1944,54 +1976,50 @@
       <c r="K11" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="O11" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>57009</v>
+        <v>57010</v>
       </c>
       <c r="B12" s="1">
-        <v>57009</v>
+        <v>57010</v>
       </c>
       <c r="C12" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="5">
-        <v>46105</v>
-      </c>
       <c r="G12" s="1">
-        <v>2</v>
-      </c>
-      <c r="I12" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J12" s="14">
-        <v>45961.9999884259</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
       <c r="K12" s="1" t="b">
         <v>1</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>57010</v>
+        <v>57011</v>
       </c>
       <c r="B13" s="1">
-        <v>57010</v>
+        <v>57011</v>
       </c>
       <c r="C13" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -2010,16 +2038,16 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>57011</v>
+        <v>57012</v>
       </c>
       <c r="B14" s="1">
-        <v>57011</v>
+        <v>57012</v>
       </c>
       <c r="C14" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>35</v>
@@ -2038,50 +2066,54 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>57012</v>
+        <v>57013</v>
       </c>
       <c r="B15" s="1">
-        <v>57012</v>
+        <v>57013</v>
       </c>
       <c r="C15" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="F15" s="5">
+        <v>46101</v>
+      </c>
       <c r="G15" s="1">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="I15" s="14">
+        <v>45901</v>
+      </c>
+      <c r="J15" s="14">
+        <v>45961.9999884259</v>
+      </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>57013</v>
+        <v>57014</v>
       </c>
       <c r="B16" s="1">
-        <v>57013</v>
+        <v>57014</v>
       </c>
       <c r="C16" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F16" s="5">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="G16" s="1">
         <v>2</v>
@@ -2096,118 +2128,86 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="1">
-        <v>57014</v>
-      </c>
-      <c r="B17" s="1">
-        <v>57014</v>
-      </c>
-      <c r="C17" s="1">
-        <v>14</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>52</v>
+    <row r="17" s="9" customFormat="1" spans="1:13">
+      <c r="A17" s="9">
+        <v>57015</v>
+      </c>
+      <c r="B17" s="9">
+        <v>57015</v>
+      </c>
+      <c r="C17" s="9">
+        <v>15</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="5">
-        <v>46102</v>
-      </c>
-      <c r="G17" s="1">
-        <v>2</v>
-      </c>
-      <c r="I17" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J17" s="14">
-        <v>45961.9999884259</v>
-      </c>
+      <c r="G17" s="9">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
       <c r="K17" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" s="9" customFormat="1" spans="1:13">
-      <c r="A18" s="9">
-        <v>57015</v>
-      </c>
-      <c r="B18" s="9">
-        <v>57015</v>
-      </c>
-      <c r="C18" s="9">
-        <v>15</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>53</v>
+      <c r="M17" s="16"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="1">
+        <v>57016</v>
+      </c>
+      <c r="B18" s="1">
+        <v>57016</v>
+      </c>
+      <c r="C18" s="1">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="9">
+      <c r="F18" s="5">
+        <v>46103</v>
+      </c>
+      <c r="G18" s="1">
         <v>1</v>
       </c>
       <c r="H18" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M18" s="16"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="1">
-        <v>57016</v>
-      </c>
-      <c r="B19" s="1">
-        <v>57016</v>
-      </c>
-      <c r="C19" s="1">
-        <v>16</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="5">
-        <v>46103</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1">
-        <v>90</v>
-      </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="5" t="s">
+      <c r="M18" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F11">
+  <conditionalFormatting sqref="F10">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F11">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
+  <conditionalFormatting sqref="F15">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
+  <conditionalFormatting sqref="F16">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
+  <conditionalFormatting sqref="F18">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2294,7 +2294,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -308,12 +308,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="L12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表的ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="64">
   <si>
     <t>序列ID</t>
   </si>
@@ -460,6 +482,9 @@
   </si>
   <si>
     <t>活跃-每日签到</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
   </si>
   <si>
     <t>商业-首充</t>
@@ -696,12 +721,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1980,7 +2005,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12">
       <c r="A12" s="1">
         <v>57010</v>
       </c>
@@ -2007,6 +2032,9 @@
       <c r="K12" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L12" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
@@ -2019,7 +2047,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -2047,7 +2075,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>35</v>
@@ -2075,7 +2103,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
@@ -2107,7 +2135,7 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>35</v>
@@ -2139,7 +2167,7 @@
         <v>15</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
@@ -2168,7 +2196,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>35</v>
@@ -2188,10 +2216,10 @@
         <v>1</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2227,10 +2255,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2238,7 +2266,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2246,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2254,7 +2282,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2294,7 +2322,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2326,7 +2354,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2334,7 +2362,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2342,7 +2370,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2350,7 +2378,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2358,7 +2386,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2366,7 +2394,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -2036,7 +2036,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12">
       <c r="A13" s="1">
         <v>57011</v>
       </c>
@@ -2061,6 +2061,9 @@
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
       <c r="K13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
         <v>1</v>
       </c>
     </row>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
   <si>
     <t>序列ID</t>
   </si>
@@ -476,6 +476,9 @@
   </si>
   <si>
     <t>商业-官方派奖</t>
+  </si>
+  <si>
+    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
     <t>10001_1000</t>
@@ -2001,8 +2004,11 @@
       <c r="K11" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2016,7 +2022,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
@@ -2033,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2047,7 +2053,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -2078,7 +2084,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>35</v>
@@ -2106,7 +2112,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
@@ -2138,7 +2144,7 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>35</v>
@@ -2170,7 +2176,7 @@
         <v>15</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
@@ -2199,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>35</v>
@@ -2219,10 +2225,10 @@
         <v>1</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2258,10 +2264,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2269,7 +2275,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2277,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2285,7 +2291,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2325,7 +2331,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2349,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2357,7 +2363,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2365,7 +2371,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2373,7 +2379,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2381,7 +2387,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2389,7 +2395,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2397,7 +2403,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
   <si>
     <t>序列ID</t>
   </si>
@@ -473,6 +473,12 @@
   </si>
   <si>
     <t>活跃-积分大奖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/01 00:00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/09/30 23:59:59 </t>
   </si>
   <si>
     <t>商业-官方派奖</t>
@@ -1203,7 +1209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1234,7 +1240,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1246,10 +1258,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1614,8 +1623,7 @@
     <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="21.875" style="10" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
     <col min="13" max="13" width="16.375" style="5" customWidth="1"/>
@@ -1627,158 +1635,158 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:15">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
@@ -1802,8 +1810,8 @@
       <c r="H5" s="1">
         <v>9999</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
       <c r="K5" s="1" t="b">
         <v>1</v>
       </c>
@@ -1833,8 +1841,8 @@
       <c r="H6" s="1">
         <v>9999</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
       <c r="K6" s="1" t="b">
         <v>1</v>
       </c>
@@ -1864,8 +1872,8 @@
       <c r="H7" s="1">
         <v>9999</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
       <c r="K7" s="1" t="b">
         <v>1</v>
       </c>
@@ -1895,8 +1903,8 @@
       <c r="H8" s="1">
         <v>9999</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
       <c r="K8" s="1" t="b">
         <v>1</v>
       </c>
@@ -1932,8 +1940,8 @@
       <c r="H9" s="1">
         <v>9999</v>
       </c>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
       <c r="K9" s="1" t="b">
         <v>1</v>
       </c>
@@ -1963,11 +1971,11 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J10" s="14">
-        <v>45961.9999884259</v>
+      <c r="I10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
@@ -1984,7 +1992,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -1995,20 +2003,20 @@
       <c r="G11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J11" s="14">
-        <v>45961.9999884259</v>
+      <c r="I11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2022,7 +2030,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
@@ -2033,13 +2041,13 @@
       <c r="H12" s="1">
         <v>9999</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
       <c r="K12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2053,7 +2061,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -2064,8 +2072,8 @@
       <c r="H13" s="1">
         <v>9999</v>
       </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
       <c r="K13" s="1" t="b">
         <v>1</v>
       </c>
@@ -2084,7 +2092,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>35</v>
@@ -2095,8 +2103,8 @@
       <c r="H14" s="1">
         <v>9999</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
       <c r="K14" s="1" t="b">
         <v>1</v>
       </c>
@@ -2112,7 +2120,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
@@ -2123,11 +2131,11 @@
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="I15" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J15" s="14">
-        <v>45961.9999884259</v>
+      <c r="I15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
@@ -2144,7 +2152,7 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>35</v>
@@ -2155,11 +2163,11 @@
       <c r="G16" s="1">
         <v>2</v>
       </c>
-      <c r="I16" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J16" s="14">
-        <v>45961.9999884259</v>
+      <c r="I16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K16" s="1" t="b">
         <v>1</v>
@@ -2176,7 +2184,7 @@
         <v>15</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
@@ -2187,12 +2195,12 @@
       <c r="H17" s="1">
         <v>9999</v>
       </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
       <c r="K17" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M17" s="16"/>
+      <c r="M17" s="17"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1">
@@ -2205,7 +2213,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>35</v>
@@ -2219,16 +2227,16 @@
       <c r="H18" s="1">
         <v>90</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2264,10 +2272,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2275,7 +2283,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2283,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2291,7 +2299,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2331,7 +2339,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2347,7 +2355,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2355,7 +2363,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2363,7 +2371,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2371,7 +2379,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2379,7 +2387,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2387,7 +2395,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2395,7 +2403,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2403,7 +2411,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -475,10 +475,10 @@
     <t>活跃-积分大奖</t>
   </si>
   <si>
-    <t xml:space="preserve">2025/09/01 00:00:00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/09/30 23:59:59 </t>
+    <t>2025/09/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2025/09/30 23:59:59</t>
   </si>
   <si>
     <t>商业-官方派奖</t>
@@ -1810,8 +1810,6 @@
       <c r="H5" s="1">
         <v>9999</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
       <c r="K5" s="1" t="b">
         <v>1</v>
       </c>
@@ -1841,8 +1839,6 @@
       <c r="H6" s="1">
         <v>9999</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
       <c r="K6" s="1" t="b">
         <v>1</v>
       </c>
@@ -1872,8 +1868,6 @@
       <c r="H7" s="1">
         <v>9999</v>
       </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
       <c r="K7" s="1" t="b">
         <v>1</v>
       </c>
@@ -1903,8 +1897,6 @@
       <c r="H8" s="1">
         <v>9999</v>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
       <c r="K8" s="1" t="b">
         <v>1</v>
       </c>
@@ -1940,8 +1932,6 @@
       <c r="H9" s="1">
         <v>9999</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
       <c r="K9" s="1" t="b">
         <v>1</v>
       </c>
@@ -2041,8 +2031,6 @@
       <c r="H12" s="1">
         <v>9999</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
       <c r="K12" s="1" t="b">
         <v>1</v>
       </c>
@@ -2072,8 +2060,6 @@
       <c r="H13" s="1">
         <v>9999</v>
       </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
       <c r="K13" s="1" t="b">
         <v>1</v>
       </c>
@@ -2103,8 +2089,6 @@
       <c r="H14" s="1">
         <v>9999</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
       <c r="K14" s="1" t="b">
         <v>1</v>
       </c>
@@ -2227,8 +2211,6 @@
       <c r="H18" s="1">
         <v>90</v>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
   <si>
     <t>序列ID</t>
   </si>
@@ -473,6 +473,12 @@
   </si>
   <si>
     <t>活跃-积分大奖</t>
+  </si>
+  <si>
+    <t>2025/09/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2025/09/30 23:59:59</t>
   </si>
   <si>
     <t>商业-官方派奖</t>
@@ -1203,7 +1209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1234,7 +1240,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1246,10 +1258,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1614,8 +1623,7 @@
     <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="21.875" style="10" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
     <col min="13" max="13" width="16.375" style="5" customWidth="1"/>
@@ -1627,158 +1635,158 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:15">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
@@ -1802,8 +1810,6 @@
       <c r="H5" s="1">
         <v>9999</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
       <c r="K5" s="1" t="b">
         <v>1</v>
       </c>
@@ -1833,8 +1839,6 @@
       <c r="H6" s="1">
         <v>9999</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
       <c r="K6" s="1" t="b">
         <v>1</v>
       </c>
@@ -1864,8 +1868,6 @@
       <c r="H7" s="1">
         <v>9999</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
       <c r="K7" s="1" t="b">
         <v>1</v>
       </c>
@@ -1895,8 +1897,6 @@
       <c r="H8" s="1">
         <v>9999</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
       <c r="K8" s="1" t="b">
         <v>1</v>
       </c>
@@ -1932,8 +1932,6 @@
       <c r="H9" s="1">
         <v>9999</v>
       </c>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
       <c r="K9" s="1" t="b">
         <v>1</v>
       </c>
@@ -1963,11 +1961,11 @@
       <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J10" s="14">
-        <v>45961.9999884259</v>
+      <c r="I10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
@@ -1984,7 +1982,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -1995,20 +1993,20 @@
       <c r="G11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J11" s="14">
-        <v>45961.9999884259</v>
+      <c r="I11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2022,7 +2020,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
@@ -2033,13 +2031,11 @@
       <c r="H12" s="1">
         <v>9999</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
       <c r="K12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2053,7 +2049,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -2064,8 +2060,6 @@
       <c r="H13" s="1">
         <v>9999</v>
       </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
       <c r="K13" s="1" t="b">
         <v>1</v>
       </c>
@@ -2084,7 +2078,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>35</v>
@@ -2095,8 +2089,6 @@
       <c r="H14" s="1">
         <v>9999</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
       <c r="K14" s="1" t="b">
         <v>1</v>
       </c>
@@ -2112,7 +2104,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
@@ -2123,11 +2115,11 @@
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="I15" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J15" s="14">
-        <v>45961.9999884259</v>
+      <c r="I15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
@@ -2144,7 +2136,7 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>35</v>
@@ -2155,11 +2147,11 @@
       <c r="G16" s="1">
         <v>2</v>
       </c>
-      <c r="I16" s="14">
-        <v>45901</v>
-      </c>
-      <c r="J16" s="14">
-        <v>45961.9999884259</v>
+      <c r="I16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K16" s="1" t="b">
         <v>1</v>
@@ -2176,7 +2168,7 @@
         <v>15</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
@@ -2187,12 +2179,12 @@
       <c r="H17" s="1">
         <v>9999</v>
       </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
       <c r="K17" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M17" s="16"/>
+      <c r="M17" s="17"/>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1">
@@ -2205,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>35</v>
@@ -2219,16 +2211,14 @@
       <c r="H18" s="1">
         <v>90</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2264,10 +2254,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2275,7 +2265,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2283,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2291,7 +2281,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2331,7 +2321,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2347,7 +2337,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2355,7 +2345,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2363,7 +2353,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2371,7 +2361,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2379,7 +2369,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2387,7 +2377,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2395,7 +2385,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2403,7 +2393,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -308,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L12" authorId="0">
+    <comment ref="L11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="67">
   <si>
     <t>序列ID</t>
   </si>
@@ -472,70 +472,70 @@
     <t>1_2_3_4_5_6_7_8_9_10_101_102_103_104_105_106_107_108</t>
   </si>
   <si>
+    <t>商业-官方派奖</t>
+  </si>
+  <si>
+    <t>2025/09/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2025/09/30 23:59:59</t>
+  </si>
+  <si>
+    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
+  </si>
+  <si>
+    <t>10001_1000</t>
+  </si>
+  <si>
+    <t>活跃-每日签到</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
+  </si>
+  <si>
+    <t>商业-首充</t>
+  </si>
+  <si>
+    <t>商业-每日首充</t>
+  </si>
+  <si>
+    <t>商业-特惠礼包</t>
+  </si>
+  <si>
+    <t>商业-阶梯集合礼包</t>
+  </si>
+  <si>
+    <t>商业-金币投资</t>
+  </si>
+  <si>
+    <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>100006_100007_100008_100009_100010</t>
+  </si>
+  <si>
+    <t>12001_10000</t>
+  </si>
+  <si>
+    <t>#备注1</t>
+  </si>
+  <si>
+    <t>#备注2</t>
+  </si>
+  <si>
+    <t>功能名称</t>
+  </si>
+  <si>
+    <t>功能-道具掉落</t>
+  </si>
+  <si>
+    <t>功能-周卡\月卡\永久卡</t>
+  </si>
+  <si>
+    <t>功能-商城</t>
+  </si>
+  <si>
     <t>活跃-积分大奖</t>
-  </si>
-  <si>
-    <t>2025/09/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2025/09/30 23:59:59</t>
-  </si>
-  <si>
-    <t>商业-官方派奖</t>
-  </si>
-  <si>
-    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
-  </si>
-  <si>
-    <t>10001_1000</t>
-  </si>
-  <si>
-    <t>活跃-每日签到</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
-  </si>
-  <si>
-    <t>商业-首充</t>
-  </si>
-  <si>
-    <t>商业-每日首充</t>
-  </si>
-  <si>
-    <t>商业-特惠礼包</t>
-  </si>
-  <si>
-    <t>商业-阶梯集合礼包</t>
-  </si>
-  <si>
-    <t>商业-金币投资</t>
-  </si>
-  <si>
-    <t>活跃-收集拼图</t>
-  </si>
-  <si>
-    <t>100006_100007_100008_100009_100010</t>
-  </si>
-  <si>
-    <t>12001_10000</t>
-  </si>
-  <si>
-    <t>#备注1</t>
-  </si>
-  <si>
-    <t>#备注2</t>
-  </si>
-  <si>
-    <t>功能名称</t>
-  </si>
-  <si>
-    <t>功能-道具掉落</t>
-  </si>
-  <si>
-    <t>功能-周卡\月卡\永久卡</t>
-  </si>
-  <si>
-    <t>功能-商城</t>
   </si>
 </sst>
 </file>
@@ -1612,7 +1612,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
@@ -1939,15 +1939,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>57008</v>
+        <v>57009</v>
       </c>
       <c r="B10" s="1">
-        <v>57008</v>
+        <v>57009</v>
       </c>
       <c r="C10" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>45</v>
@@ -1956,7 +1956,7 @@
         <v>35</v>
       </c>
       <c r="F10" s="5">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="G10" s="1">
         <v>2</v>
@@ -1970,57 +1970,54 @@
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
-        <v>57009</v>
+        <v>57010</v>
       </c>
       <c r="B11" s="1">
-        <v>57009</v>
+        <v>57010</v>
       </c>
       <c r="C11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="5">
-        <v>46105</v>
-      </c>
       <c r="G11" s="1">
-        <v>2</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>9999</v>
       </c>
       <c r="K11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="1">
-        <v>57010</v>
+        <v>57011</v>
       </c>
       <c r="B12" s="1">
-        <v>57010</v>
+        <v>57011</v>
       </c>
       <c r="C12" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
@@ -2034,19 +2031,19 @@
       <c r="K12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>57011</v>
+        <v>57012</v>
       </c>
       <c r="B13" s="1">
-        <v>57011</v>
+        <v>57012</v>
       </c>
       <c r="C13" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>53</v>
@@ -2063,19 +2060,16 @@
       <c r="K13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>57012</v>
+        <v>57013</v>
       </c>
       <c r="B14" s="1">
-        <v>57012</v>
+        <v>57013</v>
       </c>
       <c r="C14" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>54</v>
@@ -2083,11 +2077,17 @@
       <c r="E14" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="F14" s="5">
+        <v>46101</v>
+      </c>
       <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>9999</v>
+        <v>2</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>1</v>
@@ -2095,13 +2095,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>57013</v>
+        <v>57014</v>
       </c>
       <c r="B15" s="1">
-        <v>57013</v>
+        <v>57014</v>
       </c>
       <c r="C15" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>55</v>
@@ -2110,7 +2110,7 @@
         <v>35</v>
       </c>
       <c r="F15" s="5">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -2125,116 +2125,81 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="1">
-        <v>57014</v>
-      </c>
-      <c r="B16" s="1">
-        <v>57014</v>
-      </c>
-      <c r="C16" s="1">
-        <v>14</v>
-      </c>
-      <c r="D16" s="1" t="s">
+    <row r="16" s="9" customFormat="1" spans="1:13">
+      <c r="A16" s="9">
+        <v>57015</v>
+      </c>
+      <c r="B16" s="9">
+        <v>57015</v>
+      </c>
+      <c r="C16" s="9">
+        <v>15</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="5">
-        <v>46102</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
       <c r="K16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" s="9" customFormat="1" spans="1:13">
-      <c r="A17" s="9">
-        <v>57015</v>
-      </c>
-      <c r="B17" s="9">
-        <v>57015</v>
-      </c>
-      <c r="C17" s="9">
-        <v>15</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="M16" s="17"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="1">
+        <v>57016</v>
+      </c>
+      <c r="B17" s="1">
+        <v>57016</v>
+      </c>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="9">
+      <c r="F17" s="5">
+        <v>46103</v>
+      </c>
+      <c r="G17" s="1">
         <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
+        <v>90</v>
+      </c>
       <c r="K17" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M17" s="17"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="1">
-        <v>57016</v>
-      </c>
-      <c r="B18" s="1">
-        <v>57016</v>
-      </c>
-      <c r="C18" s="1">
-        <v>16</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="M17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="5">
-        <v>46103</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>90</v>
-      </c>
-      <c r="K18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="5" t="s">
+      <c r="N17" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F14">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
+  <conditionalFormatting sqref="F15">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
+  <conditionalFormatting sqref="F17">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2254,10 +2219,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2265,7 +2230,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2273,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2281,7 +2246,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2321,7 +2286,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2329,7 +2294,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2337,7 +2302,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2345,7 +2310,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2353,7 +2318,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2361,7 +2326,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2369,7 +2334,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2377,7 +2342,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2385,7 +2350,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2393,7 +2358,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -131,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -150,29 +150,6 @@
           </rPr>
           <t xml:space="preserve">
 填写dropGruop.xlsx表中 trunkID 字段的值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-填写condition.xlsx表中ID值
-参数：ID_值</t>
         </r>
       </text>
     </comment>
@@ -194,6 +171,29 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+填写condition.xlsx表中ID值
+参数：ID_值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 填写 condition.xlsx  ID</t>
         </r>
       </text>
@@ -308,7 +308,32 @@
         </r>
       </text>
     </comment>
-    <comment ref="L12" authorId="0">
+    <comment ref="M10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+初始天数30天</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -335,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
   <si>
     <t>序列ID</t>
   </si>
@@ -373,6 +398,9 @@
     <t>值1</t>
   </si>
   <si>
+    <t>值2</t>
+  </si>
+  <si>
     <t>道具掉落包ID</t>
   </si>
   <si>
@@ -430,6 +458,9 @@
     <t>value</t>
   </si>
   <si>
+    <t>valueParam</t>
+  </si>
+  <si>
     <t>dropid</t>
   </si>
   <si>
@@ -472,70 +503,70 @@
     <t>1_2_3_4_5_6_7_8_9_10_101_102_103_104_105_106_107_108</t>
   </si>
   <si>
+    <t>商业-官方派奖</t>
+  </si>
+  <si>
+    <t>2025/09/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2025/09/30 23:59:59</t>
+  </si>
+  <si>
+    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
+  </si>
+  <si>
+    <t>10001_1000</t>
+  </si>
+  <si>
+    <t>活跃-每日签到</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
+  </si>
+  <si>
+    <t>商业-首充</t>
+  </si>
+  <si>
+    <t>商业-每日首充</t>
+  </si>
+  <si>
+    <t>商业-特惠礼包</t>
+  </si>
+  <si>
+    <t>商业-阶梯集合礼包</t>
+  </si>
+  <si>
+    <t>商业-金币投资</t>
+  </si>
+  <si>
+    <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>100006_100007_100008_100009_100010</t>
+  </si>
+  <si>
+    <t>12001_10000</t>
+  </si>
+  <si>
+    <t>#备注1</t>
+  </si>
+  <si>
+    <t>#备注2</t>
+  </si>
+  <si>
+    <t>功能名称</t>
+  </si>
+  <si>
+    <t>功能-道具掉落</t>
+  </si>
+  <si>
+    <t>功能-周卡\月卡\永久卡</t>
+  </si>
+  <si>
+    <t>功能-商城</t>
+  </si>
+  <si>
     <t>活跃-积分大奖</t>
-  </si>
-  <si>
-    <t>2025/09/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2025/09/30 23:59:59</t>
-  </si>
-  <si>
-    <t>商业-官方派奖</t>
-  </si>
-  <si>
-    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
-  </si>
-  <si>
-    <t>10001_1000</t>
-  </si>
-  <si>
-    <t>活跃-每日签到</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
-  </si>
-  <si>
-    <t>商业-首充</t>
-  </si>
-  <si>
-    <t>商业-每日首充</t>
-  </si>
-  <si>
-    <t>商业-特惠礼包</t>
-  </si>
-  <si>
-    <t>商业-阶梯集合礼包</t>
-  </si>
-  <si>
-    <t>商业-金币投资</t>
-  </si>
-  <si>
-    <t>活跃-收集拼图</t>
-  </si>
-  <si>
-    <t>100006_100007_100008_100009_100010</t>
-  </si>
-  <si>
-    <t>12001_10000</t>
-  </si>
-  <si>
-    <t>#备注1</t>
-  </si>
-  <si>
-    <t>#备注2</t>
-  </si>
-  <si>
-    <t>功能名称</t>
-  </si>
-  <si>
-    <t>功能-道具掉落</t>
-  </si>
-  <si>
-    <t>功能-周卡\月卡\永久卡</t>
-  </si>
-  <si>
-    <t>功能-商城</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1258,6 +1289,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1612,7 +1644,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
@@ -1626,15 +1658,16 @@
     <col min="9" max="10" width="21.875" style="10" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.375" style="5" customWidth="1"/>
-    <col min="14" max="14" width="16.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1"/>
-    <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16.375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="16.375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="18.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="26.75" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" spans="1:15">
+    <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1671,107 +1704,116 @@
       <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
+      <c r="P1" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
+    </row>
+    <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A3" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="13" t="s">
         <v>31</v>
       </c>
+      <c r="M3" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="N3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
+      <c r="O3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1784,9 +1826,10 @@
       <c r="J4" s="12"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="14"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="13"/>
       <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
@@ -1799,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1814,7 +1857,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1828,10 +1871,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1843,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1857,10 +1900,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1872,10 +1915,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -1886,10 +1929,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1901,13 +1944,13 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="5">
+        <v>43</v>
+      </c>
+      <c r="N8" s="5">
         <v>100011</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>42</v>
+      <c r="O8" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1921,10 +1964,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1936,94 +1979,94 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
-        <v>57008</v>
+        <v>57009</v>
       </c>
       <c r="B10" s="1">
-        <v>57008</v>
+        <v>57009</v>
       </c>
       <c r="C10" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10" s="5">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="G10" s="1">
         <v>2</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16">
+        <v>1000000000</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
-        <v>57009</v>
+        <v>57010</v>
       </c>
       <c r="B11" s="1">
-        <v>57009</v>
+        <v>57010</v>
       </c>
       <c r="C11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="5">
-        <v>46105</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1">
-        <v>2</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>9999</v>
       </c>
       <c r="K11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="1">
-        <v>57010</v>
+        <v>57011</v>
       </c>
       <c r="B12" s="1">
-        <v>57010</v>
+        <v>57011</v>
       </c>
       <c r="C12" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2034,25 +2077,25 @@
       <c r="K12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>57011</v>
+        <v>57012</v>
       </c>
       <c r="B13" s="1">
-        <v>57011</v>
+        <v>57012</v>
       </c>
       <c r="C13" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2063,31 +2106,34 @@
       <c r="K13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>57012</v>
+        <v>57013</v>
       </c>
       <c r="B14" s="1">
-        <v>57012</v>
+        <v>57013</v>
       </c>
       <c r="C14" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="F14" s="5">
+        <v>46101</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>9999</v>
+        <v>2</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>1</v>
@@ -2095,146 +2141,111 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>57013</v>
+        <v>57014</v>
       </c>
       <c r="B15" s="1">
-        <v>57013</v>
+        <v>57014</v>
       </c>
       <c r="C15" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F15" s="5">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="1">
-        <v>57014</v>
-      </c>
-      <c r="B16" s="1">
-        <v>57014</v>
-      </c>
-      <c r="C16" s="1">
-        <v>14</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>56</v>
+    <row r="16" s="9" customFormat="1" spans="1:14">
+      <c r="A16" s="9">
+        <v>57015</v>
+      </c>
+      <c r="B16" s="9">
+        <v>57015</v>
+      </c>
+      <c r="C16" s="9">
+        <v>15</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="5">
-        <v>46102</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>47</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
       <c r="K16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" s="9" customFormat="1" spans="1:13">
-      <c r="A17" s="9">
-        <v>57015</v>
-      </c>
-      <c r="B17" s="9">
-        <v>57015</v>
-      </c>
-      <c r="C17" s="9">
-        <v>15</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>57</v>
+      <c r="N16" s="18"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="1">
+        <v>57016</v>
+      </c>
+      <c r="B17" s="1">
+        <v>57016</v>
+      </c>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="9">
+        <v>37</v>
+      </c>
+      <c r="F17" s="5">
+        <v>46103</v>
+      </c>
+      <c r="G17" s="1">
         <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
+        <v>90</v>
+      </c>
       <c r="K17" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M17" s="17"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="1">
-        <v>57016</v>
-      </c>
-      <c r="B18" s="1">
-        <v>57016</v>
-      </c>
-      <c r="C18" s="1">
-        <v>16</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="5">
-        <v>46103</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>90</v>
-      </c>
-      <c r="K18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="N18" s="1" t="s">
+      <c r="N17" s="5" t="s">
         <v>60</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F14">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
+  <conditionalFormatting sqref="F15">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
+  <conditionalFormatting sqref="F17">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2254,10 +2265,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2265,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2273,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2281,7 +2292,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2289,7 +2300,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2297,7 +2308,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2305,7 +2316,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2313,7 +2324,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2321,7 +2332,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2329,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2337,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2345,7 +2356,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2353,7 +2364,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2361,7 +2372,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2369,7 +2380,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2377,7 +2388,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2385,7 +2396,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2393,7 +2404,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -131,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -150,29 +150,6 @@
           </rPr>
           <t xml:space="preserve">
 填写dropGruop.xlsx表中 trunkID 字段的值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-填写condition.xlsx表中ID值
-参数：ID_值</t>
         </r>
       </text>
     </comment>
@@ -194,6 +171,29 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+填写condition.xlsx表中ID值
+参数：ID_值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 填写 condition.xlsx  ID</t>
         </r>
       </text>
@@ -305,6 +305,31 @@
           </rPr>
           <t xml:space="preserve">
 对应配置表的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+初始天数30天</t>
         </r>
       </text>
     </comment>
@@ -335,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
   <si>
     <t>序列ID</t>
   </si>
@@ -373,6 +398,9 @@
     <t>值1</t>
   </si>
   <si>
+    <t>值2</t>
+  </si>
+  <si>
     <t>道具掉落包ID</t>
   </si>
   <si>
@@ -428,6 +456,9 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>valueParam</t>
   </si>
   <si>
     <t>dropid</t>
@@ -1209,7 +1240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1258,6 +1289,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1612,7 +1644,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
@@ -1626,15 +1658,16 @@
     <col min="9" max="10" width="21.875" style="10" customWidth="1"/>
     <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.375" style="5" customWidth="1"/>
-    <col min="14" max="14" width="16.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1"/>
-    <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16.375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="16.375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="18.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="26.75" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" spans="1:15">
+    <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1671,107 +1704,116 @@
       <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
+      <c r="P1" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
+    </row>
+    <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A3" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="13" t="s">
         <v>31</v>
       </c>
+      <c r="M3" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="N3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
+      <c r="O3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1784,9 +1826,10 @@
       <c r="J4" s="12"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="14"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="13"/>
       <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
@@ -1799,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1814,7 +1857,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1828,10 +1871,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1843,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1857,10 +1900,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1872,10 +1915,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -1886,10 +1929,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1901,13 +1944,13 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="5">
+        <v>43</v>
+      </c>
+      <c r="N8" s="5">
         <v>100011</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>42</v>
+      <c r="O8" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1921,10 +1964,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1936,10 +1979,10 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <v>57009</v>
       </c>
@@ -1950,10 +1993,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10" s="5">
         <v>46105</v>
@@ -1962,19 +2005,22 @@
         <v>2</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="M10" s="16">
+        <v>1000000000</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1988,10 +2034,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -2003,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2017,10 +2063,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2046,10 +2092,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2072,10 +2118,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F14" s="5">
         <v>46101</v>
@@ -2084,10 +2130,10 @@
         <v>2</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>1</v>
@@ -2104,10 +2150,10 @@
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F15" s="5">
         <v>46102</v>
@@ -2116,16 +2162,16 @@
         <v>2</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" s="9" customFormat="1" spans="1:13">
+    <row r="16" s="9" customFormat="1" spans="1:14">
       <c r="A16" s="9">
         <v>57015</v>
       </c>
@@ -2136,10 +2182,10 @@
         <v>15</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G16" s="9">
         <v>1</v>
@@ -2147,14 +2193,14 @@
       <c r="H16" s="1">
         <v>9999</v>
       </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
       <c r="K16" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M16" s="17"/>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="N16" s="18"/>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="1">
         <v>57016</v>
       </c>
@@ -2165,10 +2211,10 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F17" s="5">
         <v>46103</v>
@@ -2182,11 +2228,11 @@
       <c r="K17" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>59</v>
+      <c r="N17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2219,10 +2265,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2230,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2238,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2246,7 +2292,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2254,7 +2300,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2262,7 +2308,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2270,7 +2316,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2278,7 +2324,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2286,7 +2332,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2294,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2302,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2310,7 +2356,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2318,7 +2364,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2326,7 +2372,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2334,7 +2380,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2342,7 +2388,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2350,7 +2396,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2358,7 +2404,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -329,7 +329,10 @@
 官方派奖：奖池金币数量
 总量 ÷ 平均中奖金额 = 中奖次数
 1000000000 ÷ 718000 = 1392.7577
-初始天数30天</t>
+初始天数30天
+========================================
+统计类型：1 有效下注 、 2 充值 
+</t>
         </r>
       </text>
     </comment>
@@ -360,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
   <si>
     <t>序列ID</t>
   </si>
@@ -513,6 +516,9 @@
   </si>
   <si>
     <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
+  </si>
+  <si>
+    <t>2000000000_1</t>
   </si>
   <si>
     <t>10001_1000</t>
@@ -2016,11 +2022,11 @@
       <c r="L10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M10" s="16">
-        <v>1000000000</v>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2034,7 +2040,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>37</v>
@@ -2049,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2063,7 +2069,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>37</v>
@@ -2092,7 +2098,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>37</v>
@@ -2118,7 +2124,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>37</v>
@@ -2150,7 +2156,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>37</v>
@@ -2182,7 +2188,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>37</v>
@@ -2211,7 +2217,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>37</v>
@@ -2229,10 +2235,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2265,10 +2271,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2276,7 +2282,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2284,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2292,7 +2298,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2332,7 +2338,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2340,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2356,7 +2362,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2364,7 +2370,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2372,7 +2378,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2380,7 +2386,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2388,7 +2394,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2396,7 +2402,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2404,7 +2410,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -358,12 +358,56 @@
         </r>
       </text>
     </comment>
+    <comment ref="L16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置表-GrowthFund.xlsx中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+参数：售价_原价_总计获得</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
   <si>
     <t>序列ID</t>
   </si>
@@ -542,37 +586,46 @@
     <t>商业-阶梯集合礼包</t>
   </si>
   <si>
+    <t>商业-成长基金</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20</t>
+  </si>
+  <si>
+    <t>599_9999_21000000</t>
+  </si>
+  <si>
+    <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>100006_100007_100008_100009_100010</t>
+  </si>
+  <si>
+    <t>12001_10000</t>
+  </si>
+  <si>
+    <t>#备注1</t>
+  </si>
+  <si>
+    <t>#备注2</t>
+  </si>
+  <si>
+    <t>功能名称</t>
+  </si>
+  <si>
+    <t>功能-道具掉落</t>
+  </si>
+  <si>
+    <t>功能-周卡\月卡\永久卡</t>
+  </si>
+  <si>
+    <t>功能-商城</t>
+  </si>
+  <si>
+    <t>活跃-积分大奖</t>
+  </si>
+  <si>
     <t>商业-金币投资</t>
-  </si>
-  <si>
-    <t>活跃-收集拼图</t>
-  </si>
-  <si>
-    <t>100006_100007_100008_100009_100010</t>
-  </si>
-  <si>
-    <t>12001_10000</t>
-  </si>
-  <si>
-    <t>#备注1</t>
-  </si>
-  <si>
-    <t>#备注2</t>
-  </si>
-  <si>
-    <t>功能名称</t>
-  </si>
-  <si>
-    <t>功能-道具掉落</t>
-  </si>
-  <si>
-    <t>功能-周卡\月卡\永久卡</t>
-  </si>
-  <si>
-    <t>功能-商城</t>
-  </si>
-  <si>
-    <t>活跃-积分大奖</t>
   </si>
 </sst>
 </file>
@@ -1653,20 +1706,20 @@
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.375" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.875" style="10" customWidth="1"/>
-    <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="16.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.40833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.08333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="10" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="41.875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="15.375" style="1" customWidth="1"/>
     <col min="16" max="16" width="18.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="9" style="1"/>
     <col min="18" max="18" width="26.75" style="1" customWidth="1"/>
@@ -2204,6 +2257,12 @@
       <c r="K16" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="N16" s="18"/>
     </row>
     <row r="17" spans="1:15">
@@ -2217,7 +2276,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>37</v>
@@ -2235,10 +2294,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2271,10 +2330,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2282,7 +2341,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2290,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2298,7 +2357,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2338,7 +2397,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2346,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2402,7 +2461,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2410,7 +2469,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -104,7 +104,8 @@
 2、【限时活动】
 时间段内开启：
 注：配置[开启\结束时间、是否开启] 字段,这两个字段为“&amp;&amp;”和的关系
-，不需要配置[持续时间]字段</t>
+，不需要配置[持续时间]字段
+3.【循环活动】根据日期来</t>
         </r>
       </text>
     </comment>
@@ -331,7 +332,7 @@
 1000000000 ÷ 718000 = 1392.7577
 初始天数30天
 ========================================
-统计类型：1 有效下注 、 2 充值 
+统计类型：充值 
 </t>
         </r>
       </text>
@@ -407,7 +408,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
   <si>
     <t>序列ID</t>
   </si>
@@ -553,43 +554,49 @@
     <t>商业-官方派奖</t>
   </si>
   <si>
+    <t>0 0 0 1,10,16 * ?</t>
+  </si>
+  <si>
+    <t>0 0 0 5,15,21 * ?</t>
+  </si>
+  <si>
+    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
+  </si>
+  <si>
+    <t>2000000000_1000</t>
+  </si>
+  <si>
+    <t>10001_1000</t>
+  </si>
+  <si>
+    <t>活跃-每日签到</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
+  </si>
+  <si>
+    <t>商业-首充</t>
+  </si>
+  <si>
+    <t>商业-每日首充</t>
+  </si>
+  <si>
+    <t>商业-特惠礼包</t>
+  </si>
+  <si>
     <t>2025/09/01 00:00:00</t>
   </si>
   <si>
     <t>2025/09/30 23:59:59</t>
   </si>
   <si>
-    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
-  </si>
-  <si>
-    <t>2000000000_1</t>
-  </si>
-  <si>
-    <t>10001_1000</t>
-  </si>
-  <si>
-    <t>活跃-每日签到</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
-  </si>
-  <si>
-    <t>商业-首充</t>
-  </si>
-  <si>
-    <t>商业-每日首充</t>
-  </si>
-  <si>
-    <t>商业-特惠礼包</t>
-  </si>
-  <si>
     <t>商业-阶梯集合礼包</t>
   </si>
   <si>
     <t>商业-成长基金</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20</t>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
   </si>
   <si>
     <t>599_9999_21000000</t>
@@ -1348,7 +1355,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1717,7 +1724,7 @@
     <col min="9" max="10" width="21.25" style="10" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.4083333333333" style="1" customWidth="1"/>
     <col min="14" max="14" width="41.875" style="5" customWidth="1"/>
     <col min="15" max="15" width="15.375" style="1" customWidth="1"/>
     <col min="16" max="16" width="18.625" style="1" customWidth="1"/>
@@ -2061,7 +2068,7 @@
         <v>46105</v>
       </c>
       <c r="G10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>48</v>
@@ -2189,10 +2196,10 @@
         <v>2</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>1</v>
@@ -2209,7 +2216,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>37</v>
@@ -2221,10 +2228,10 @@
         <v>2</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
@@ -2241,7 +2248,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>37</v>
@@ -2258,10 +2265,10 @@
         <v>1</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N16" s="18"/>
     </row>
@@ -2276,7 +2283,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>37</v>
@@ -2294,24 +2301,24 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F17">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2330,10 +2337,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2341,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2349,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2357,7 +2364,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2397,7 +2404,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2405,7 +2412,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2453,7 +2460,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2461,7 +2468,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2469,7 +2476,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -104,7 +104,8 @@
 2、【限时活动】
 时间段内开启：
 注：配置[开启\结束时间、是否开启] 字段,这两个字段为“&amp;&amp;”和的关系
-，不需要配置[持续时间]字段</t>
+，不需要配置[持续时间]字段
+3.【循环活动】根据日期来</t>
         </r>
       </text>
     </comment>
@@ -331,7 +332,7 @@
 1000000000 ÷ 718000 = 1392.7577
 初始天数30天
 ========================================
-统计类型：1 有效下注 、 2 充值 
+统计类型：充值 
 </t>
         </r>
       </text>
@@ -355,6 +356,50 @@
           </rPr>
           <t xml:space="preserve">
 对应配置表的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置表-GrowthFund.xlsx中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+参数：售价_原价_总计获得</t>
         </r>
       </text>
     </comment>
@@ -363,7 +408,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
   <si>
     <t>序列ID</t>
   </si>
@@ -509,70 +554,85 @@
     <t>商业-官方派奖</t>
   </si>
   <si>
+    <t>0 0 0 1,10,16 * ?</t>
+  </si>
+  <si>
+    <t>0 0 0 5,15,21 * ?</t>
+  </si>
+  <si>
+    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
+  </si>
+  <si>
+    <t>2000000000_1000</t>
+  </si>
+  <si>
+    <t>10001_1000</t>
+  </si>
+  <si>
+    <t>活跃-每日签到</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
+  </si>
+  <si>
+    <t>商业-首充</t>
+  </si>
+  <si>
+    <t>商业-每日首充</t>
+  </si>
+  <si>
+    <t>商业-特惠礼包</t>
+  </si>
+  <si>
     <t>2025/09/01 00:00:00</t>
   </si>
   <si>
     <t>2025/09/30 23:59:59</t>
   </si>
   <si>
-    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
-  </si>
-  <si>
-    <t>2000000000_1</t>
-  </si>
-  <si>
-    <t>10001_1000</t>
-  </si>
-  <si>
-    <t>活跃-每日签到</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
-  </si>
-  <si>
-    <t>商业-首充</t>
-  </si>
-  <si>
-    <t>商业-每日首充</t>
-  </si>
-  <si>
-    <t>商业-特惠礼包</t>
-  </si>
-  <si>
     <t>商业-阶梯集合礼包</t>
   </si>
   <si>
+    <t>商业-成长基金</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
+  </si>
+  <si>
+    <t>599_9999_21000000</t>
+  </si>
+  <si>
+    <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>100006_100007_100008_100009_100010</t>
+  </si>
+  <si>
+    <t>12001_10000</t>
+  </si>
+  <si>
+    <t>#备注1</t>
+  </si>
+  <si>
+    <t>#备注2</t>
+  </si>
+  <si>
+    <t>功能名称</t>
+  </si>
+  <si>
+    <t>功能-道具掉落</t>
+  </si>
+  <si>
+    <t>功能-周卡\月卡\永久卡</t>
+  </si>
+  <si>
+    <t>功能-商城</t>
+  </si>
+  <si>
+    <t>活跃-积分大奖</t>
+  </si>
+  <si>
     <t>商业-金币投资</t>
-  </si>
-  <si>
-    <t>活跃-收集拼图</t>
-  </si>
-  <si>
-    <t>100006_100007_100008_100009_100010</t>
-  </si>
-  <si>
-    <t>12001_10000</t>
-  </si>
-  <si>
-    <t>#备注1</t>
-  </si>
-  <si>
-    <t>#备注2</t>
-  </si>
-  <si>
-    <t>功能名称</t>
-  </si>
-  <si>
-    <t>功能-道具掉落</t>
-  </si>
-  <si>
-    <t>功能-周卡\月卡\永久卡</t>
-  </si>
-  <si>
-    <t>功能-商城</t>
-  </si>
-  <si>
-    <t>活跃-积分大奖</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1355,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1653,20 +1713,20 @@
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.375" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.875" style="10" customWidth="1"/>
-    <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="16.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.40833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.08333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="10" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.4083333333333" style="1" customWidth="1"/>
+    <col min="14" max="14" width="41.875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="15.375" style="1" customWidth="1"/>
     <col min="16" max="16" width="18.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="9" style="1"/>
     <col min="18" max="18" width="26.75" style="1" customWidth="1"/>
@@ -2008,7 +2068,7 @@
         <v>46105</v>
       </c>
       <c r="G10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>48</v>
@@ -2136,10 +2196,10 @@
         <v>2</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>1</v>
@@ -2156,7 +2216,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>37</v>
@@ -2168,10 +2228,10 @@
         <v>2</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
@@ -2188,7 +2248,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>37</v>
@@ -2204,6 +2264,12 @@
       <c r="K16" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="N16" s="18"/>
     </row>
     <row r="17" spans="1:15">
@@ -2217,7 +2283,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>37</v>
@@ -2235,24 +2301,24 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F17">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2271,10 +2337,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2282,7 +2348,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2290,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2298,7 +2364,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2338,7 +2404,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2346,7 +2412,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2394,7 +2460,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2402,7 +2468,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2410,7 +2476,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -596,7 +596,7 @@
     <t>商业-成长基金</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
   </si>
   <si>
     <t>599_9999_21000000</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -150,52 +150,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-填写dropGruop.xlsx表中 trunkID 字段的值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-填写condition.xlsx表中ID值
-参数：ID_值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-填写 condition.xlsx  ID</t>
+填写dropConfig.xlsx表中 id 字段的值</t>
         </r>
       </text>
     </comment>
@@ -408,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
   <si>
     <t>序列ID</t>
   </si>
@@ -449,13 +404,7 @@
     <t>值2</t>
   </si>
   <si>
-    <t>道具掉落包ID</t>
-  </si>
-  <si>
-    <t>掉落条件</t>
-  </si>
-  <si>
-    <t>进度触发类型</t>
+    <t>掉落id</t>
   </si>
   <si>
     <t>int</t>
@@ -509,16 +458,10 @@
     <t>valueParam</t>
   </si>
   <si>
-    <t>dropid</t>
-  </si>
-  <si>
-    <t>dropcondition</t>
-  </si>
-  <si>
-    <t>triggerType</t>
-  </si>
-  <si>
-    <t>功能-每日奖金(原月卡)</t>
+    <t>dropConfigId</t>
+  </si>
+  <si>
+    <t>付费-每日奖金(常驻)</t>
   </si>
   <si>
     <t>1_1</t>
@@ -527,54 +470,117 @@
     <t>1_2_3</t>
   </si>
   <si>
+    <t>活跃-摇钱树(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8</t>
+  </si>
+  <si>
+    <t>付费-储钱罐(常驻)</t>
+  </si>
+  <si>
+    <t>活跃&amp;付费-刮刮乐(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_101_102_103_104</t>
+  </si>
+  <si>
+    <t>活跃-推广分享(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_101_102_103_104_105_106_107_108</t>
+  </si>
+  <si>
+    <t>付费-官方派奖(常驻)</t>
+  </si>
+  <si>
+    <t>0 0 0 1,10,16 * ?</t>
+  </si>
+  <si>
+    <t>0 0 0 5,15,21 * ?</t>
+  </si>
+  <si>
+    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
+  </si>
+  <si>
+    <t>2000000000_1000</t>
+  </si>
+  <si>
+    <t>活跃-每日签到(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
+  </si>
+  <si>
+    <t>付费-首充(常驻)</t>
+  </si>
+  <si>
+    <t>付费-每日首充</t>
+  </si>
+  <si>
+    <t>付费-特惠礼包</t>
+  </si>
+  <si>
+    <t>2025/09/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2025/09/30 23:59:59</t>
+  </si>
+  <si>
+    <t>付费-集合礼包</t>
+  </si>
+  <si>
+    <t>活跃&amp;付费-成长基金(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
+  </si>
+  <si>
+    <t>599_9999_21000000</t>
+  </si>
+  <si>
+    <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>#备注1</t>
+  </si>
+  <si>
+    <t>#备注2</t>
+  </si>
+  <si>
+    <t>功能名称</t>
+  </si>
+  <si>
+    <t>功能-道具掉落</t>
+  </si>
+  <si>
+    <t>功能-周卡\月卡\永久卡</t>
+  </si>
+  <si>
     <t>商业-摇钱树-常驻</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8</t>
-  </si>
-  <si>
     <t>商业-储钱罐-常驻</t>
   </si>
   <si>
     <t>商业-刮刮卡-常驻</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8_9_101_102_103_104</t>
-  </si>
-  <si>
-    <t>12001_100000</t>
-  </si>
-  <si>
     <t>活跃-推广分享功能</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8_9_10_101_102_103_104_105_106_107_108</t>
+    <t>功能-商城</t>
+  </si>
+  <si>
+    <t>活跃-积分大奖</t>
   </si>
   <si>
     <t>商业-官方派奖</t>
   </si>
   <si>
-    <t>0 0 0 1,10,16 * ?</t>
-  </si>
-  <si>
-    <t>0 0 0 5,15,21 * ?</t>
-  </si>
-  <si>
-    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
-  </si>
-  <si>
-    <t>2000000000_1000</t>
-  </si>
-  <si>
-    <t>10001_1000</t>
-  </si>
-  <si>
     <t>活跃-每日签到</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
-  </si>
-  <si>
     <t>商业-首充</t>
   </si>
   <si>
@@ -584,55 +590,13 @@
     <t>商业-特惠礼包</t>
   </si>
   <si>
-    <t>2025/09/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2025/09/30 23:59:59</t>
-  </si>
-  <si>
     <t>商业-阶梯集合礼包</t>
   </si>
   <si>
-    <t>商业-成长基金</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
-  </si>
-  <si>
-    <t>599_9999_21000000</t>
-  </si>
-  <si>
-    <t>活跃-收集拼图</t>
-  </si>
-  <si>
-    <t>100006_100007_100008_100009_100010</t>
-  </si>
-  <si>
-    <t>12001_10000</t>
-  </si>
-  <si>
-    <t>#备注1</t>
-  </si>
-  <si>
-    <t>#备注2</t>
-  </si>
-  <si>
-    <t>功能名称</t>
-  </si>
-  <si>
-    <t>功能-道具掉落</t>
-  </si>
-  <si>
-    <t>功能-周卡\月卡\永久卡</t>
-  </si>
-  <si>
-    <t>功能-商城</t>
-  </si>
-  <si>
-    <t>活跃-积分大奖</t>
-  </si>
-  <si>
     <t>商业-金币投资</t>
+  </si>
+  <si>
+    <t>我的赌场</t>
   </si>
 </sst>
 </file>
@@ -645,7 +609,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -679,6 +643,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -827,12 +797,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1176,137 +1146,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1334,6 +1304,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1342,6 +1315,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -1349,13 +1325,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1710,192 +1686,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.40833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.08333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="10" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="11" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.4083333333333" style="1" customWidth="1"/>
     <col min="14" max="14" width="41.875" style="5" customWidth="1"/>
-    <col min="15" max="15" width="15.375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="18.625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="26.75" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="15" max="15" width="9" style="1"/>
+    <col min="16" max="16" width="26.75" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="11" t="s">
+    <row r="1" s="8" customFormat="1" spans="1:14">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+    </row>
+    <row r="2" s="8" customFormat="1" spans="1:14">
+      <c r="A2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="B2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="11" t="s">
+      <c r="F2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="J2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11" t="s">
+      <c r="K2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="L2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="M2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="N2" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" s="8" customFormat="1" spans="1:14">
+      <c r="A3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="B3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="I3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="K3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="M3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="N3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
+    </row>
+    <row r="4" s="8" customFormat="1" spans="1:14">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
@@ -1908,10 +1862,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1923,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1937,10 +1891,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1952,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1966,10 +1920,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1981,10 +1935,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -1995,10 +1949,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2010,13 +1964,10 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N8" s="5">
-        <v>100011</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2030,10 +1981,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -2045,10 +1996,10 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>57009</v>
       </c>
@@ -2059,10 +2010,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F10" s="5">
         <v>46105</v>
@@ -2070,23 +2021,20 @@
       <c r="G10" s="1">
         <v>3</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>49</v>
+      <c r="I10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2100,10 +2048,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -2115,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2129,10 +2077,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2147,164 +2095,179 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="1">
+    <row r="13" s="9" customFormat="1" spans="1:14">
+      <c r="A13" s="9">
         <v>57012</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="9">
         <v>57012</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="9">
         <v>12</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="D13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9">
         <v>9999</v>
       </c>
-      <c r="K13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="1">
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="13"/>
+    </row>
+    <row r="14" s="9" customFormat="1" spans="1:14">
+      <c r="A14" s="9">
         <v>57013</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="9">
         <v>57013</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="9">
         <v>13</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="5">
+      <c r="D14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="13">
         <v>46101</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="9">
         <v>2</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="1">
+      <c r="H14" s="9"/>
+      <c r="I14" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" s="9" customFormat="1" spans="1:14">
+      <c r="A15" s="9">
         <v>57014</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="9">
         <v>57014</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="9">
         <v>14</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="5">
+      <c r="D15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="13">
         <v>46102</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="9">
         <v>2</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" s="9" customFormat="1" spans="1:14">
-      <c r="A16" s="9">
+      <c r="H15" s="9"/>
+      <c r="I15" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" s="10" customFormat="1" spans="1:14">
+      <c r="A16" s="10">
         <v>57015</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="10">
         <v>57015</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <v>15</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>61</v>
+      <c r="D16" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="9">
+        <v>33</v>
+      </c>
+      <c r="G16" s="10">
         <v>1</v>
       </c>
       <c r="H16" s="1">
         <v>9999</v>
       </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
       <c r="K16" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="N16" s="18"/>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="1">
+      <c r="L16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="20"/>
+    </row>
+    <row r="17" s="9" customFormat="1" spans="1:14">
+      <c r="A17" s="9">
         <v>57016</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="9">
         <v>57016</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="9">
         <v>16</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17" s="5">
+      <c r="D17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="13">
         <v>46103</v>
       </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="G17" s="9">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9">
         <v>90</v>
       </c>
-      <c r="K17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>66</v>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="13">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2337,10 +2300,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2348,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2356,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2364,7 +2327,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2372,7 +2335,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2380,7 +2343,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2388,7 +2351,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2396,7 +2359,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2404,7 +2367,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2412,7 +2375,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2420,7 +2383,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2428,7 +2391,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2436,7 +2399,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2444,7 +2407,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2452,7 +2415,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2460,7 +2423,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2468,7 +2431,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2476,7 +2439,15 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -150,52 +150,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-填写dropGruop.xlsx表中 trunkID 字段的值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-填写condition.xlsx表中ID值
-参数：ID_值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-填写 condition.xlsx  ID</t>
+填写dropConfig.xlsx表中 id 字段的值</t>
         </r>
       </text>
     </comment>
@@ -306,6 +261,28 @@
           </rPr>
           <t xml:space="preserve">
 对应配置表的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+时 分 秒 日期1,日期2,日期3 * ？</t>
         </r>
       </text>
     </comment>
@@ -408,7 +385,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="77">
   <si>
     <t>序列ID</t>
   </si>
@@ -449,21 +426,12 @@
     <t>值2</t>
   </si>
   <si>
-    <t>道具掉落包ID</t>
-  </si>
-  <si>
-    <t>掉落条件</t>
-  </si>
-  <si>
-    <t>进度触发类型</t>
+    <t>掉落id</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -509,16 +477,10 @@
     <t>valueParam</t>
   </si>
   <si>
-    <t>dropid</t>
-  </si>
-  <si>
-    <t>dropcondition</t>
-  </si>
-  <si>
-    <t>triggerType</t>
-  </si>
-  <si>
-    <t>功能-每日奖金(原月卡)</t>
+    <t>dropConfigId</t>
+  </si>
+  <si>
+    <t>付费-每日奖金(常驻)</t>
   </si>
   <si>
     <t>1_1</t>
@@ -527,54 +489,117 @@
     <t>1_2_3</t>
   </si>
   <si>
+    <t>活跃-摇钱树(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8</t>
+  </si>
+  <si>
+    <t>付费-储钱罐(常驻)</t>
+  </si>
+  <si>
+    <t>活跃&amp;付费-刮刮乐(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_101_102_103_104</t>
+  </si>
+  <si>
+    <t>活跃-推广分享(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_101_102_103_104_105_106_107_108</t>
+  </si>
+  <si>
+    <t>付费-官方派奖(常驻)</t>
+  </si>
+  <si>
+    <t>0 0 0 1,10,16 * ?</t>
+  </si>
+  <si>
+    <t>0 0 0 5,15,21 * ?</t>
+  </si>
+  <si>
+    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
+  </si>
+  <si>
+    <t>2000000000_1000</t>
+  </si>
+  <si>
+    <t>活跃-每日签到(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
+  </si>
+  <si>
+    <t>付费-首充(常驻)</t>
+  </si>
+  <si>
+    <t>付费-每日首充</t>
+  </si>
+  <si>
+    <t>付费-特惠礼包</t>
+  </si>
+  <si>
+    <t>2025/09/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2025/09/30 23:59:59</t>
+  </si>
+  <si>
+    <t>付费-集合礼包</t>
+  </si>
+  <si>
+    <t>活跃&amp;付费-成长基金(常驻)</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
+  </si>
+  <si>
+    <t>599_9999_21000000</t>
+  </si>
+  <si>
+    <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>#备注1</t>
+  </si>
+  <si>
+    <t>#备注2</t>
+  </si>
+  <si>
+    <t>功能名称</t>
+  </si>
+  <si>
+    <t>功能-道具掉落</t>
+  </si>
+  <si>
+    <t>功能-周卡\月卡\永久卡</t>
+  </si>
+  <si>
     <t>商业-摇钱树-常驻</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8</t>
-  </si>
-  <si>
     <t>商业-储钱罐-常驻</t>
   </si>
   <si>
     <t>商业-刮刮卡-常驻</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8_9_101_102_103_104</t>
-  </si>
-  <si>
-    <t>12001_100000</t>
-  </si>
-  <si>
     <t>活跃-推广分享功能</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8_9_10_101_102_103_104_105_106_107_108</t>
+    <t>功能-商城</t>
+  </si>
+  <si>
+    <t>活跃-积分大奖</t>
   </si>
   <si>
     <t>商业-官方派奖</t>
   </si>
   <si>
-    <t>0 0 0 1,10,16 * ?</t>
-  </si>
-  <si>
-    <t>0 0 0 5,15,21 * ?</t>
-  </si>
-  <si>
-    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
-  </si>
-  <si>
-    <t>2000000000_1000</t>
-  </si>
-  <si>
-    <t>10001_1000</t>
-  </si>
-  <si>
     <t>活跃-每日签到</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
-  </si>
-  <si>
     <t>商业-首充</t>
   </si>
   <si>
@@ -584,55 +609,13 @@
     <t>商业-特惠礼包</t>
   </si>
   <si>
-    <t>2025/09/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2025/09/30 23:59:59</t>
-  </si>
-  <si>
     <t>商业-阶梯集合礼包</t>
   </si>
   <si>
-    <t>商业-成长基金</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
-  </si>
-  <si>
-    <t>599_9999_21000000</t>
-  </si>
-  <si>
-    <t>活跃-收集拼图</t>
-  </si>
-  <si>
-    <t>100006_100007_100008_100009_100010</t>
-  </si>
-  <si>
-    <t>12001_10000</t>
-  </si>
-  <si>
-    <t>#备注1</t>
-  </si>
-  <si>
-    <t>#备注2</t>
-  </si>
-  <si>
-    <t>功能名称</t>
-  </si>
-  <si>
-    <t>功能-道具掉落</t>
-  </si>
-  <si>
-    <t>功能-周卡\月卡\永久卡</t>
-  </si>
-  <si>
-    <t>功能-商城</t>
-  </si>
-  <si>
-    <t>活跃-积分大奖</t>
-  </si>
-  <si>
     <t>商业-金币投资</t>
+  </si>
+  <si>
+    <t>我的赌场</t>
   </si>
 </sst>
 </file>
@@ -645,7 +628,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -679,6 +662,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1176,137 +1165,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1334,6 +1323,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1342,6 +1334,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -1349,13 +1344,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1710,192 +1705,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.40833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.08333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="10" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="11" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.4083333333333" style="1" customWidth="1"/>
     <col min="14" max="14" width="41.875" style="5" customWidth="1"/>
-    <col min="15" max="15" width="15.375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="18.625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="26.75" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="15" max="15" width="9" style="1"/>
+    <col min="16" max="16" width="26.75" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="11" t="s">
+    <row r="1" s="8" customFormat="1" ht="15" spans="1:14">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+    </row>
+    <row r="2" s="8" customFormat="1" ht="15" spans="1:14">
+      <c r="A2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="B2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="11" t="s">
+      <c r="F2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11" t="s">
+      <c r="L2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="M2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="8" customFormat="1" ht="15" spans="1:14">
+      <c r="A3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="C3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="11" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11" t="s">
+      <c r="H3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="I3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="J3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="K3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="L3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="M3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="N3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
+    </row>
+    <row r="4" s="8" customFormat="1" ht="15" spans="1:14">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
@@ -1908,10 +1881,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1923,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1937,10 +1910,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1952,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1966,10 +1939,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1981,10 +1954,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -1995,10 +1968,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2010,13 +1983,10 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N8" s="5">
-        <v>100011</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2030,10 +2000,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -2045,10 +2015,10 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>57009</v>
       </c>
@@ -2059,10 +2029,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F10" s="5">
         <v>46105</v>
@@ -2070,23 +2040,20 @@
       <c r="G10" s="1">
         <v>3</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>49</v>
+      <c r="I10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2100,10 +2067,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -2115,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2129,10 +2096,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -2147,178 +2114,193 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="1">
+    <row r="13" s="9" customFormat="1" spans="1:14">
+      <c r="A13" s="9">
         <v>57012</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="9">
         <v>57012</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="9">
         <v>12</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="D13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9">
         <v>9999</v>
       </c>
-      <c r="K13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="1">
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="13"/>
+    </row>
+    <row r="14" s="9" customFormat="1" spans="1:14">
+      <c r="A14" s="9">
         <v>57013</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="9">
         <v>57013</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="9">
         <v>13</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="5">
+      <c r="D14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="13">
         <v>46101</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="9">
         <v>2</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="1">
+      <c r="H14" s="9"/>
+      <c r="I14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" s="9" customFormat="1" spans="1:14">
+      <c r="A15" s="9">
         <v>57014</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="9">
         <v>57014</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="9">
         <v>14</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="5">
+      <c r="D15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="13">
         <v>46102</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="9">
         <v>2</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" s="9" customFormat="1" spans="1:14">
-      <c r="A16" s="9">
+      <c r="H15" s="9"/>
+      <c r="I15" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" s="10" customFormat="1" spans="1:14">
+      <c r="A16" s="10">
         <v>57015</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="10">
         <v>57015</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <v>15</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>61</v>
+      <c r="D16" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="9">
+        <v>32</v>
+      </c>
+      <c r="G16" s="10">
         <v>1</v>
       </c>
       <c r="H16" s="1">
         <v>9999</v>
       </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
       <c r="K16" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="N16" s="18"/>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="1">
+      <c r="L16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" s="20"/>
+    </row>
+    <row r="17" s="9" customFormat="1" spans="1:14">
+      <c r="A17" s="9">
         <v>57016</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="9">
         <v>57016</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="9">
         <v>16</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17" s="5">
+      <c r="D17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="13">
         <v>46103</v>
       </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="G17" s="9">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9">
         <v>90</v>
       </c>
-      <c r="K17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>66</v>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="13">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F17">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2337,10 +2319,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2348,7 +2330,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2356,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2364,7 +2346,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2372,7 +2354,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2380,7 +2362,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2388,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2396,7 +2378,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2404,7 +2386,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2412,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2420,7 +2402,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2428,7 +2410,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2436,7 +2418,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2444,7 +2426,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2452,7 +2434,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2460,7 +2442,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2468,7 +2450,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2476,7 +2458,15 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -286,6 +286,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="J10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+时 分 秒 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="M10" authorId="0">
       <text>
         <r>
@@ -307,14 +329,159 @@
 官方派奖：奖池金币数量
 总量 ÷ 平均中奖金额 = 中奖次数
 1000000000 ÷ 718000 = 1392.7577
-初始天数30天
 ========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)
 统计类型：充值 
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="L11" authorId="0">
+    <comment ref="I11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+时 分 秒 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+时 分 秒 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)
+统计类型：充值 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+时 分 秒 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+时 分 秒 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)
+统计类型：充值 
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -336,7 +503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L16" authorId="0">
+    <comment ref="L18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -358,7 +525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M16" authorId="0">
+    <comment ref="M18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -385,7 +552,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
   <si>
     <t>序列ID</t>
   </si>
@@ -510,19 +677,46 @@
     <t>1_2_3_4_5_6_7_8_9_10_101_102_103_104_105_106_107_108</t>
   </si>
   <si>
-    <t>付费-官方派奖(常驻)</t>
-  </si>
-  <si>
-    <t>0 0 0 1,10,16 * ?</t>
-  </si>
-  <si>
-    <t>0 0 0 5,15,21 * ?</t>
-  </si>
-  <si>
-    <t>101_102_103_104_105_106_107_108_109_110_111_112_201_202_203_204_205_206_207_208_209_210_211_212_301_302_303_304_305_306_307_308_309_310_311_312</t>
-  </si>
-  <si>
-    <t>2000000000_1000</t>
+    <t>付费-官方派奖(常驻)-每天开</t>
+  </si>
+  <si>
+    <t>0 0 0 * * ?</t>
+  </si>
+  <si>
+    <t>23 59 59 * * ?</t>
+  </si>
+  <si>
+    <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
+  </si>
+  <si>
+    <t>500000000_1000_1</t>
+  </si>
+  <si>
+    <t>付费-官方派奖(常驻)-时段开</t>
+  </si>
+  <si>
+    <t>0 0 0 1 * ?</t>
+  </si>
+  <si>
+    <t>0 0 0 5 * ?</t>
+  </si>
+  <si>
+    <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
+  </si>
+  <si>
+    <t>1000000000_1000_2</t>
+  </si>
+  <si>
+    <t>0 0 0 15 * ?</t>
+  </si>
+  <si>
+    <t>0 0 0 20 * ?</t>
+  </si>
+  <si>
+    <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
+  </si>
+  <si>
+    <t>2000000000_1000_3</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -827,7 +1021,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -843,6 +1037,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.0999786370433668"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1171,7 +1371,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1195,16 +1395,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1213,89 +1413,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1323,6 +1523,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1332,22 +1535,28 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1705,7 +1914,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -1716,7 +1925,7 @@
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="11" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.4083333333333" style="1" customWidth="1"/>
@@ -1727,148 +1936,148 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:14">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:14">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:14">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:14">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="15"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1">
@@ -2018,289 +2227,375 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1">
+    <row r="10" s="9" customFormat="1" spans="1:14">
+      <c r="A10" s="9">
+        <v>57101</v>
+      </c>
+      <c r="B10" s="9">
         <v>57009</v>
       </c>
-      <c r="B10" s="1">
+      <c r="C10" s="9">
+        <v>9</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="9">
+        <v>3</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="14"/>
+    </row>
+    <row r="11" s="9" customFormat="1" spans="1:14">
+      <c r="A11" s="9">
+        <v>57102</v>
+      </c>
+      <c r="B11" s="9">
         <v>57009</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C11" s="9">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F11" s="14">
         <v>46105</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="1" t="b">
+      <c r="H11" s="9"/>
+      <c r="I11" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="1">
+      <c r="L11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="14"/>
+    </row>
+    <row r="12" s="9" customFormat="1" spans="1:14">
+      <c r="A12" s="9">
+        <v>57103</v>
+      </c>
+      <c r="B12" s="9">
+        <v>57009</v>
+      </c>
+      <c r="C12" s="9">
+        <v>9</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="14">
+        <v>46105</v>
+      </c>
+      <c r="G12" s="9">
+        <v>3</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12" s="14"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="1">
         <v>57010</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B13" s="1">
         <v>57010</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C13" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G13" s="1">
         <v>1</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H13" s="1">
         <v>9999</v>
       </c>
-      <c r="K11" s="1" t="b">
+      <c r="K13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="1">
+      <c r="L13" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="1">
         <v>57011</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B14" s="1">
         <v>57011</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C14" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G14" s="1">
         <v>1</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H14" s="1">
         <v>9999</v>
       </c>
-      <c r="K12" s="1" t="b">
+      <c r="K14" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L14" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" s="9" customFormat="1" spans="1:14">
-      <c r="A13" s="9">
+    <row r="15" s="10" customFormat="1" spans="1:14">
+      <c r="A15" s="10">
         <v>57012</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B15" s="10">
         <v>57012</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C15" s="10">
         <v>12</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="D15" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9">
+      <c r="F15" s="10"/>
+      <c r="G15" s="10">
         <v>1</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="9" t="b">
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="13"/>
-    </row>
-    <row r="14" s="9" customFormat="1" spans="1:14">
-      <c r="A14" s="9">
-        <v>57013</v>
-      </c>
-      <c r="B14" s="9">
-        <v>57013</v>
-      </c>
-      <c r="C14" s="9">
-        <v>13</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="13">
-        <v>46101</v>
-      </c>
-      <c r="G14" s="9">
-        <v>2</v>
-      </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="13"/>
-    </row>
-    <row r="15" s="9" customFormat="1" spans="1:14">
-      <c r="A15" s="9">
-        <v>57014</v>
-      </c>
-      <c r="B15" s="9">
-        <v>57014</v>
-      </c>
-      <c r="C15" s="9">
-        <v>14</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="13">
-        <v>46102</v>
-      </c>
-      <c r="G15" s="9">
-        <v>2</v>
-      </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="K15" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="13"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="15"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:14">
       <c r="A16" s="10">
+        <v>57013</v>
+      </c>
+      <c r="B16" s="10">
+        <v>57013</v>
+      </c>
+      <c r="C16" s="10">
+        <v>13</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="15">
+        <v>46101</v>
+      </c>
+      <c r="G16" s="10">
+        <v>2</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="15"/>
+    </row>
+    <row r="17" s="10" customFormat="1" spans="1:14">
+      <c r="A17" s="10">
+        <v>57014</v>
+      </c>
+      <c r="B17" s="10">
+        <v>57014</v>
+      </c>
+      <c r="C17" s="10">
+        <v>14</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="15">
+        <v>46102</v>
+      </c>
+      <c r="G17" s="10">
+        <v>2</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="15"/>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:14">
+      <c r="A18" s="11">
         <v>57015</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B18" s="11">
         <v>57015</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C18" s="11">
         <v>15</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G18" s="11">
         <v>1</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="1" t="b">
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="N16" s="20"/>
-    </row>
-    <row r="17" s="9" customFormat="1" spans="1:14">
-      <c r="A17" s="9">
+      <c r="L18" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="N18" s="23"/>
+    </row>
+    <row r="19" s="10" customFormat="1" spans="1:14">
+      <c r="A19" s="10">
         <v>57016</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B19" s="10">
         <v>57016</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C19" s="10">
         <v>16</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="9" t="s">
+      <c r="D19" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F19" s="15">
         <v>46103</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G19" s="10">
         <v>1</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="9" t="b">
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="13">
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="15">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2319,10 +2614,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2330,7 +2625,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2338,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2346,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2354,7 +2649,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2362,7 +2657,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2370,7 +2665,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2378,7 +2673,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2386,7 +2681,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2394,7 +2689,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2402,7 +2697,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2410,7 +2705,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2418,7 +2713,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2426,7 +2721,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2434,7 +2729,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2442,7 +2737,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2450,7 +2745,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2458,7 +2753,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2466,7 +2761,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -282,7 +282,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-时 分 秒 日期1,日期2,日期3 * ？</t>
+秒 分 时 日期1,日期2,日期3 * ？</t>
         </r>
       </text>
     </comment>
@@ -304,7 +304,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-时 分 秒 日期1,日期2,日期3 * ？</t>
+秒 分 时 日期1,日期2,日期3 * ？</t>
         </r>
       </text>
     </comment>
@@ -354,7 +354,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-时 分 秒 日期1,日期2,日期3 * ？</t>
+秒 分 时 日期1,日期2,日期3 * ？</t>
         </r>
       </text>
     </comment>
@@ -376,7 +376,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-时 分 秒 日期1,日期2,日期3 * ？
+秒 分 时 日期1,日期2,日期3 * ？
 </t>
         </r>
       </text>
@@ -426,7 +426,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-时 分 秒 日期1,日期2,日期3 * ？</t>
+秒 分 时 日期1,日期2,日期3 * ？</t>
         </r>
       </text>
     </comment>
@@ -448,7 +448,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-时 分 秒 日期1,日期2,日期3 * ？
+秒 分 时 日期1,日期2,日期3 * ？
 </t>
         </r>
       </text>
@@ -683,7 +683,7 @@
     <t>0 0 0 * * ?</t>
   </si>
   <si>
-    <t>23 59 59 * * ?</t>
+    <t>59 59 23 * * ?</t>
   </si>
   <si>
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17A9E7E-D25B-414E-8467-EA2D6852E528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -29,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -79,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -109,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -132,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -154,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0">
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -176,7 +182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="0">
+    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -198,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L7" authorId="0">
+    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -220,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -242,7 +248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0">
+    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -264,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I10" authorId="0">
+    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -286,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="0">
+    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -308,7 +314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="0">
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -336,7 +342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -358,7 +364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -381,7 +387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M11" authorId="0">
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -408,7 +414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -430,7 +436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0">
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -453,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M12" authorId="0">
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -481,7 +487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L13" authorId="0">
+    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -503,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L18" authorId="0">
+    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -525,7 +531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M18" authorId="0">
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -552,7 +558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="89">
   <si>
     <t>序列ID</t>
   </si>
@@ -749,9 +755,6 @@
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
   </si>
   <si>
-    <t>599_9999_21000000</t>
-  </si>
-  <si>
     <t>活跃-收集拼图</t>
   </si>
   <si>
@@ -810,19 +813,29 @@
   </si>
   <si>
     <t>我的赌场</t>
+  </si>
+  <si>
+    <t>值3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;BigDecimal&gt;{_}</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>599_9999</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>bigDecimalParam</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -861,153 +874,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1020,8 +889,35 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1030,216 +926,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505"/>
+        <fgColor theme="0" tint="-0.14993743705557422"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.0999786370433668"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1247,255 +963,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1566,59 +1040,62 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1631,6 +1108,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1908,34 +1388,34 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
     <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.4083333333333" style="1" customWidth="1"/>
-    <col min="14" max="14" width="41.875" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9" style="1"/>
-    <col min="16" max="16" width="26.75" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
+    <col min="13" max="14" width="19.375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="41.875" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9" style="1"/>
+    <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" spans="1:14">
+    <row r="1" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1975,11 +1455,14 @@
       <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:14">
+    <row r="2" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
@@ -2017,11 +1500,14 @@
       <c r="M2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="O2" s="17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="1" ht="15" spans="1:14">
+    <row r="3" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>18</v>
       </c>
@@ -2059,11 +1545,14 @@
       <c r="M3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" s="17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" ht="15" spans="1:14">
+    <row r="4" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2077,9 +1566,10 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
-      <c r="N4" s="17"/>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" s="13"/>
+      <c r="O4" s="17"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>57002</v>
       </c>
@@ -2108,7 +1598,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>57003</v>
       </c>
@@ -2137,7 +1627,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>57004</v>
       </c>
@@ -2166,7 +1656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -2194,11 +1684,11 @@
       <c r="L8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>57006</v>
       </c>
@@ -2227,7 +1717,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" s="9" customFormat="1" spans="1:14">
+    <row r="10" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>57101</v>
       </c>
@@ -2247,7 +1737,6 @@
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="H10" s="9"/>
       <c r="I10" s="19" t="s">
         <v>42</v>
       </c>
@@ -2263,9 +1752,10 @@
       <c r="M10" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="14"/>
-    </row>
-    <row r="11" s="9" customFormat="1" spans="1:14">
+      <c r="N10" s="20"/>
+      <c r="O10" s="14"/>
+    </row>
+    <row r="11" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>57102</v>
       </c>
@@ -2287,7 +1777,6 @@
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="H11" s="9"/>
       <c r="I11" s="19" t="s">
         <v>47</v>
       </c>
@@ -2303,9 +1792,10 @@
       <c r="M11" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="14"/>
-    </row>
-    <row r="12" s="9" customFormat="1" spans="1:14">
+      <c r="N11" s="20"/>
+      <c r="O11" s="14"/>
+    </row>
+    <row r="12" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>57103</v>
       </c>
@@ -2327,7 +1817,6 @@
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="H12" s="9"/>
       <c r="I12" s="19" t="s">
         <v>51</v>
       </c>
@@ -2343,9 +1832,10 @@
       <c r="M12" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="N12" s="14"/>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="N12" s="20"/>
+      <c r="O12" s="14"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>57010</v>
       </c>
@@ -2374,7 +1864,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>57011</v>
       </c>
@@ -2403,7 +1893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" s="10" customFormat="1" spans="1:14">
+    <row r="15" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>57012</v>
       </c>
@@ -2419,7 +1909,6 @@
       <c r="E15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="10"/>
       <c r="G15" s="10">
         <v>1</v>
       </c>
@@ -2431,11 +1920,9 @@
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="15"/>
-    </row>
-    <row r="16" s="10" customFormat="1" spans="1:14">
+      <c r="O15" s="15"/>
+    </row>
+    <row r="16" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>57013</v>
       </c>
@@ -2457,7 +1944,6 @@
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="H16" s="10"/>
       <c r="I16" s="21" t="s">
         <v>60</v>
       </c>
@@ -2467,11 +1953,9 @@
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="15"/>
-    </row>
-    <row r="17" s="10" customFormat="1" spans="1:14">
+      <c r="O16" s="15"/>
+    </row>
+    <row r="17" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
         <v>57014</v>
       </c>
@@ -2493,7 +1977,6 @@
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="H17" s="10"/>
       <c r="I17" s="21" t="s">
         <v>60</v>
       </c>
@@ -2503,11 +1986,9 @@
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="15"/>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:14">
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
         <v>57015</v>
       </c>
@@ -2537,12 +2018,15 @@
       <c r="L18" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="M18" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="N18" s="23"/>
-    </row>
-    <row r="19" s="10" customFormat="1" spans="1:14">
+      <c r="M18" s="11">
+        <v>21000000</v>
+      </c>
+      <c r="N18" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="O18" s="23"/>
+    </row>
+    <row r="19" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <v>57016</v>
       </c>
@@ -2553,7 +2037,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>32</v>
@@ -2572,244 +2056,240 @@
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="15">
+      <c r="O19" s="15">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A5:D31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" ht="16.5" spans="1:2">
+    <row r="5" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:2">
+    </row>
+    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:2">
-      <c r="A7" s="3">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:2">
+    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" ht="21.95" customHeight="1" spans="1:4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" ht="21.95" customHeight="1" spans="1:4">
+    <row r="28" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" ht="21.95" customHeight="1" spans="1:4">
+    <row r="29" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" ht="21.95" customHeight="1" spans="1:4">
+    <row r="30" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
     </row>
-    <row r="31" ht="21.95" customHeight="1" spans="1:4">
+    <row r="31" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="A27:A31">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17A9E7E-D25B-414E-8467-EA2D6852E528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -35,12 +29,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -160,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="L5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -182,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="L6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -204,7 +198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="L7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -226,7 +220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="L8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -248,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="L9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -270,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="I10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -292,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="J10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -314,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="M10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -342,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="I11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -364,7 +358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="J11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -387,7 +381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="M11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -414,7 +408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+    <comment ref="I12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -436,7 +430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+    <comment ref="J12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -459,7 +453,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+    <comment ref="M12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +481,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+    <comment ref="L13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+    <comment ref="L18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -531,7 +525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+    <comment ref="M18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -599,6 +593,9 @@
     <t>值2</t>
   </si>
   <si>
+    <t>值3</t>
+  </si>
+  <si>
     <t>掉落id</t>
   </si>
   <si>
@@ -614,6 +611,9 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>list&lt;BigDecimal&gt;{_}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -650,6 +650,9 @@
     <t>valueParam</t>
   </si>
   <si>
+    <t>bigDecimalParam</t>
+  </si>
+  <si>
     <t>dropConfigId</t>
   </si>
   <si>
@@ -755,6 +758,9 @@
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
   </si>
   <si>
+    <t>5.99_99.99</t>
+  </si>
+  <si>
     <t>活跃-收集拼图</t>
   </si>
   <si>
@@ -813,29 +819,19 @@
   </si>
   <si>
     <t>我的赌场</t>
-  </si>
-  <si>
-    <t>值3</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;BigDecimal&gt;{_}</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>599_9999</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>bigDecimalParam</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -874,9 +870,159 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFBFBFBF"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -889,35 +1035,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -926,36 +1045,228 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14993743705557422"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="0" tint="-0.14996795556505"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.0999786370433668"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEDD5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -963,13 +1274,270 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1021,81 +1589,97 @@
     <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1108,9 +1692,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1388,34 +1969,34 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
     <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
-    <col min="13" max="14" width="19.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="13" max="14" width="19.4083333333333" style="1" customWidth="1"/>
     <col min="15" max="15" width="41.875" style="5" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1455,104 +2036,104 @@
       <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="O1" s="17" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="O1" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A3" s="13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1566,10 +2147,10 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="17"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N4" s="21"/>
+      <c r="O4" s="18"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>57002</v>
       </c>
@@ -1580,10 +2161,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1595,10 +2176,11 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="N5" s="22"/>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>57003</v>
       </c>
@@ -1609,10 +2191,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1624,10 +2206,11 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+      <c r="N6" s="22"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>57004</v>
       </c>
@@ -1638,10 +2221,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1653,10 +2236,11 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="N7" s="22"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -1667,10 +2251,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1682,13 +2266,14 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="N8" s="22"/>
       <c r="O8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14">
       <c r="A9" s="1">
         <v>57006</v>
       </c>
@@ -1699,10 +2284,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1714,10 +2299,11 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="N9" s="22"/>
+    </row>
+    <row r="10" s="9" customFormat="1" spans="1:15">
       <c r="A10" s="9">
         <v>57101</v>
       </c>
@@ -1728,34 +2314,35 @@
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>43</v>
+      <c r="H10" s="9"/>
+      <c r="I10" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K10" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="N10" s="20"/>
+        <v>47</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" s="25"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" s="9" customFormat="1" spans="1:15">
       <c r="A11" s="9">
         <v>57102</v>
       </c>
@@ -1766,10 +2353,10 @@
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F11" s="14">
         <v>46105</v>
@@ -1777,25 +2364,26 @@
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>48</v>
+      <c r="H11" s="9"/>
+      <c r="I11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>51</v>
       </c>
       <c r="K11" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="20"/>
+        <v>52</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="25"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" s="9" customFormat="1" spans="1:15">
       <c r="A12" s="9">
         <v>57103</v>
       </c>
@@ -1806,10 +2394,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F12" s="14">
         <v>46105</v>
@@ -1817,25 +2405,26 @@
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>52</v>
+      <c r="H12" s="9"/>
+      <c r="I12" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>55</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N12" s="20"/>
+        <v>56</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="25"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14">
       <c r="A13" s="1">
         <v>57010</v>
       </c>
@@ -1846,10 +2435,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1861,10 +2450,11 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="N13" s="22"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1">
         <v>57011</v>
       </c>
@@ -1875,10 +2465,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1892,8 +2482,9 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N14" s="22"/>
+    </row>
+    <row r="15" s="10" customFormat="1" spans="1:15">
       <c r="A15" s="10">
         <v>57012</v>
       </c>
@@ -1904,25 +2495,29 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>32</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F15" s="10"/>
       <c r="G15" s="10">
         <v>1</v>
       </c>
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="27"/>
       <c r="O15" s="15"/>
     </row>
-    <row r="16" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" s="10" customFormat="1" spans="1:15">
       <c r="A16" s="10">
         <v>57013</v>
       </c>
@@ -1933,10 +2528,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F16" s="15">
         <v>46101</v>
@@ -1944,18 +2539,22 @@
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>61</v>
+      <c r="H16" s="10"/>
+      <c r="I16" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="27"/>
       <c r="O16" s="15"/>
     </row>
-    <row r="17" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" s="10" customFormat="1" spans="1:15">
       <c r="A17" s="10">
         <v>57014</v>
       </c>
@@ -1966,10 +2565,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F17" s="15">
         <v>46102</v>
@@ -1977,18 +2576,22 @@
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>61</v>
+      <c r="H17" s="10"/>
+      <c r="I17" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="27"/>
       <c r="O17" s="15"/>
     </row>
-    <row r="18" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" s="11" customFormat="1" spans="1:15">
       <c r="A18" s="11">
         <v>57015</v>
       </c>
@@ -1999,10 +2602,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>
@@ -2010,23 +2613,23 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M18" s="11">
         <v>21000000</v>
       </c>
-      <c r="N18" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="O18" s="23"/>
-    </row>
-    <row r="19" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N18" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="O18" s="30"/>
+    </row>
+    <row r="19" s="10" customFormat="1" spans="1:15">
       <c r="A19" s="10">
         <v>57016</v>
       </c>
@@ -2037,10 +2640,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F19" s="15">
         <v>46103</v>
@@ -2051,245 +2654,253 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="27"/>
       <c r="O19" s="15">
         <v>3</v>
       </c>
     </row>
+    <row r="20" spans="14:14">
+      <c r="N20" s="22"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A5:D31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:2">
       <c r="A7" s="3">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:2">
       <c r="A8" s="3">
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:2">
       <c r="A9" s="3">
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:2">
       <c r="A10" s="3">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:2">
       <c r="A11" s="3">
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:2">
       <c r="A12" s="3">
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:2">
       <c r="A13" s="3">
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:2">
       <c r="A14" s="3">
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:2">
       <c r="A15" s="3">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:2">
       <c r="A16" s="3">
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:2">
       <c r="A17" s="3">
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:2">
       <c r="A18" s="3">
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:2">
       <c r="A19" s="3">
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:2">
       <c r="A20" s="3">
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:2">
       <c r="A22" s="3">
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" ht="21.95" customHeight="1" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="21.95" customHeight="1" spans="1:4">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="21.95" customHeight="1" spans="1:4">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="21.95" customHeight="1" spans="1:4">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
     </row>
-    <row r="31" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="21.95" customHeight="1" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="A27:A31">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -132,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -552,7 +552,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="89">
   <si>
     <t>序列ID</t>
   </si>
@@ -593,6 +593,9 @@
     <t>值2</t>
   </si>
   <si>
+    <t>值3</t>
+  </si>
+  <si>
     <t>掉落id</t>
   </si>
   <si>
@@ -608,6 +611,9 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>list&lt;BigDecimal&gt;{_}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -644,6 +650,9 @@
     <t>valueParam</t>
   </si>
   <si>
+    <t>bigDecimalParam</t>
+  </si>
+  <si>
     <t>dropConfigId</t>
   </si>
   <si>
@@ -749,7 +758,7 @@
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
   </si>
   <si>
-    <t>599_9999_21000000</t>
+    <t>5.99_99.99</t>
   </si>
   <si>
     <t>活跃-收集拼图</t>
@@ -822,7 +831,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -862,6 +871,12 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFBFBFBF"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1021,7 +1036,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1054,12 +1069,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDBEDD5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1239,12 +1266,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1365,88 +1407,82 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1455,10 +1491,10 @@
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1467,10 +1503,10 @@
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1479,10 +1515,10 @@
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1491,11 +1527,17 @@
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1547,20 +1589,39 @@
     <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1914,7 +1975,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -1928,14 +1989,14 @@
     <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.4083333333333" style="1" customWidth="1"/>
-    <col min="14" max="14" width="41.875" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9" style="1"/>
-    <col min="16" max="16" width="26.75" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="13" max="14" width="19.4083333333333" style="1" customWidth="1"/>
+    <col min="15" max="15" width="41.875" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9" style="1"/>
+    <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" spans="1:14">
+    <row r="1" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1978,92 +2039,101 @@
       <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:14">
+      <c r="O1" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" s="8" customFormat="1" ht="15" spans="1:14">
+    </row>
+    <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A3" s="13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" s="8" customFormat="1" ht="15" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2077,9 +2147,10 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
-      <c r="N4" s="17"/>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" s="21"/>
+      <c r="O4" s="18"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>57002</v>
       </c>
@@ -2090,10 +2161,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -2105,10 +2176,11 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>36</v>
+      </c>
+      <c r="N5" s="22"/>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>57003</v>
       </c>
@@ -2119,10 +2191,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -2134,10 +2206,11 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>38</v>
+      </c>
+      <c r="N6" s="22"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>57004</v>
       </c>
@@ -2148,10 +2221,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -2163,10 +2236,11 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>36</v>
+      </c>
+      <c r="N7" s="22"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -2177,10 +2251,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2192,13 +2266,14 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="5">
+        <v>41</v>
+      </c>
+      <c r="N8" s="22"/>
+      <c r="O8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:14">
       <c r="A9" s="1">
         <v>57006</v>
       </c>
@@ -2209,10 +2284,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -2224,10 +2299,11 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" s="9" customFormat="1" spans="1:14">
+        <v>43</v>
+      </c>
+      <c r="N9" s="22"/>
+    </row>
+    <row r="10" s="9" customFormat="1" spans="1:15">
       <c r="A10" s="9">
         <v>57101</v>
       </c>
@@ -2238,34 +2314,35 @@
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
       <c r="H10" s="9"/>
-      <c r="I10" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>43</v>
+      <c r="I10" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="K10" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="N10" s="14"/>
-    </row>
-    <row r="11" s="9" customFormat="1" spans="1:14">
+        <v>47</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" s="25"/>
+      <c r="O10" s="14"/>
+    </row>
+    <row r="11" s="9" customFormat="1" spans="1:15">
       <c r="A11" s="9">
         <v>57102</v>
       </c>
@@ -2276,10 +2353,10 @@
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F11" s="14">
         <v>46105</v>
@@ -2288,24 +2365,25 @@
         <v>3</v>
       </c>
       <c r="H11" s="9"/>
-      <c r="I11" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>48</v>
+      <c r="I11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>51</v>
       </c>
       <c r="K11" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="14"/>
-    </row>
-    <row r="12" s="9" customFormat="1" spans="1:14">
+        <v>52</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="25"/>
+      <c r="O11" s="14"/>
+    </row>
+    <row r="12" s="9" customFormat="1" spans="1:15">
       <c r="A12" s="9">
         <v>57103</v>
       </c>
@@ -2316,10 +2394,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F12" s="14">
         <v>46105</v>
@@ -2328,24 +2406,25 @@
         <v>3</v>
       </c>
       <c r="H12" s="9"/>
-      <c r="I12" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>52</v>
+      <c r="I12" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>55</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N12" s="14"/>
-    </row>
-    <row r="13" spans="1:12">
+        <v>56</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="25"/>
+      <c r="O12" s="14"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="1">
         <v>57010</v>
       </c>
@@ -2356,10 +2435,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2371,10 +2450,11 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>59</v>
+      </c>
+      <c r="N13" s="22"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1">
         <v>57011</v>
       </c>
@@ -2385,10 +2465,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2402,8 +2482,9 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" s="10" customFormat="1" spans="1:14">
+      <c r="N14" s="22"/>
+    </row>
+    <row r="15" s="10" customFormat="1" spans="1:15">
       <c r="A15" s="10">
         <v>57012</v>
       </c>
@@ -2414,10 +2495,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10">
@@ -2426,16 +2507,17 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
-      <c r="N15" s="15"/>
-    </row>
-    <row r="16" s="10" customFormat="1" spans="1:14">
+      <c r="N15" s="27"/>
+      <c r="O15" s="15"/>
+    </row>
+    <row r="16" s="10" customFormat="1" spans="1:15">
       <c r="A16" s="10">
         <v>57013</v>
       </c>
@@ -2446,10 +2528,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F16" s="15">
         <v>46101</v>
@@ -2458,20 +2540,21 @@
         <v>2</v>
       </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>61</v>
+      <c r="I16" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
-      <c r="N16" s="15"/>
-    </row>
-    <row r="17" s="10" customFormat="1" spans="1:14">
+      <c r="N16" s="27"/>
+      <c r="O16" s="15"/>
+    </row>
+    <row r="17" s="10" customFormat="1" spans="1:15">
       <c r="A17" s="10">
         <v>57014</v>
       </c>
@@ -2482,10 +2565,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F17" s="15">
         <v>46102</v>
@@ -2494,20 +2577,21 @@
         <v>2</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>61</v>
+      <c r="I17" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
-      <c r="N17" s="15"/>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:14">
+      <c r="N17" s="27"/>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:15">
       <c r="A18" s="11">
         <v>57015</v>
       </c>
@@ -2518,10 +2602,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>
@@ -2529,20 +2613,23 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="N18" s="23"/>
-    </row>
-    <row r="19" s="10" customFormat="1" spans="1:14">
+        <v>67</v>
+      </c>
+      <c r="M18" s="11">
+        <v>21000000</v>
+      </c>
+      <c r="N18" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="O18" s="30"/>
+    </row>
+    <row r="19" s="10" customFormat="1" spans="1:15">
       <c r="A19" s="10">
         <v>57016</v>
       </c>
@@ -2553,10 +2640,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F19" s="15">
         <v>46103</v>
@@ -2567,16 +2654,20 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
-      <c r="N19" s="15">
+      <c r="N19" s="27"/>
+      <c r="O19" s="15">
         <v>3</v>
       </c>
+    </row>
+    <row r="20" spans="14:14">
+      <c r="N20" s="22"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -2614,10 +2705,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2625,7 +2716,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2633,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2641,7 +2732,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2649,7 +2740,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2657,7 +2748,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2665,7 +2756,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2673,7 +2764,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2681,7 +2772,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2689,7 +2780,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2697,7 +2788,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2705,7 +2796,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2713,7 +2804,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2721,7 +2812,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2729,7 +2820,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2737,7 +2828,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2745,7 +2836,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2753,7 +2844,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2761,7 +2852,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -330,7 +330,7 @@
 总量 ÷ 平均中奖金额 = 中奖次数
 1000000000 ÷ 718000 = 1392.7577
 ========================================
-参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
 统计类型：充值 
 </t>
         </r>
@@ -403,7 +403,7 @@
 总量 ÷ 平均中奖金额 = 中奖次数
 1000000000 ÷ 718000 = 1392.7577
 ========================================
-参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
 统计类型：充值 </t>
         </r>
       </text>
@@ -475,7 +475,7 @@
 总量 ÷ 平均中奖金额 = 中奖次数
 1000000000 ÷ 718000 = 1392.7577
 ========================================
-参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
 统计类型：充值 
 </t>
         </r>
@@ -698,7 +698,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>500000000_1000_1</t>
+    <t>500000000_1000_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
@@ -713,7 +713,7 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>1000000000_1000_2</t>
+    <t>1000000000_1000_2_2</t>
   </si>
   <si>
     <t>0 0 0 15 * ?</t>
@@ -725,7 +725,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>2000000000_1000_3</t>
+    <t>2000000000_1000_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -1537,7 +1537,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1600,9 +1600,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1619,9 +1616,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1989,7 +1983,8 @@
     <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="13" max="14" width="19.4083333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="23.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.4083333333333" style="1" customWidth="1"/>
     <col min="15" max="15" width="41.875" style="5" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
@@ -2147,7 +2142,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="17"/>
       <c r="O4" s="18"/>
     </row>
     <row r="5" spans="1:14">
@@ -2178,7 +2173,7 @@
       <c r="L5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="22"/>
+      <c r="N5" s="21"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1">
@@ -2208,7 +2203,7 @@
       <c r="L6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="22"/>
+      <c r="N6" s="21"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1">
@@ -2238,7 +2233,7 @@
       <c r="L7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="22"/>
+      <c r="N7" s="21"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
@@ -2268,7 +2263,7 @@
       <c r="L8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N8" s="22"/>
+      <c r="N8" s="21"/>
       <c r="O8" s="5">
         <v>1</v>
       </c>
@@ -2301,7 +2296,7 @@
       <c r="L9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="N9" s="22"/>
+      <c r="N9" s="21"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:15">
       <c r="A10" s="9">
@@ -2324,10 +2319,10 @@
         <v>3</v>
       </c>
       <c r="H10" s="9"/>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="22" t="s">
         <v>46</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2336,10 +2331,10 @@
       <c r="L10" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N10" s="25"/>
+      <c r="N10" s="24"/>
       <c r="O10" s="14"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:15">
@@ -2365,10 +2360,10 @@
         <v>3</v>
       </c>
       <c r="H11" s="9"/>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="22" t="s">
         <v>51</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2377,10 +2372,10 @@
       <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M11" s="24" t="s">
+      <c r="M11" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="N11" s="25"/>
+      <c r="N11" s="24"/>
       <c r="O11" s="14"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:15">
@@ -2406,10 +2401,10 @@
         <v>3</v>
       </c>
       <c r="H12" s="9"/>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J12" s="22" t="s">
         <v>55</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2418,10 +2413,10 @@
       <c r="L12" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="M12" s="24" t="s">
+      <c r="M12" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="N12" s="25"/>
+      <c r="N12" s="24"/>
       <c r="O12" s="14"/>
     </row>
     <row r="13" spans="1:14">
@@ -2452,7 +2447,7 @@
       <c r="L13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N13" s="22"/>
+      <c r="N13" s="21"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1">
@@ -2482,7 +2477,7 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="N14" s="22"/>
+      <c r="N14" s="21"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:15">
       <c r="A15" s="10">
@@ -2507,14 +2502,14 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
-      <c r="N15" s="27"/>
+      <c r="N15" s="26"/>
       <c r="O15" s="15"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:15">
@@ -2540,10 +2535,10 @@
         <v>2</v>
       </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="J16" s="26" t="s">
+      <c r="J16" s="25" t="s">
         <v>64</v>
       </c>
       <c r="K16" s="10" t="b">
@@ -2551,7 +2546,7 @@
       </c>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
-      <c r="N16" s="27"/>
+      <c r="N16" s="26"/>
       <c r="O16" s="15"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:15">
@@ -2577,10 +2572,10 @@
         <v>2</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="26" t="s">
+      <c r="I17" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="J17" s="26" t="s">
+      <c r="J17" s="25" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="10" t="b">
@@ -2588,7 +2583,7 @@
       </c>
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
-      <c r="N17" s="27"/>
+      <c r="N17" s="26"/>
       <c r="O17" s="15"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:15">
@@ -2613,8 +2608,8 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
@@ -2624,10 +2619,10 @@
       <c r="M18" s="11">
         <v>21000000</v>
       </c>
-      <c r="N18" s="29" t="s">
+      <c r="N18" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="O18" s="30"/>
+      <c r="O18" s="28"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:15">
       <c r="A19" s="10">
@@ -2654,20 +2649,20 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
-      <c r="N19" s="27"/>
+      <c r="N19" s="26"/>
       <c r="O19" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="14:14">
-      <c r="N20" s="22"/>
+      <c r="N20" s="21"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99E4968-EE9B-4C46-8706-ACCE3E2F2C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -29,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -79,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -109,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -132,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -154,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0">
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -176,7 +182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="0">
+    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -198,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L7" authorId="0">
+    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -220,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -242,7 +248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0">
+    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -264,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I10" authorId="0">
+    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -286,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="0">
+    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -308,7 +314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="0">
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -336,7 +342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -358,7 +364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -381,7 +387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M11" authorId="0">
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -408,7 +414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -430,7 +436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0">
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -453,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M12" authorId="0">
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -481,7 +487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L13" authorId="0">
+    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -503,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L18" authorId="0">
+    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -525,7 +531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M18" authorId="0">
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -544,6 +550,28 @@
           </rPr>
           <t xml:space="preserve">
 参数：售价_原价_总计获得</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+购买金额_原价金额</t>
         </r>
       </text>
     </comment>
@@ -552,7 +580,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
   <si>
     <t>序列ID</t>
   </si>
@@ -755,10 +783,13 @@
     <t>活跃&amp;付费-成长基金(常驻)</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
-  </si>
-  <si>
-    <t>5.99_99.99</t>
+    <t>1_5</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
+  </si>
+  <si>
+    <t>4.99_174.65</t>
   </si>
   <si>
     <t>活跃-收集拼图</t>
@@ -819,19 +850,17 @@
   </si>
   <si>
     <t>我的赌场</t>
+  </si>
+  <si>
+    <t>list&lt;long&gt;{_}</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -870,7 +899,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -879,150 +908,6 @@
       <color rgb="FFBFBFBF"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1035,8 +920,29 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1045,25 +951,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505"/>
+        <fgColor theme="0" tint="-0.14993743705557422"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.0999786370433668"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1075,7 +981,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1085,188 +991,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1289,255 +1015,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1621,59 +1105,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1686,6 +1167,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1963,35 +1447,35 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
     <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="23.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.4083333333333" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.375" style="1" customWidth="1"/>
     <col min="15" max="15" width="41.875" style="5" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" ht="15" spans="1:15">
+    <row r="1" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -2038,7 +1522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
+    <row r="2" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -2073,8 +1557,8 @@
       <c r="L2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="19" t="s">
-        <v>18</v>
+      <c r="M2" s="29" t="s">
+        <v>90</v>
       </c>
       <c r="N2" s="20" t="s">
         <v>19</v>
@@ -2083,7 +1567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
+    <row r="3" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>20</v>
       </c>
@@ -2128,7 +1612,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
+    <row r="4" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2145,7 +1629,7 @@
       <c r="N4" s="17"/>
       <c r="O4" s="18"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>57002</v>
       </c>
@@ -2175,7 +1659,7 @@
       </c>
       <c r="N5" s="21"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>57003</v>
       </c>
@@ -2205,7 +1689,7 @@
       </c>
       <c r="N6" s="21"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>57004</v>
       </c>
@@ -2235,7 +1719,7 @@
       </c>
       <c r="N7" s="21"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -2268,7 +1752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>57006</v>
       </c>
@@ -2298,7 +1782,7 @@
       </c>
       <c r="N9" s="21"/>
     </row>
-    <row r="10" s="9" customFormat="1" spans="1:15">
+    <row r="10" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>57101</v>
       </c>
@@ -2318,7 +1802,6 @@
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="H10" s="9"/>
       <c r="I10" s="22" t="s">
         <v>45</v>
       </c>
@@ -2337,7 +1820,7 @@
       <c r="N10" s="24"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" s="9" customFormat="1" spans="1:15">
+    <row r="11" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>57102</v>
       </c>
@@ -2359,7 +1842,6 @@
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="H11" s="9"/>
       <c r="I11" s="22" t="s">
         <v>50</v>
       </c>
@@ -2378,7 +1860,7 @@
       <c r="N11" s="24"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" s="9" customFormat="1" spans="1:15">
+    <row r="12" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>57103</v>
       </c>
@@ -2400,7 +1882,6 @@
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="H12" s="9"/>
       <c r="I12" s="22" t="s">
         <v>54</v>
       </c>
@@ -2419,7 +1900,7 @@
       <c r="N12" s="24"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>57010</v>
       </c>
@@ -2449,7 +1930,7 @@
       </c>
       <c r="N13" s="21"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>57011</v>
       </c>
@@ -2479,7 +1960,7 @@
       </c>
       <c r="N14" s="21"/>
     </row>
-    <row r="15" s="10" customFormat="1" spans="1:15">
+    <row r="15" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>57012</v>
       </c>
@@ -2495,7 +1976,6 @@
       <c r="E15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="10"/>
       <c r="G15" s="10">
         <v>1</v>
       </c>
@@ -2507,12 +1987,10 @@
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
       <c r="N15" s="26"/>
       <c r="O15" s="15"/>
     </row>
-    <row r="16" s="10" customFormat="1" spans="1:15">
+    <row r="16" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>57013</v>
       </c>
@@ -2534,7 +2012,6 @@
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="H16" s="10"/>
       <c r="I16" s="25" t="s">
         <v>63</v>
       </c>
@@ -2544,12 +2021,10 @@
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
       <c r="N16" s="26"/>
       <c r="O16" s="15"/>
     </row>
-    <row r="17" s="10" customFormat="1" spans="1:15">
+    <row r="17" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
         <v>57014</v>
       </c>
@@ -2571,7 +2046,6 @@
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="H17" s="10"/>
       <c r="I17" s="25" t="s">
         <v>63</v>
       </c>
@@ -2581,12 +2055,10 @@
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
       <c r="N17" s="26"/>
       <c r="O17" s="15"/>
     </row>
-    <row r="18" s="11" customFormat="1" spans="1:15">
+    <row r="18" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
         <v>57015</v>
       </c>
@@ -2600,7 +2072,7 @@
         <v>66</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>
@@ -2614,17 +2086,17 @@
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M18" s="11">
         <v>21000000</v>
       </c>
       <c r="N18" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O18" s="28"/>
     </row>
-    <row r="19" s="10" customFormat="1" spans="1:15">
+    <row r="19" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <v>57016</v>
       </c>
@@ -2635,7 +2107,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>35</v>
@@ -2654,248 +2126,244 @@
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
       <c r="N19" s="26"/>
       <c r="O19" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="14:14">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="N20" s="21"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A5:D31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" ht="16.5" spans="1:2">
+    <row r="5" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" ht="21.95" customHeight="1" spans="1:4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" ht="21.95" customHeight="1" spans="1:4">
+    <row r="28" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" ht="21.95" customHeight="1" spans="1:4">
+    <row r="29" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" ht="21.95" customHeight="1" spans="1:4">
+    <row r="30" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
     </row>
-    <row r="31" ht="21.95" customHeight="1" spans="1:4">
+    <row r="31" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="A27:A31">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -543,7 +543,29 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-参数：售价_原价_总计获得</t>
+参数：金币总获得量_商品打折前原价</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+渠道ID_商品ID|……</t>
         </r>
       </text>
     </comment>
@@ -552,7 +574,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>序列ID</t>
   </si>
@@ -593,7 +615,7 @@
     <t>值2</t>
   </si>
   <si>
-    <t>值3</t>
+    <t>渠道和商品ID</t>
   </si>
   <si>
     <t>掉落id</t>
@@ -611,7 +633,10 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>list&lt;BigDecimal&gt;{_}</t>
+    <t>list&lt;long&gt;{_}</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -755,10 +780,16 @@
     <t>活跃&amp;付费-成长基金(常驻)</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_21_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120_121</t>
-  </si>
-  <si>
-    <t>5.99_99.99</t>
+    <t>1_5</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
+  </si>
+  <si>
+    <t>17466000_174.65</t>
+  </si>
+  <si>
+    <t>1_google499|2_ios499</t>
   </si>
   <si>
     <t>活跃-收集拼图</t>
@@ -831,7 +862,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -870,7 +901,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1045,7 +1083,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505"/>
+        <fgColor theme="0" tint="-0.149937437055574"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1057,7 +1095,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1075,12 +1113,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDBEDD5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1160,6 +1192,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1407,137 +1445,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1592,13 +1630,10 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1608,11 +1643,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1975,16 +2010,16 @@
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.1" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
     <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5583333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="23.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.4083333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="36.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="23.25" style="1" customWidth="1"/>
     <col min="15" max="15" width="41.875" style="5" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
@@ -2038,7 +2073,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="1" ht="15" spans="1:15">
+    <row r="2" s="8" customFormat="1" spans="1:15">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -2070,14 +2105,14 @@
       <c r="K2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="18" t="s">
         <v>18</v>
       </c>
       <c r="M2" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="20" t="s">
         <v>19</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="O2" s="18" t="s">
         <v>15</v>
@@ -2085,47 +2120,47 @@
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:15">
       <c r="A3" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:15">
@@ -2156,10 +2191,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -2171,9 +2206,9 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="21"/>
+        <v>37</v>
+      </c>
+      <c r="N5" s="20"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1">
@@ -2186,10 +2221,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -2201,9 +2236,9 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N6" s="21"/>
+        <v>39</v>
+      </c>
+      <c r="N6" s="20"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1">
@@ -2216,10 +2251,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -2231,9 +2266,9 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7" s="21"/>
+        <v>37</v>
+      </c>
+      <c r="N7" s="20"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
@@ -2246,10 +2281,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2261,9 +2296,9 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="21"/>
+        <v>42</v>
+      </c>
+      <c r="N8" s="20"/>
       <c r="O8" s="5">
         <v>1</v>
       </c>
@@ -2279,10 +2314,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -2294,9 +2329,9 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" s="21"/>
+        <v>44</v>
+      </c>
+      <c r="N9" s="20"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:15">
       <c r="A10" s="9">
@@ -2309,32 +2344,31 @@
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="22" t="s">
+      <c r="I10" s="21" t="s">
         <v>46</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="K10" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N10" s="24"/>
+      <c r="M10" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" s="23"/>
       <c r="O10" s="14"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:15">
@@ -2348,10 +2382,10 @@
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="14">
         <v>46105</v>
@@ -2359,23 +2393,22 @@
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="22" t="s">
+      <c r="I11" s="21" t="s">
         <v>51</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>52</v>
       </c>
       <c r="K11" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="N11" s="24"/>
+      <c r="M11" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="23"/>
       <c r="O11" s="14"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:15">
@@ -2389,10 +2422,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="14">
         <v>46105</v>
@@ -2400,23 +2433,22 @@
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="22" t="s">
+      <c r="I12" s="21" t="s">
         <v>55</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>56</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="N12" s="24"/>
+      <c r="M12" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" s="23"/>
       <c r="O12" s="14"/>
     </row>
     <row r="13" spans="1:14">
@@ -2430,10 +2462,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2445,9 +2477,9 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="21"/>
+        <v>60</v>
+      </c>
+      <c r="N13" s="20"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1">
@@ -2460,10 +2492,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2477,7 +2509,7 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="N14" s="21"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:15">
       <c r="A15" s="10">
@@ -2490,26 +2522,23 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="10"/>
+        <v>36</v>
+      </c>
       <c r="G15" s="10">
         <v>1</v>
       </c>
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="26"/>
+      <c r="N15" s="25"/>
       <c r="O15" s="15"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:15">
@@ -2523,10 +2552,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="15">
         <v>46101</v>
@@ -2534,19 +2563,16 @@
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="25" t="s">
+      <c r="I16" s="24" t="s">
         <v>64</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="26"/>
+      <c r="N16" s="25"/>
       <c r="O16" s="15"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:15">
@@ -2560,10 +2586,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17" s="15">
         <v>46102</v>
@@ -2571,19 +2597,16 @@
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="J17" s="25" t="s">
+      <c r="I17" s="24" t="s">
         <v>64</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="26"/>
+      <c r="N17" s="25"/>
       <c r="O17" s="15"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:15">
@@ -2597,10 +2620,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>
@@ -2608,21 +2631,21 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="M18" s="11">
-        <v>21000000</v>
-      </c>
-      <c r="N18" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="O18" s="28"/>
+        <v>69</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="O18" s="27"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:15">
       <c r="A19" s="10">
@@ -2635,10 +2658,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19" s="15">
         <v>46103</v>
@@ -2649,20 +2672,18 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="26"/>
+      <c r="N19" s="25"/>
       <c r="O19" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="14:14">
-      <c r="N20" s="21"/>
+      <c r="N20" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -2700,10 +2721,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2711,7 +2732,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2719,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2727,7 +2748,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2735,7 +2756,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2743,7 +2764,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2751,7 +2772,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2759,7 +2780,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2767,7 +2788,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2775,7 +2796,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2783,7 +2804,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2791,7 +2812,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2799,7 +2820,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2807,7 +2828,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2815,7 +2836,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2823,7 +2844,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2831,7 +2852,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2839,7 +2860,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2847,7 +2868,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -543,8 +543,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-获得道具数量_购买原价
-</t>
+获得道具数量_购买原价_实际购买价格</t>
         </r>
       </text>
     </comment>
@@ -575,7 +574,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="96">
   <si>
     <t>序列ID</t>
   </si>
@@ -796,7 +795,10 @@
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
   </si>
   <si>
-    <t>17466000_174.65</t>
+    <t>1022501_100_1022502_50</t>
+  </si>
+  <si>
+    <t>17466000_174.65_4.99</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
@@ -1074,12 +1076,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2029,8 +2031,8 @@
     <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="22.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.85" style="1" customWidth="1"/>
+    <col min="13" max="13" width="27.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="23.5" style="1" customWidth="1"/>
     <col min="15" max="15" width="23.25" style="1" customWidth="1"/>
     <col min="16" max="16" width="41.875" style="5" customWidth="1"/>
     <col min="17" max="17" width="9" style="1"/>
@@ -2664,12 +2666,14 @@
       <c r="L18" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="M18" s="11"/>
+      <c r="M18" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="N18" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O18" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P18" s="29"/>
     </row>
@@ -2684,7 +2688,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2747,10 +2751,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2758,7 +2762,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2766,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2774,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2782,7 +2786,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2790,7 +2794,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2798,7 +2802,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2806,7 +2810,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2814,7 +2818,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2822,7 +2826,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2830,7 +2834,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2838,7 +2842,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2846,7 +2850,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2854,7 +2858,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2862,7 +2866,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2870,7 +2874,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2878,7 +2882,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2886,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2894,7 +2898,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="98">
   <si>
     <t>序列ID</t>
   </si>
@@ -702,6 +702,12 @@
     <t>活跃-摇钱树(常驻)</t>
   </si>
   <si>
+    <t>2025/10/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2025/11/30 23:59:59</t>
+  </si>
+  <si>
     <t>1_2_3_4_5_6_7_8</t>
   </si>
   <si>
@@ -795,10 +801,10 @@
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
   </si>
   <si>
-    <t>1022501_100_1022502_50</t>
-  </si>
-  <si>
-    <t>17466000_174.65_4.99</t>
+    <t>1022501_10_1022502_20_1022503_20_1010302_5</t>
+  </si>
+  <si>
+    <t>10479000_174.65_4.99</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
@@ -1076,12 +1082,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2251,16 +2257,19 @@
         <v>39</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>9999</v>
+        <v>2</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O6" s="22"/>
     </row>
@@ -2275,7 +2284,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -2305,7 +2314,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>39</v>
@@ -2320,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O8" s="22"/>
       <c r="P8" s="5">
@@ -2338,7 +2347,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -2353,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O9" s="22"/>
     </row>
@@ -2368,7 +2377,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>39</v>
@@ -2378,19 +2387,19 @@
         <v>3</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K10" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N10" s="24"/>
       <c r="O10" s="25"/>
@@ -2407,7 +2416,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>39</v>
@@ -2419,19 +2428,19 @@
         <v>3</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K11" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M11" s="24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N11" s="24"/>
       <c r="O11" s="25"/>
@@ -2448,7 +2457,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>39</v>
@@ -2460,19 +2469,19 @@
         <v>3</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J12" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N12" s="24"/>
       <c r="O12" s="25"/>
@@ -2489,7 +2498,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>39</v>
@@ -2504,7 +2513,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O13" s="22"/>
     </row>
@@ -2519,7 +2528,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>39</v>
@@ -2549,7 +2558,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -2579,7 +2588,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -2591,10 +2600,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
@@ -2613,7 +2622,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -2625,10 +2634,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
@@ -2647,10 +2656,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>
@@ -2664,16 +2673,16 @@
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O18" s="22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P18" s="29"/>
     </row>
@@ -2688,7 +2697,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2751,10 +2760,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2762,7 +2771,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2770,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2778,7 +2787,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2786,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2794,7 +2803,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2802,7 +2811,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2810,7 +2819,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2818,7 +2827,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2826,7 +2835,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2834,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2842,7 +2851,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:2">
@@ -2850,7 +2859,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:2">
@@ -2858,7 +2867,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:2">
@@ -2866,7 +2875,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:2">
@@ -2874,7 +2883,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:2">
@@ -2882,7 +2891,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:2">
@@ -2890,7 +2899,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2898,7 +2907,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -2332,9 +2332,6 @@
         <v>47</v>
       </c>
       <c r="O8" s="22"/>
-      <c r="P8" s="5">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
@@ -2717,9 +2714,7 @@
         <v>1</v>
       </c>
       <c r="O19" s="27"/>
-      <c r="P19" s="15">
-        <v>3</v>
-      </c>
+      <c r="P19" s="15"/>
     </row>
     <row r="20" spans="15:15">
       <c r="O20" s="22"/>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99E4968-EE9B-4C46-8706-ACCE3E2F2C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -35,12 +29,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -160,7 +154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="L5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -182,7 +176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="L6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -204,7 +198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="L7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -226,7 +220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="L8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -248,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="L9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -270,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="I10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -292,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="J10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -314,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="M10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -342,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="I11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -364,7 +358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="J11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -387,7 +381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="M11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -414,7 +408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+    <comment ref="I12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -436,7 +430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+    <comment ref="J12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -459,7 +453,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+    <comment ref="M12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +481,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+    <comment ref="L13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+    <comment ref="L18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -531,7 +525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+    <comment ref="N18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -549,11 +543,12 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-参数：售价_原价_总计获得</t>
+获得道具数量_购买原价
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+    <comment ref="O18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -571,7 +566,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-购买金额_原价金额</t>
+渠道ID_商品ID|……</t>
         </r>
       </text>
     </comment>
@@ -580,7 +575,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>序列ID</t>
   </si>
@@ -624,6 +619,9 @@
     <t>值3</t>
   </si>
   <si>
+    <t>渠道和商品ID</t>
+  </si>
+  <si>
     <t>掉落id</t>
   </si>
   <si>
@@ -639,9 +637,15 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>list&lt;long&gt;{_}</t>
+  </si>
+  <si>
     <t>list&lt;BigDecimal&gt;{_}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -681,6 +685,9 @@
     <t>bigDecimalParam</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>dropConfigId</t>
   </si>
   <si>
@@ -789,7 +796,10 @@
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
   </si>
   <si>
-    <t>4.99_174.65</t>
+    <t>17466000_174.65</t>
+  </si>
+  <si>
+    <t>1_google499|2_ios499</t>
   </si>
   <si>
     <t>活跃-收集拼图</t>
@@ -850,17 +860,19 @@
   </si>
   <si>
     <t>我的赌场</t>
-  </si>
-  <si>
-    <t>list&lt;long&gt;{_}</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,10 +916,162 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFBFBFBF"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -920,29 +1084,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -951,25 +1094,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14993743705557422"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="0" tint="-0.149937437055574"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.0999786370433668"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -981,7 +1124,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -991,8 +1134,182 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1015,9 +1332,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1076,14 +1635,17 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1096,7 +1658,7 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1105,56 +1667,59 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1167,9 +1732,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1447,14 +2009,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
@@ -1467,15 +2029,16 @@
     <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="23.375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="41.875" style="5" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1"/>
-    <col min="17" max="17" width="26.75" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="13" max="13" width="22.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.85" style="1" customWidth="1"/>
+    <col min="15" max="15" width="23.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="41.875" style="5" customWidth="1"/>
+    <col min="17" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="26.75" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1518,101 +2081,110 @@
       <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="P1" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A2" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A3" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1627,9 +2199,10 @@
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="17"/>
-      <c r="O4" s="18"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O4" s="17"/>
+      <c r="P4" s="18"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <v>57002</v>
       </c>
@@ -1640,10 +2213,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1655,11 +2228,11 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="21"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="O5" s="22"/>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>57003</v>
       </c>
@@ -1670,10 +2243,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1685,11 +2258,11 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N6" s="21"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="O6" s="22"/>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <v>57004</v>
       </c>
@@ -1700,10 +2273,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1715,11 +2288,11 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7" s="21"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="O7" s="22"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -1730,10 +2303,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1745,14 +2318,14 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="21"/>
-      <c r="O8" s="5">
+        <v>45</v>
+      </c>
+      <c r="O8" s="22"/>
+      <c r="P8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <v>57006</v>
       </c>
@@ -1763,10 +2336,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1778,11 +2351,11 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" s="21"/>
-    </row>
-    <row r="10" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="O9" s="22"/>
+    </row>
+    <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
         <v>57101</v>
       </c>
@@ -1793,34 +2366,35 @@
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>46</v>
+      <c r="I10" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="K10" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" s="23" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="M10" s="24" t="s">
+        <v>52</v>
       </c>
       <c r="N10" s="24"/>
-      <c r="O10" s="14"/>
-    </row>
-    <row r="11" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O10" s="25"/>
+      <c r="P10" s="14"/>
+    </row>
+    <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
         <v>57102</v>
       </c>
@@ -1831,10 +2405,10 @@
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F11" s="14">
         <v>46105</v>
@@ -1842,25 +2416,26 @@
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>51</v>
+      <c r="I11" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>55</v>
       </c>
       <c r="K11" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>53</v>
+        <v>56</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>57</v>
       </c>
       <c r="N11" s="24"/>
-      <c r="O11" s="14"/>
-    </row>
-    <row r="12" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O11" s="25"/>
+      <c r="P11" s="14"/>
+    </row>
+    <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
         <v>57103</v>
       </c>
@@ -1871,10 +2446,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F12" s="14">
         <v>46105</v>
@@ -1882,25 +2457,26 @@
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="22" t="s">
-        <v>55</v>
+      <c r="I12" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>59</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="N12" s="24"/>
-      <c r="O12" s="14"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="25"/>
+      <c r="P12" s="14"/>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
         <v>57010</v>
       </c>
@@ -1911,10 +2487,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -1926,11 +2502,11 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="21"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+      <c r="O13" s="22"/>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
         <v>57011</v>
       </c>
@@ -1941,10 +2517,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -1958,9 +2534,9 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="N14" s="21"/>
-    </row>
-    <row r="15" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O14" s="22"/>
+    </row>
+    <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
         <v>57012</v>
       </c>
@@ -1971,10 +2547,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G15" s="10">
         <v>1</v>
@@ -1982,15 +2558,15 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="N15" s="26"/>
-      <c r="O15" s="15"/>
-    </row>
-    <row r="16" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O15" s="27"/>
+      <c r="P15" s="15"/>
+    </row>
+    <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
         <v>57013</v>
       </c>
@@ -2001,10 +2577,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F16" s="15">
         <v>46101</v>
@@ -2012,19 +2588,19 @@
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="25" t="s">
-        <v>64</v>
+      <c r="I16" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="N16" s="26"/>
-      <c r="O16" s="15"/>
-    </row>
-    <row r="17" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O16" s="27"/>
+      <c r="P16" s="15"/>
+    </row>
+    <row r="17" s="10" customFormat="1" spans="1:16">
       <c r="A17" s="10">
         <v>57014</v>
       </c>
@@ -2035,10 +2611,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F17" s="15">
         <v>46102</v>
@@ -2046,19 +2622,19 @@
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>64</v>
+      <c r="I17" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="N17" s="26"/>
-      <c r="O17" s="15"/>
-    </row>
-    <row r="18" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="O17" s="27"/>
+      <c r="P17" s="15"/>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:16">
       <c r="A18" s="11">
         <v>57015</v>
       </c>
@@ -2069,10 +2645,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>
@@ -2080,23 +2656,24 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="M18" s="11">
-        <v>21000000</v>
-      </c>
-      <c r="N18" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="O18" s="28"/>
-    </row>
-    <row r="19" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="O18" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="P18" s="29"/>
+    </row>
+    <row r="19" s="10" customFormat="1" spans="1:16">
       <c r="A19" s="10">
         <v>57016</v>
       </c>
@@ -2107,10 +2684,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F19" s="15">
         <v>46103</v>
@@ -2121,249 +2698,251 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="N19" s="26"/>
-      <c r="O19" s="15">
+      <c r="O19" s="27"/>
+      <c r="P19" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="N20" s="21"/>
+    <row r="20" spans="15:15">
+      <c r="O20" s="22"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A5:D31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:2">
       <c r="A7" s="3">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:2">
       <c r="A8" s="3">
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:2">
       <c r="A9" s="3">
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:2">
       <c r="A10" s="3">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:2">
       <c r="A11" s="3">
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:2">
       <c r="A12" s="3">
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:2">
       <c r="A13" s="3">
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:2">
       <c r="A14" s="3">
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:2">
       <c r="A15" s="3">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:2">
       <c r="A16" s="3">
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:2">
       <c r="A17" s="3">
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:2">
       <c r="A18" s="3">
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:2">
       <c r="A19" s="3">
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:2">
       <c r="A20" s="3">
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:2">
       <c r="A22" s="3">
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" ht="21.95" customHeight="1" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="21.95" customHeight="1" spans="1:4">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="21.95" customHeight="1" spans="1:4">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="21.95" customHeight="1" spans="1:4">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
     </row>
-    <row r="31" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="21.95" customHeight="1" spans="1:4">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="A27:A31">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -738,34 +738,34 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>500000000_1000_1_1</t>
+    <t>89050000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
   </si>
   <si>
-    <t>0 0 0 1 * ?</t>
-  </si>
-  <si>
-    <t>0 0 0 5 * ?</t>
+    <t>0 0 0 10 * ?</t>
+  </si>
+  <si>
+    <t>59 59 23 10 * ?</t>
   </si>
   <si>
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>1000000000_1000_2_2</t>
-  </si>
-  <si>
-    <t>0 0 0 15 * ?</t>
+    <t>534300000_50_2_2</t>
   </si>
   <si>
     <t>0 0 0 20 * ?</t>
   </si>
   <si>
+    <t>59 59 23 20 * ?</t>
+  </si>
+  <si>
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>2000000000_1000_3_2</t>
+    <t>6678780000_500_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -1082,12 +1082,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1631,32 +1631,29 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -1668,6 +1665,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
@@ -2071,10 +2071,10 @@
       <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="13" t="s">
@@ -2086,13 +2086,13 @@
       <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2119,28 +2119,28 @@
       <c r="H2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="14" t="s">
         <v>17</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2167,10 +2167,10 @@
       <c r="H3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="14" t="s">
         <v>31</v>
       </c>
       <c r="K3" s="13" t="s">
@@ -2182,13 +2182,13 @@
       <c r="M3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="16" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2201,16 +2201,16 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="18"/>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="16"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>57002</v>
       </c>
@@ -2238,9 +2238,9 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="22"/>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="O5" s="20"/>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>57003</v>
       </c>
@@ -2271,9 +2271,9 @@
       <c r="L6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="O6" s="22"/>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="O6" s="20"/>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>57004</v>
       </c>
@@ -2301,9 +2301,9 @@
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="22"/>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="O7" s="20"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>57005</v>
       </c>
@@ -2331,9 +2331,9 @@
       <c r="L8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="O8" s="22"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="O8" s="20"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <v>57006</v>
       </c>
@@ -2361,7 +2361,7 @@
       <c r="L9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="20"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2379,14 +2379,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="14"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="22" t="s">
         <v>52</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2395,12 +2395,12 @@
       <c r="L10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="24"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="14"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="21"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2418,16 +2418,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="21">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="22" t="s">
         <v>57</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2436,12 +2436,12 @@
       <c r="L11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="24" t="s">
+      <c r="M11" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="24"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="14"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="21"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2459,16 +2459,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="21">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J12" s="22" t="s">
         <v>61</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2477,14 +2477,14 @@
       <c r="L12" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="24" t="s">
+      <c r="M12" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="N12" s="24"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="14"/>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" s="23"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="21"/>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1">
         <v>57010</v>
       </c>
@@ -2512,9 +2512,9 @@
       <c r="L13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O13" s="22"/>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="O13" s="20"/>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1">
         <v>57011</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="22"/>
+      <c r="O14" s="20"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2566,13 +2566,13 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O15" s="27"/>
-      <c r="P15" s="15"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="27"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2590,23 +2590,23 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="27">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="26" t="s">
+      <c r="J16" s="25" t="s">
         <v>70</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O16" s="27"/>
-      <c r="P16" s="15"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="27"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:16">
       <c r="A17" s="10">
@@ -2624,23 +2624,23 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="27">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="26" t="s">
+      <c r="I17" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="26" t="s">
+      <c r="J17" s="25" t="s">
         <v>70</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="27"/>
-      <c r="P17" s="15"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="27"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:16">
       <c r="A18" s="11">
@@ -2678,7 +2678,7 @@
       <c r="N18" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="O18" s="22" t="s">
+      <c r="O18" s="20" t="s">
         <v>77</v>
       </c>
       <c r="P18" s="29"/>
@@ -2699,7 +2699,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="27">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2708,16 +2708,16 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="27"/>
-      <c r="P19" s="15"/>
-    </row>
-    <row r="20" spans="15:15">
-      <c r="O20" s="22"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="27"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="O20" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -2849,7 +2849,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:2">
+    <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="3">
         <v>11</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:2">
+    <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="3">
         <v>12</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:2">
+    <row r="19" ht="16.5" spans="1:4">
       <c r="A19" s="3">
         <v>13</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:2">
+    <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="3">
         <v>14</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:2">
+    <row r="21" ht="16.5" spans="1:4">
       <c r="A21" s="4">
         <v>15</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:2">
+    <row r="22" ht="16.5" spans="1:4">
       <c r="A22" s="3">
         <v>16</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>101</v>
       </c>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -702,6 +702,9 @@
     <t>活跃-摇钱树(常驻)</t>
   </si>
   <si>
+    <t>1_5</t>
+  </si>
+  <si>
     <t>2025/10/01 00:00:00</t>
   </si>
   <si>
@@ -793,9 +796,6 @@
   </si>
   <si>
     <t>活跃&amp;付费-成长基金(常驻)</t>
-  </si>
-  <si>
-    <t>1_5</t>
   </si>
   <si>
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
@@ -1082,12 +1082,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2254,22 +2254,22 @@
         <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O6" s="20"/>
     </row>
@@ -2284,7 +2284,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -2314,7 +2314,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>39</v>
@@ -2329,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O8" s="20"/>
     </row>
@@ -2344,7 +2344,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -2359,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O9" s="20"/>
     </row>
@@ -2374,7 +2374,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>39</v>
@@ -2384,19 +2384,19 @@
         <v>3</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N10" s="23"/>
       <c r="O10" s="24"/>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>39</v>
@@ -2425,19 +2425,19 @@
         <v>3</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N11" s="23"/>
       <c r="O11" s="24"/>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>39</v>
@@ -2466,19 +2466,19 @@
         <v>3</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N12" s="23"/>
       <c r="O12" s="24"/>
@@ -2495,7 +2495,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>39</v>
@@ -2510,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O13" s="20"/>
     </row>
@@ -2525,10 +2525,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2555,7 +2555,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -2585,7 +2585,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -2597,10 +2597,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J16" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
@@ -2619,7 +2619,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -2631,10 +2631,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J17" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
@@ -2653,10 +2653,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -741,7 +741,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>89050000_10_1_1</t>
+    <t>10680000_1_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
@@ -756,7 +756,7 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>534300000_50_2_2</t>
+    <t>64110000_5_2_2</t>
   </si>
   <si>
     <t>0 0 0 20 * ?</t>
@@ -768,7 +768,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>6678780000_500_3_2</t>
+    <t>400720000_25_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="96">
   <si>
     <t>序列ID</t>
   </si>
@@ -741,34 +741,28 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>10680000_1_1_1</t>
+    <t>10680000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
   </si>
   <si>
-    <t>0 0 0 10 * ?</t>
-  </si>
-  <si>
-    <t>59 59 23 10 * ?</t>
+    <t>0 0 0 1 * ?</t>
+  </si>
+  <si>
+    <t>59 59 23 28 * ?</t>
   </si>
   <si>
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>64110000_5_2_2</t>
-  </si>
-  <si>
-    <t>0 0 0 20 * ?</t>
-  </si>
-  <si>
-    <t>59 59 23 20 * ?</t>
+    <t>64110000_50_2_2</t>
   </si>
   <si>
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>400720000_25_3_2</t>
+    <t>400720000_500_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -2466,19 +2460,19 @@
         <v>3</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N12" s="23"/>
       <c r="O12" s="24"/>
@@ -2495,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>39</v>
@@ -2510,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O13" s="20"/>
     </row>
@@ -2525,7 +2519,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>42</v>
@@ -2555,7 +2549,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -2585,7 +2579,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -2597,10 +2591,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J16" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
@@ -2619,7 +2613,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -2631,10 +2625,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J17" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
@@ -2653,7 +2647,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>42</v>
@@ -2670,16 +2664,16 @@
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="N18" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="O18" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="N18" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="O18" s="20" t="s">
-        <v>77</v>
       </c>
       <c r="P18" s="29"/>
     </row>
@@ -2694,7 +2688,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2755,10 +2749,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2766,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2774,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2782,7 +2776,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2790,7 +2784,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2798,7 +2792,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2806,7 +2800,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2814,7 +2808,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2822,7 +2816,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2830,7 +2824,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2838,7 +2832,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2846,7 +2840,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -2854,7 +2848,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -2862,7 +2856,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -2870,7 +2864,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -2878,7 +2872,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -2886,7 +2880,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -2894,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2902,7 +2896,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -711,7 +711,7 @@
     <t>2025/11/30 23:59:59</t>
   </si>
   <si>
-    <t>1_2_3_4_5_6_7_8</t>
+    <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15</t>
   </si>
   <si>
     <t>付费-储钱罐(常驻)</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -741,7 +741,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>10680000_10_1_1</t>
+    <t>57990000_40_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
@@ -756,13 +756,13 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>64110000_50_2_2</t>
+    <t>773300000_200_2_2</t>
   </si>
   <si>
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>400720000_500_3_2</t>
+    <t>7733020000_1000_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -798,7 +798,7 @@
     <t>1022501_10_1022502_20_1022503_20_1010302_5</t>
   </si>
   <si>
-    <t>10479000_174.65_4.99</t>
+    <t>16766400_39.92_4.99</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -708,7 +708,7 @@
     <t>2025/10/01 00:00:00</t>
   </si>
   <si>
-    <t>2025/11/30 23:59:59</t>
+    <t>2025/12/31 23:59:59</t>
   </si>
   <si>
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -569,12 +569,79 @@
         </r>
       </text>
     </comment>
+    <comment ref="I20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+期数</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="98">
   <si>
     <t>序列ID</t>
   </si>
@@ -805,6 +872,12 @@
   </si>
   <si>
     <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>付费-无尽优惠(常驻)-时段开</t>
+  </si>
+  <si>
+    <t>1_</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1087,7 +1160,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1109,6 +1182,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1458,7 +1537,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1482,16 +1561,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1500,89 +1579,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1619,28 +1698,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1653,7 +1735,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1669,6 +1751,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2028,7 +2117,7 @@
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="12" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="13" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.125" style="1" customWidth="1"/>
@@ -2041,168 +2130,168 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13" t="s">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="O3" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="P3" s="17" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="16"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="17"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1">
@@ -2232,7 +2321,7 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="20"/>
+      <c r="O5" s="21"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
@@ -2253,10 +2342,10 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="13" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="1" t="b">
@@ -2265,7 +2354,7 @@
       <c r="L6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="20"/>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2295,7 +2384,7 @@
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="20"/>
+      <c r="O7" s="21"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
@@ -2325,7 +2414,7 @@
       <c r="L8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="20"/>
+      <c r="O8" s="21"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1">
@@ -2355,7 +2444,7 @@
       <c r="L9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="20"/>
+      <c r="O9" s="21"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2373,14 +2462,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="21"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="23" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2389,12 +2478,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="23"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="21"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="22"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2412,16 +2501,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="23" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2430,12 +2519,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="M11" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="21"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="22"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2453,16 +2542,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="22">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="23" t="s">
         <v>58</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2471,12 +2560,12 @@
       <c r="L12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="23" t="s">
+      <c r="M12" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="21"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="22"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1">
@@ -2506,7 +2595,7 @@
       <c r="L13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="21"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2536,7 +2625,7 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="20"/>
+      <c r="O14" s="21"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2560,13 +2649,13 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O15" s="26"/>
-      <c r="P15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="28"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2584,23 +2673,23 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="J16" s="25" t="s">
+      <c r="J16" s="26" t="s">
         <v>69</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O16" s="26"/>
-      <c r="P16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="28"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:16">
       <c r="A17" s="10">
@@ -2618,23 +2707,23 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="26" t="s">
         <v>69</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="26"/>
-      <c r="P17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="28"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:16">
       <c r="A18" s="11">
@@ -2658,8 +2747,8 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
@@ -2672,10 +2761,10 @@
       <c r="N18" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="O18" s="20" t="s">
+      <c r="O18" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="P18" s="29"/>
+      <c r="P18" s="30"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:16">
       <c r="A19" s="10">
@@ -2693,7 +2782,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2702,35 +2791,72 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="26"/>
-      <c r="P19" s="27"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="O20" s="20"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="28"/>
+    </row>
+    <row r="20" s="12" customFormat="1" spans="1:16">
+      <c r="A20" s="12">
+        <v>57203</v>
+      </c>
+      <c r="B20" s="12">
+        <v>57017</v>
+      </c>
+      <c r="C20" s="12">
+        <v>17</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="31"/>
+      <c r="G20" s="12">
+        <v>3</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="J20" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="12">
+        <v>1</v>
+      </c>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="31"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
+  <conditionalFormatting sqref="F17">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
+  <conditionalFormatting sqref="F19">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2749,10 +2875,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2760,7 +2886,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2768,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2776,7 +2902,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2784,7 +2910,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2792,7 +2918,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2800,7 +2926,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2808,7 +2934,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2816,7 +2942,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2824,7 +2950,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2832,7 +2958,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2840,7 +2966,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -2848,7 +2974,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -2856,7 +2982,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -2864,7 +2990,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -2872,7 +2998,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -2880,7 +3006,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -2896,7 +3022,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -641,7 +641,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="99">
   <si>
     <t>序列ID</t>
   </si>
@@ -841,7 +841,10 @@
     <t>付费-首充(常驻)</t>
   </si>
   <si>
-    <t>付费-每日首充</t>
+    <t>付费-每日充值</t>
+  </si>
+  <si>
+    <t>1_2_3_4_101_102_103_104_105</t>
   </si>
   <si>
     <t>付费-特惠礼包</t>
@@ -2654,6 +2657,9 @@
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
+      <c r="L15" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="O15" s="27"/>
       <c r="P15" s="28"/>
     </row>
@@ -2668,7 +2674,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -2680,10 +2686,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
@@ -2702,7 +2708,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -2714,10 +2720,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
@@ -2736,7 +2742,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>42</v>
@@ -2753,16 +2759,16 @@
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P18" s="30"/>
     </row>
@@ -2777,7 +2783,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2810,10 +2816,10 @@
         <v>17</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="31"/>
       <c r="G20" s="12">
@@ -2875,10 +2881,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2886,7 +2892,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -2894,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -2902,7 +2908,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -2910,7 +2916,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -2918,7 +2924,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -2926,7 +2932,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -2934,7 +2940,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -2942,7 +2948,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -2950,7 +2956,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -2958,7 +2964,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -2966,7 +2972,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -2974,7 +2980,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -2982,7 +2988,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -2990,7 +2996,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -2998,7 +3004,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3014,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3022,7 +3028,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -636,12 +636,79 @@
         </r>
       </text>
     </comment>
+    <comment ref="I21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+期数</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="99">
   <si>
     <t>序列ID</t>
   </si>
@@ -880,7 +947,7 @@
     <t>付费-无尽优惠(常驻)-时段开</t>
   </si>
   <si>
-    <t>1_</t>
+    <t>付费-新游冲刺(常驻)-时段开</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1152,12 +1219,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1664,7 +1731,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1702,6 +1769,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -2109,7 +2179,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2120,7 +2190,7 @@
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="13" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="14" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.125" style="1" customWidth="1"/>
@@ -2133,168 +2203,168 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="P2" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="20" t="s">
+      <c r="O3" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="17"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="18"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1">
@@ -2324,7 +2394,7 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="21"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
@@ -2345,10 +2415,10 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="14" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="1" t="b">
@@ -2357,7 +2427,7 @@
       <c r="L6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="21"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2387,7 +2457,7 @@
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="21"/>
+      <c r="O7" s="22"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
@@ -2417,7 +2487,7 @@
       <c r="L8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="21"/>
+      <c r="O8" s="22"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1">
@@ -2447,7 +2517,7 @@
       <c r="L9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="21"/>
+      <c r="O9" s="22"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2465,14 +2535,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="22"/>
+      <c r="F10" s="23"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="24" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2481,12 +2551,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="24"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="22"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="23"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2504,16 +2574,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="23">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="24" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2522,12 +2592,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="24" t="s">
+      <c r="M11" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="24"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="22"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="23"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2545,16 +2615,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="23">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J12" s="24" t="s">
         <v>58</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2563,12 +2633,12 @@
       <c r="L12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="24" t="s">
+      <c r="M12" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="N12" s="24"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="22"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="23"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1">
@@ -2598,7 +2668,7 @@
       <c r="L13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O13" s="21"/>
+      <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2628,7 +2698,7 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="21"/>
+      <c r="O14" s="22"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2652,16 +2722,16 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="O15" s="27"/>
-      <c r="P15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="29"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2679,25 +2749,25 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="26" t="s">
+      <c r="J16" s="27" t="s">
         <v>70</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O16" s="27"/>
-      <c r="P16" s="28"/>
-    </row>
-    <row r="17" s="10" customFormat="1" spans="1:16">
+      <c r="O16" s="28"/>
+      <c r="P16" s="29"/>
+    </row>
+    <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
         <v>57014</v>
       </c>
@@ -2713,25 +2783,25 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="29">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="26" t="s">
+      <c r="I17" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="26" t="s">
+      <c r="J17" s="27" t="s">
         <v>70</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="27"/>
-      <c r="P17" s="28"/>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:16">
+      <c r="O17" s="28"/>
+      <c r="P17" s="29"/>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
         <v>57015</v>
       </c>
@@ -2753,8 +2823,8 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
@@ -2767,12 +2837,12 @@
       <c r="N18" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="O18" s="21" t="s">
+      <c r="O18" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="P18" s="30"/>
-    </row>
-    <row r="19" s="10" customFormat="1" spans="1:16">
+      <c r="P18" s="31"/>
+    </row>
+    <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
         <v>57016</v>
       </c>
@@ -2788,7 +2858,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2797,15 +2867,15 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="27"/>
-      <c r="P19" s="28"/>
-    </row>
-    <row r="20" s="12" customFormat="1" spans="1:16">
+      <c r="O19" s="28"/>
+      <c r="P19" s="29"/>
+    </row>
+    <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
         <v>57203</v>
       </c>
@@ -2819,16 +2889,16 @@
         <v>78</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="31"/>
+        <v>39</v>
+      </c>
+      <c r="F20" s="32"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="32" t="s">
+      <c r="J20" s="33" t="s">
         <v>58</v>
       </c>
       <c r="K20" s="12" t="b">
@@ -2837,31 +2907,74 @@
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="31"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="32"/>
+    </row>
+    <row r="21" s="13" customFormat="1" spans="1:18">
+      <c r="A21" s="12">
+        <v>57303</v>
+      </c>
+      <c r="B21" s="12">
+        <v>57018</v>
+      </c>
+      <c r="C21" s="12">
+        <v>18</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="32"/>
+      <c r="G21" s="12">
+        <v>3</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="12">
+        <v>1</v>
+      </c>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
+  <conditionalFormatting sqref="F21">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -708,7 +708,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="103">
   <si>
     <t>序列ID</t>
   </si>
@@ -948,6 +948,18 @@
   </si>
   <si>
     <t>付费-新游冲刺(常驻)-时段开</t>
+  </si>
+  <si>
+    <t>活动-买一送七(常驻)-时段开</t>
+  </si>
+  <si>
+    <t>2025/12/03 00:00:00</t>
+  </si>
+  <si>
+    <t>2026/12/31 23:59:59</t>
+  </si>
+  <si>
+    <t>1_google199|2_ios199</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1219,18 +1231,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1263,6 +1275,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1282,6 +1300,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDBEDD5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1607,7 +1631,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1631,16 +1655,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1649,89 +1673,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1774,28 +1798,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1808,7 +1835,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1831,6 +1858,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2179,7 +2227,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2190,7 +2238,7 @@
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="14" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="15" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.125" style="1" customWidth="1"/>
@@ -2203,168 +2251,168 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15" t="s">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="18"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="19"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1">
@@ -2394,7 +2442,7 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="22"/>
+      <c r="O5" s="23"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
@@ -2415,10 +2463,10 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="15" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="1" t="b">
@@ -2427,7 +2475,7 @@
       <c r="L6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="22"/>
+      <c r="O6" s="23"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2457,7 +2505,7 @@
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="22"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
@@ -2487,7 +2535,7 @@
       <c r="L8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="22"/>
+      <c r="O8" s="23"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1">
@@ -2517,7 +2565,7 @@
       <c r="L9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="23"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2535,14 +2583,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="25" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2551,12 +2599,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="25" t="s">
+      <c r="M10" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="25"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="23"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="24"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2574,16 +2622,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="25" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2592,12 +2640,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="M11" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="25"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="23"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="24"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2615,16 +2663,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="25" t="s">
         <v>58</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2633,12 +2681,12 @@
       <c r="L12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="25" t="s">
+      <c r="M12" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="N12" s="25"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="23"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="24"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1">
@@ -2668,7 +2716,7 @@
       <c r="L13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O13" s="22"/>
+      <c r="O13" s="23"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2698,7 +2746,7 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="22"/>
+      <c r="O14" s="23"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2722,16 +2770,16 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="O15" s="28"/>
-      <c r="P15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="30"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2749,23 +2797,23 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="27" t="s">
+      <c r="I16" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="28" t="s">
         <v>70</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O16" s="28"/>
-      <c r="P16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="30"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
@@ -2783,23 +2831,23 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="27" t="s">
+      <c r="I17" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="27" t="s">
+      <c r="J17" s="28" t="s">
         <v>70</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="28"/>
-      <c r="P17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="30"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
@@ -2823,8 +2871,8 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
@@ -2837,10 +2885,10 @@
       <c r="N18" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="O18" s="22" t="s">
+      <c r="O18" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="P18" s="31"/>
+      <c r="P18" s="32"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -2858,7 +2906,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2867,13 +2915,13 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="28"/>
-      <c r="P19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="30"/>
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
@@ -2891,14 +2939,14 @@
       <c r="E20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="32"/>
+      <c r="F20" s="33"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="33" t="s">
+      <c r="I20" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="33" t="s">
+      <c r="J20" s="34" t="s">
         <v>58</v>
       </c>
       <c r="K20" s="12" t="b">
@@ -2907,10 +2955,10 @@
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="32"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="33"/>
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
@@ -2928,15 +2976,15 @@
       <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="32"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="12">
         <v>3</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="33" t="s">
+      <c r="I21" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="J21" s="33" t="s">
+      <c r="J21" s="34" t="s">
         <v>58</v>
       </c>
       <c r="K21" s="12" t="b">
@@ -2945,36 +2993,79 @@
       <c r="L21" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="32"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="33"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
+    <row r="22" s="14" customFormat="1" spans="1:18">
+      <c r="A22" s="36">
+        <v>57403</v>
+      </c>
+      <c r="B22" s="36">
+        <v>57019</v>
+      </c>
+      <c r="C22" s="37">
+        <v>19</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="38">
+        <v>46106</v>
+      </c>
+      <c r="G22" s="36">
+        <v>2</v>
+      </c>
+      <c r="H22" s="36"/>
+      <c r="I22" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="12">
+        <v>1</v>
+      </c>
+      <c r="O22" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="P22" s="42"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
+  <conditionalFormatting sqref="F21">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
+  <conditionalFormatting sqref="F22">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2994,10 +3085,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3005,7 +3096,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3013,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3021,7 +3112,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3029,7 +3120,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3037,7 +3128,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3045,7 +3136,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3053,7 +3144,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3061,7 +3152,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3069,7 +3160,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3077,7 +3168,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3085,7 +3176,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3093,7 +3184,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3101,7 +3192,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3109,7 +3200,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3117,7 +3208,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3125,7 +3216,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3141,7 +3232,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -703,12 +703,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="L22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+期数</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="101">
   <si>
     <t>序列ID</t>
   </si>
@@ -950,16 +972,10 @@
     <t>付费-新游冲刺(常驻)-时段开</t>
   </si>
   <si>
-    <t>活动-买一送七(常驻)-时段开</t>
-  </si>
-  <si>
-    <t>2025/12/03 00:00:00</t>
-  </si>
-  <si>
-    <t>2026/12/31 23:59:59</t>
-  </si>
-  <si>
-    <t>1_google199|2_ios199</t>
+    <t>买一送七-时段开</t>
+  </si>
+  <si>
+    <t>1_google299|2_ios299</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1231,18 +1247,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1275,12 +1291,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1300,12 +1310,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDBEDD5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1631,7 +1635,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1655,16 +1659,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1673,89 +1677,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1798,31 +1802,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1835,7 +1836,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1858,26 +1859,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2238,7 +2221,7 @@
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="15" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="14" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.125" style="1" customWidth="1"/>
@@ -2251,168 +2234,168 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="P3" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="19"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="18"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1">
@@ -2442,7 +2425,7 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
@@ -2463,10 +2446,10 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="14" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="1" t="b">
@@ -2475,7 +2458,7 @@
       <c r="L6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="23"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2505,7 +2488,7 @@
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="22"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
@@ -2535,7 +2518,7 @@
       <c r="L8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="23"/>
+      <c r="O8" s="22"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1">
@@ -2565,7 +2548,7 @@
       <c r="L9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="23"/>
+      <c r="O9" s="22"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2583,14 +2566,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="24"/>
+      <c r="F10" s="23"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="24" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2599,12 +2582,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="26"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="24"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="23"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2622,16 +2605,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="23">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="24" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2640,12 +2623,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="26"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="24"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="23"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2663,16 +2646,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="23">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="24" t="s">
         <v>58</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2681,12 +2664,12 @@
       <c r="L12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="26" t="s">
+      <c r="M12" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="N12" s="26"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="24"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="23"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1">
@@ -2716,7 +2699,7 @@
       <c r="L13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O13" s="23"/>
+      <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2746,7 +2729,7 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="23"/>
+      <c r="O14" s="22"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2770,16 +2753,16 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="O15" s="29"/>
-      <c r="P15" s="30"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="29"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2797,23 +2780,23 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="28" t="s">
+      <c r="J16" s="27" t="s">
         <v>70</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="30"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="29"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
@@ -2831,23 +2814,23 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="28" t="s">
+      <c r="J17" s="27" t="s">
         <v>70</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="29"/>
-      <c r="P17" s="30"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="29"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
@@ -2871,8 +2854,8 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
@@ -2885,10 +2868,10 @@
       <c r="N18" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="O18" s="23" t="s">
+      <c r="O18" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="P18" s="32"/>
+      <c r="P18" s="31"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -2906,7 +2889,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2915,13 +2898,13 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="29"/>
-      <c r="P19" s="30"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="29"/>
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
@@ -2939,14 +2922,14 @@
       <c r="E20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="33"/>
+      <c r="F20" s="32"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="34" t="s">
+      <c r="J20" s="33" t="s">
         <v>58</v>
       </c>
       <c r="K20" s="12" t="b">
@@ -2955,10 +2938,10 @@
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="33"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="32"/>
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
@@ -2976,15 +2959,15 @@
       <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="33"/>
+      <c r="F21" s="32"/>
       <c r="G21" s="12">
         <v>3</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="34" t="s">
+      <c r="I21" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="J21" s="34" t="s">
+      <c r="J21" s="33" t="s">
         <v>58</v>
       </c>
       <c r="K21" s="12" t="b">
@@ -2993,21 +2976,21 @@
       <c r="L21" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="33"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="32"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
-    <row r="22" s="14" customFormat="1" spans="1:18">
-      <c r="A22" s="36">
+    <row r="22" s="13" customFormat="1" spans="1:18">
+      <c r="A22" s="12">
         <v>57403</v>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="12">
         <v>57019</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="12">
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
@@ -3016,54 +2999,56 @@
       <c r="E22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="38">
-        <v>46106</v>
-      </c>
-      <c r="G22" s="36">
-        <v>2</v>
-      </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="J22" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="K22" s="40" t="b">
+      <c r="F22" s="32"/>
+      <c r="G22" s="12">
+        <v>3</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="12" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="12">
         <v>1</v>
       </c>
-      <c r="O22" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="P22" s="42"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
+  <conditionalFormatting sqref="F21">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -3085,10 +3070,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3096,7 +3081,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3104,7 +3089,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3112,7 +3097,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3120,7 +3105,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3128,7 +3113,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3136,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3144,7 +3129,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3152,7 +3137,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3160,7 +3145,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3168,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3176,7 +3161,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3184,7 +3169,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3192,7 +3177,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3200,7 +3185,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3208,7 +3193,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3216,7 +3201,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3232,7 +3217,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -569,51 +569,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="L20" authorId="0">
       <text>
         <r>
@@ -633,77 +588,10 @@
           </rPr>
           <t xml:space="preserve">
 期数</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？
-</t>
         </r>
       </text>
     </comment>
     <comment ref="L21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-期数</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -730,7 +618,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="103">
   <si>
     <t>序列ID</t>
   </si>
@@ -969,13 +857,19 @@
     <t>付费-无尽优惠(常驻)-时段开</t>
   </si>
   <si>
+    <t>2025/12/03 00:00:00</t>
+  </si>
+  <si>
+    <t>2026/12/31 23:59:59</t>
+  </si>
+  <si>
     <t>付费-新游冲刺(常驻)-时段开</t>
   </si>
   <si>
-    <t>买一送七-时段开</t>
-  </si>
-  <si>
-    <t>1_google299|2_ios299</t>
+    <t>活动-买一送七(常驻)-时段开</t>
+  </si>
+  <si>
+    <t>1_google199|2_ios199</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1258,7 +1152,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1286,6 +1180,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1635,7 +1535,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1659,16 +1559,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1677,89 +1577,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1802,28 +1702,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1836,7 +1739,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1855,12 +1758,24 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2221,7 +2136,7 @@
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="14" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="15" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.125" style="1" customWidth="1"/>
@@ -2234,168 +2149,168 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15" t="s">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="18"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="19"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1">
@@ -2425,7 +2340,7 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="22"/>
+      <c r="O5" s="23"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
@@ -2446,10 +2361,10 @@
       <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="15" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="1" t="b">
@@ -2458,7 +2373,7 @@
       <c r="L6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="22"/>
+      <c r="O6" s="23"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2488,7 +2403,7 @@
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="22"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
@@ -2518,7 +2433,7 @@
       <c r="L8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="22"/>
+      <c r="O8" s="23"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1">
@@ -2548,7 +2463,7 @@
       <c r="L9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="23"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2566,14 +2481,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="23"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="25" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2582,12 +2497,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="25" t="s">
+      <c r="M10" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="25"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="23"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="24"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2605,16 +2520,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="25" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2623,12 +2538,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="M11" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="25"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="23"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="24"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2646,16 +2561,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="25" t="s">
         <v>58</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2664,12 +2579,12 @@
       <c r="L12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="25" t="s">
+      <c r="M12" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="N12" s="25"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="23"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="24"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1">
@@ -2699,7 +2614,7 @@
       <c r="L13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O13" s="22"/>
+      <c r="O13" s="23"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2729,7 +2644,7 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="22"/>
+      <c r="O14" s="23"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2753,16 +2668,16 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
       <c r="K15" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="O15" s="28"/>
-      <c r="P15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="30"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2780,23 +2695,23 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="27" t="s">
+      <c r="I16" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="28" t="s">
         <v>70</v>
       </c>
       <c r="K16" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O16" s="28"/>
-      <c r="P16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="30"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
@@ -2814,23 +2729,23 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="27" t="s">
+      <c r="I17" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="27" t="s">
+      <c r="J17" s="28" t="s">
         <v>70</v>
       </c>
       <c r="K17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="28"/>
-      <c r="P17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="30"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
@@ -2854,8 +2769,8 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
@@ -2868,10 +2783,10 @@
       <c r="N18" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="O18" s="22" t="s">
+      <c r="O18" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="P18" s="31"/>
+      <c r="P18" s="32"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -2889,7 +2804,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2898,13 +2813,13 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
       <c r="K19" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O19" s="28"/>
-      <c r="P19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="30"/>
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
@@ -2922,15 +2837,15 @@
       <c r="E20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="32"/>
+      <c r="F20" s="33"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="J20" s="33" t="s">
-        <v>58</v>
+      <c r="I20" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>80</v>
       </c>
       <c r="K20" s="12" t="b">
         <v>0</v>
@@ -2938,10 +2853,10 @@
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="32"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="33"/>
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
@@ -2954,21 +2869,21 @@
         <v>18</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="32"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="12">
         <v>3</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="J21" s="33" t="s">
-        <v>58</v>
+      <c r="I21" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>80</v>
       </c>
       <c r="K21" s="12" t="b">
         <v>0</v>
@@ -2976,79 +2891,77 @@
       <c r="L21" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="32"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="33"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
-    <row r="22" s="13" customFormat="1" spans="1:18">
-      <c r="A22" s="12">
+    <row r="22" s="14" customFormat="1" spans="1:18">
+      <c r="A22" s="14">
         <v>57403</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="14">
         <v>57019</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="36">
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="12">
-        <v>3</v>
-      </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="J22" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="12" t="b">
+      <c r="F22" s="37">
+        <v>46106</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="K22" s="38" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="12">
         <v>1</v>
       </c>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
+      <c r="O22" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="P22" s="40"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -3070,10 +2983,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3081,7 +2994,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3089,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3097,7 +3010,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3105,7 +3018,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3113,7 +3026,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3121,7 +3034,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3129,7 +3042,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3137,7 +3050,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3145,7 +3058,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3153,7 +3066,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3161,7 +3074,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3169,7 +3082,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3177,7 +3090,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3185,7 +3098,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3193,7 +3106,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3201,7 +3114,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3217,7 +3130,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -785,7 +785,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>57990000_40_1_1</t>
+    <t>20980000_100_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
@@ -800,13 +800,13 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>773300000_200_2_2</t>
+    <t>209890000_500_2_2</t>
   </si>
   <si>
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>7733020000_1000_3_2</t>
+    <t>4197880000_5000_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -1141,12 +1141,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="104">
   <si>
     <t>序列ID</t>
   </si>
@@ -870,6 +870,9 @@
   </si>
   <si>
     <t>1_google199|2_ios199</t>
+  </si>
+  <si>
+    <t>活动-财富轮盘-常驻</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1141,12 +1144,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2125,7 +2128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2823,7 +2826,7 @@
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
-        <v>57203</v>
+        <v>57017</v>
       </c>
       <c r="B20" s="12">
         <v>57017</v>
@@ -2860,7 +2863,7 @@
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
-        <v>57303</v>
+        <v>57018</v>
       </c>
       <c r="B21" s="12">
         <v>57018</v>
@@ -2899,8 +2902,8 @@
       <c r="R21" s="12"/>
     </row>
     <row r="22" s="14" customFormat="1" spans="1:18">
-      <c r="A22" s="14">
-        <v>57403</v>
+      <c r="A22" s="12">
+        <v>57019</v>
       </c>
       <c r="B22" s="14">
         <v>57019</v>
@@ -2938,32 +2941,70 @@
       </c>
       <c r="P22" s="40"/>
     </row>
+    <row r="23" s="14" customFormat="1" spans="1:18">
+      <c r="A23" s="12">
+        <v>57020</v>
+      </c>
+      <c r="B23" s="14">
+        <v>57020</v>
+      </c>
+      <c r="C23" s="36">
+        <v>20</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="37">
+        <v>46106</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>9999</v>
+      </c>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12">
+        <v>1</v>
+      </c>
+      <c r="P23" s="40"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
+  <conditionalFormatting sqref="F21">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
+  <conditionalFormatting sqref="F22">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
+  <conditionalFormatting sqref="F23">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2983,10 +3024,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -2994,7 +3035,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3002,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3010,7 +3051,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3018,7 +3059,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3026,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3034,7 +3075,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3042,7 +3083,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3050,7 +3091,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3058,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3066,7 +3107,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3074,7 +3115,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3082,7 +3123,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3090,7 +3131,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3098,7 +3139,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3106,7 +3147,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3114,7 +3155,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3130,7 +3171,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -618,7 +618,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="105">
   <si>
     <t>序列ID</t>
   </si>
@@ -752,7 +752,7 @@
     <t>2025/10/01 00:00:00</t>
   </si>
   <si>
-    <t>2025/12/31 23:59:59</t>
+    <t>2026/12/31 23:59:59</t>
   </si>
   <si>
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15</t>
@@ -785,28 +785,34 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>20980000_100_1_1</t>
+    <t>9400000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
   </si>
   <si>
-    <t>0 0 0 1 * ?</t>
-  </si>
-  <si>
-    <t>59 59 23 28 * ?</t>
+    <t>0 0 0 7 * ?</t>
+  </si>
+  <si>
+    <t>59 59 23 11 * ?</t>
   </si>
   <si>
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>209890000_500_2_2</t>
+    <t>239300000_10_2_2</t>
+  </si>
+  <si>
+    <t>0 0 0 21 * ?</t>
+  </si>
+  <si>
+    <t>59 59 23 25 * ?</t>
   </si>
   <si>
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>4197880000_5000_3_2</t>
+    <t>119000000_10_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -858,9 +864,6 @@
   </si>
   <si>
     <t>2025/12/03 00:00:00</t>
-  </si>
-  <si>
-    <t>2026/12/31 23:59:59</t>
   </si>
   <si>
     <t>付费-新游冲刺(常驻)-时段开</t>
@@ -1144,18 +1147,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1207,6 +1210,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1538,7 +1547,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1562,16 +1571,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1580,85 +1589,85 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1732,6 +1741,9 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1742,7 +1754,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1770,9 +1782,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2337,13 +2346,13 @@
       <c r="H5" s="1">
         <v>9999</v>
       </c>
-      <c r="K5" s="1" t="b">
-        <v>1</v>
+      <c r="K5" s="23" t="b">
+        <v>0</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="23"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
@@ -2376,7 +2385,7 @@
       <c r="L6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="23"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2400,13 +2409,13 @@
       <c r="H7" s="1">
         <v>9999</v>
       </c>
-      <c r="K7" s="1" t="b">
-        <v>1</v>
+      <c r="K7" s="23" t="b">
+        <v>0</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="24"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
@@ -2430,13 +2439,13 @@
       <c r="H8" s="1">
         <v>9999</v>
       </c>
-      <c r="K8" s="1" t="b">
-        <v>1</v>
+      <c r="K8" s="23" t="b">
+        <v>0</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="23"/>
+      <c r="O8" s="24"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1">
@@ -2466,7 +2475,7 @@
       <c r="L9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="23"/>
+      <c r="O9" s="24"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2484,14 +2493,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="24"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="26" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2500,12 +2509,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="26"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="24"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="25"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2523,16 +2532,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="26" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2541,12 +2550,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="26"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="24"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="25"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2564,30 +2573,30 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>58</v>
+      <c r="I12" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>62</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M12" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12" s="26"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="24"/>
+        <v>63</v>
+      </c>
+      <c r="M12" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" s="27"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="25"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1">
@@ -2600,7 +2609,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>39</v>
@@ -2611,13 +2620,13 @@
       <c r="H13" s="1">
         <v>9999</v>
       </c>
-      <c r="K13" s="1" t="b">
-        <v>1</v>
+      <c r="K13" s="23" t="b">
+        <v>0</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13" s="23"/>
+        <v>66</v>
+      </c>
+      <c r="O13" s="24"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2630,10 +2639,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2641,13 +2650,13 @@
       <c r="H14" s="1">
         <v>9999</v>
       </c>
-      <c r="K14" s="1" t="b">
-        <v>1</v>
+      <c r="K14" s="23" t="b">
+        <v>0</v>
       </c>
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="23"/>
+      <c r="O14" s="24"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2660,7 +2669,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -2671,16 +2680,16 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="10" t="b">
-        <v>1</v>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="23" t="b">
+        <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="O15" s="29"/>
-      <c r="P15" s="30"/>
+        <v>69</v>
+      </c>
+      <c r="O15" s="30"/>
+      <c r="P15" s="31"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2693,28 +2702,28 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" s="29"/>
-      <c r="P16" s="30"/>
+      <c r="I16" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="30"/>
+      <c r="P16" s="31"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
@@ -2727,28 +2736,28 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" s="29"/>
-      <c r="P17" s="30"/>
+      <c r="I17" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="K17" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" s="30"/>
+      <c r="P17" s="31"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
@@ -2761,7 +2770,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>42</v>
@@ -2772,24 +2781,24 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="1" t="b">
-        <v>1</v>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="23" t="b">
+        <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="O18" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="P18" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="O18" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="P18" s="33"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -2802,12 +2811,12 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2816,13 +2825,13 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" s="29"/>
-      <c r="P19" s="30"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" s="30"/>
+      <c r="P19" s="31"/>
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
@@ -2835,31 +2844,31 @@
         <v>17</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="33"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="J20" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="K20" s="12" t="b">
+      <c r="I20" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="K20" s="23" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="33"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="34"/>
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
@@ -2872,32 +2881,32 @@
         <v>18</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="33"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="12">
         <v>3</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="J21" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="K21" s="12" t="b">
+      <c r="I21" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="K21" s="23" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="33"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="34"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
@@ -2908,36 +2917,36 @@
       <c r="B22" s="14">
         <v>57019</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="37">
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="38">
         <v>46106</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="14"/>
-      <c r="I22" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="J22" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="K22" s="38" t="b">
+      <c r="I22" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" s="23" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="12">
         <v>1</v>
       </c>
       <c r="O22" s="39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P22" s="40"/>
     </row>
@@ -2948,16 +2957,16 @@
       <c r="B23" s="14">
         <v>57020</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="37">
         <v>20</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="38">
         <v>46106</v>
       </c>
       <c r="G23" s="14">
@@ -2966,8 +2975,8 @@
       <c r="H23" s="14">
         <v>9999</v>
       </c>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
       <c r="K23" s="1" t="b">
         <v>1</v>
       </c>
@@ -3024,10 +3033,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3035,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3043,7 +3052,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3051,7 +3060,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3059,7 +3068,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3067,7 +3076,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3075,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3083,7 +3092,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3091,7 +3100,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3099,7 +3108,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3107,7 +3116,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3115,7 +3124,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3123,7 +3132,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3131,7 +3140,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3139,7 +3148,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3147,7 +3156,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3155,7 +3164,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3171,7 +3180,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -785,7 +785,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>9400000_10_1_1</t>
+    <t>1242800000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
@@ -800,7 +800,7 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>239300000_10_2_2</t>
+    <t>8285700000_10_2_2</t>
   </si>
   <si>
     <t>0 0 0 21 * ?</t>
@@ -812,7 +812,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>119000000_10_3_2</t>
+    <t>4142800000_10_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -2439,8 +2439,8 @@
       <c r="H8" s="1">
         <v>9999</v>
       </c>
-      <c r="K8" s="23" t="b">
-        <v>0</v>
+      <c r="K8" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>48</v>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -785,7 +785,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>1242800000_10_1_1</t>
+    <t>1280000000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
@@ -800,7 +800,7 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>8285700000_10_2_2</t>
+    <t>8280000000_10_2_2</t>
   </si>
   <si>
     <t>0 0 0 21 * ?</t>
@@ -812,7 +812,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>4142800000_10_3_2</t>
+    <t>3890000000_10_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -785,7 +785,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>1242800000_10_1_1</t>
+    <t>9400000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
@@ -800,7 +800,7 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>8285700000_10_2_2</t>
+    <t>239300000_10_2_2</t>
   </si>
   <si>
     <t>0 0 0 21 * ?</t>
@@ -812,7 +812,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>4142800000_10_3_2</t>
+    <t>119000000_10_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -2439,8 +2439,8 @@
       <c r="H8" s="1">
         <v>9999</v>
       </c>
-      <c r="K8" s="9" t="b">
-        <v>1</v>
+      <c r="K8" s="23" t="b">
+        <v>0</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>48</v>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -785,7 +785,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>9400000_10_1_1</t>
+    <t>1280000000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-时段开</t>
@@ -800,7 +800,7 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>239300000_10_2_2</t>
+    <t>8280000000_10_2_2</t>
   </si>
   <si>
     <t>0 0 0 21 * ?</t>
@@ -812,7 +812,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>119000000_10_3_2</t>
+    <t>3890000000_10_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -2439,8 +2439,8 @@
       <c r="H8" s="1">
         <v>9999</v>
       </c>
-      <c r="K8" s="23" t="b">
-        <v>0</v>
+      <c r="K8" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>48</v>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -481,6 +481,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="E13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+绑定手机后才可以参加活动</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="L13" authorId="0">
       <text>
         <r>
@@ -499,7 +521,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-对应配置表的ID</t>
+对应配置表DailyRewards的ID</t>
         </r>
       </text>
     </comment>
@@ -618,7 +640,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="106">
   <si>
     <t>序列ID</t>
   </si>
@@ -816,6 +838,9 @@
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
+  </si>
+  <si>
+    <t>4_1</t>
   </si>
   <si>
     <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
@@ -2612,7 +2637,7 @@
         <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2620,11 +2645,11 @@
       <c r="H13" s="1">
         <v>9999</v>
       </c>
-      <c r="K13" s="23" t="b">
-        <v>0</v>
+      <c r="K13" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O13" s="24"/>
     </row>
@@ -2639,7 +2664,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>39</v>
@@ -2669,7 +2694,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -2686,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O15" s="30"/>
       <c r="P15" s="31"/>
@@ -2702,7 +2727,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -2714,10 +2739,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K16" s="23" t="b">
         <v>0</v>
@@ -2736,7 +2761,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -2748,10 +2773,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K17" s="23" t="b">
         <v>0</v>
@@ -2770,7 +2795,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>42</v>
@@ -2787,16 +2812,16 @@
         <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" s="33"/>
     </row>
@@ -2811,7 +2836,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2844,7 +2869,7 @@
         <v>17</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>39</v>
@@ -2854,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>44</v>
@@ -2881,7 +2906,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>39</v>
@@ -2892,7 +2917,7 @@
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J21" s="35" t="s">
         <v>44</v>
@@ -2921,7 +2946,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>39</v>
@@ -2934,7 +2959,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J22" s="35" t="s">
         <v>44</v>
@@ -2946,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P22" s="40"/>
     </row>
@@ -2961,7 +2986,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>39</v>
@@ -3033,10 +3058,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3044,7 +3069,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3052,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3060,7 +3085,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3068,7 +3093,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3076,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3084,7 +3109,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3092,7 +3117,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3100,7 +3125,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3108,7 +3133,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3116,7 +3141,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3124,7 +3149,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3132,7 +3157,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3140,7 +3165,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3148,7 +3173,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3156,7 +3181,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3164,7 +3189,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3172,7 +3197,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3180,7 +3205,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
   <si>
     <t>序列ID</t>
   </si>
@@ -810,7 +810,7 @@
     <t>1280000000_10_1_1</t>
   </si>
   <si>
-    <t>付费-官方派奖(常驻)-时段开</t>
+    <t>付费-官方派奖(常驻)-7号开</t>
   </si>
   <si>
     <t>0 0 0 7 * ?</t>
@@ -823,6 +823,9 @@
   </si>
   <si>
     <t>8280000000_10_2_2</t>
+  </si>
+  <si>
+    <t>付费-官方派奖(常驻)-21号开</t>
   </si>
   <si>
     <t>0 0 0 21 * ?</t>
@@ -1172,12 +1175,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2168,7 +2171,7 @@
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
@@ -2593,7 +2596,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>39</v>
@@ -2605,19 +2608,19 @@
         <v>3</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N12" s="27"/>
       <c r="O12" s="28"/>
@@ -2634,10 +2637,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2649,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O13" s="24"/>
     </row>
@@ -2664,7 +2667,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>39</v>
@@ -2694,7 +2697,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -2711,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O15" s="30"/>
       <c r="P15" s="31"/>
@@ -2727,7 +2730,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -2739,10 +2742,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K16" s="23" t="b">
         <v>0</v>
@@ -2761,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -2773,10 +2776,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K17" s="23" t="b">
         <v>0</v>
@@ -2795,7 +2798,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>42</v>
@@ -2812,16 +2815,16 @@
         <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P18" s="33"/>
     </row>
@@ -2836,7 +2839,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2869,7 +2872,7 @@
         <v>17</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>39</v>
@@ -2879,7 +2882,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>44</v>
@@ -2906,7 +2909,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>39</v>
@@ -2917,7 +2920,7 @@
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J21" s="35" t="s">
         <v>44</v>
@@ -2946,7 +2949,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>39</v>
@@ -2959,7 +2962,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J22" s="35" t="s">
         <v>44</v>
@@ -2971,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P22" s="40"/>
     </row>
@@ -2986,7 +2989,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>39</v>
@@ -3058,10 +3061,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3069,7 +3072,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3077,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3085,7 +3088,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3093,7 +3096,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3101,7 +3104,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3109,7 +3112,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3117,7 +3120,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3125,7 +3128,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3133,7 +3136,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3141,7 +3144,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3149,7 +3152,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3157,7 +3160,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3165,7 +3168,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3173,7 +3176,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3181,7 +3184,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3189,7 +3192,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3197,7 +3200,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
   <si>
     <t>序列ID</t>
   </si>
@@ -759,7 +759,7 @@
     <t>付费-每日奖金(常驻)</t>
   </si>
   <si>
-    <t>1_1</t>
+    <t>playerLevel(1)</t>
   </si>
   <si>
     <t>1_2_3</t>
@@ -768,7 +768,7 @@
     <t>活跃-摇钱树(常驻)</t>
   </si>
   <si>
-    <t>1_5</t>
+    <t>playerLevel(5)</t>
   </si>
   <si>
     <t>2025/10/01 00:00:00</t>
@@ -810,7 +810,7 @@
     <t>1280000000_10_1_1</t>
   </si>
   <si>
-    <t>付费-官方派奖(常驻)-时段开</t>
+    <t>付费-官方派奖(常驻)-7号开</t>
   </si>
   <si>
     <t>0 0 0 7 * ?</t>
@@ -825,6 +825,9 @@
     <t>8280000000_10_2_2</t>
   </si>
   <si>
+    <t>付费-官方派奖(常驻)-21号开</t>
+  </si>
+  <si>
     <t>0 0 0 21 * ?</t>
   </si>
   <si>
@@ -840,7 +843,7 @@
     <t>活跃-每日签到(常驻)</t>
   </si>
   <si>
-    <t>4_1</t>
+    <t>bindPhone()</t>
   </si>
   <si>
     <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
@@ -1172,12 +1175,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2168,8 +2171,8 @@
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
@@ -2593,7 +2596,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>39</v>
@@ -2605,19 +2608,19 @@
         <v>3</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N12" s="27"/>
       <c r="O12" s="28"/>
@@ -2634,10 +2637,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -2649,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O13" s="24"/>
     </row>
@@ -2664,7 +2667,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>39</v>
@@ -2694,7 +2697,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -2711,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O15" s="30"/>
       <c r="P15" s="31"/>
@@ -2727,7 +2730,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -2739,10 +2742,10 @@
         <v>2</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K16" s="23" t="b">
         <v>0</v>
@@ -2761,7 +2764,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -2773,10 +2776,10 @@
         <v>2</v>
       </c>
       <c r="I17" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K17" s="23" t="b">
         <v>0</v>
@@ -2795,9 +2798,9 @@
         <v>15</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G18" s="11">
@@ -2812,16 +2815,16 @@
         <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P18" s="33"/>
     </row>
@@ -2836,7 +2839,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2869,7 +2872,7 @@
         <v>17</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>39</v>
@@ -2879,7 +2882,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>44</v>
@@ -2906,7 +2909,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>39</v>
@@ -2917,7 +2920,7 @@
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J21" s="35" t="s">
         <v>44</v>
@@ -2946,7 +2949,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>39</v>
@@ -2959,7 +2962,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J22" s="35" t="s">
         <v>44</v>
@@ -2971,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P22" s="40"/>
     </row>
@@ -2986,7 +2989,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>39</v>
@@ -3058,10 +3061,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3069,7 +3072,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3077,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3085,7 +3088,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3093,7 +3096,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3101,7 +3104,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3109,7 +3112,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3117,7 +3120,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3125,7 +3128,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3133,7 +3136,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3141,7 +3144,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3149,7 +3152,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3157,7 +3160,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3165,7 +3168,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3173,7 +3176,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3181,7 +3184,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3189,7 +3192,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3197,7 +3200,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -1175,18 +1175,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1207,211 +1207,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6C6AC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBEDD5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1575,7 +1569,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1599,16 +1593,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1617,89 +1611,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1736,53 +1730,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1798,24 +1795,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2382,38 +2386,43 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="1">
+    <row r="6" s="9" customFormat="1" spans="1:16">
+      <c r="A6" s="9">
         <v>57003</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="9">
         <v>57003</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="9">
         <v>3</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="1">
+      <c r="F6" s="9"/>
+      <c r="G6" s="9">
         <v>2</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="H6" s="9"/>
+      <c r="I6" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="1" t="b">
+      <c r="K6" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="24"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="27"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2445,65 +2454,77 @@
       </c>
       <c r="O7" s="24"/>
     </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="1">
+    <row r="8" s="9" customFormat="1" spans="1:16">
+      <c r="A8" s="9">
         <v>57005</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="9">
         <v>57005</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="9">
         <v>5</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="1">
+      <c r="F8" s="9"/>
+      <c r="G8" s="9">
         <v>1</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="9">
         <v>9999</v>
       </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
       <c r="K8" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="24"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="1">
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="27"/>
+    </row>
+    <row r="9" s="9" customFormat="1" spans="1:16">
+      <c r="A9" s="9">
         <v>57006</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="9">
         <v>57006</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="9">
         <v>6</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="1">
+      <c r="F9" s="9"/>
+      <c r="G9" s="9">
         <v>1</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="9">
         <v>9999</v>
       </c>
-      <c r="K9" s="1" t="b">
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="O9" s="24"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="27"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2521,14 +2542,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="25"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="I10" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="26" t="s">
+      <c r="J10" s="25" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2537,12 +2558,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="27" t="s">
+      <c r="M10" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="27"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="25"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="27"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2560,16 +2581,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="27">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="26" t="s">
+      <c r="I11" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="26" t="s">
+      <c r="J11" s="25" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2578,12 +2599,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="25"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="27"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2601,16 +2622,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="27">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="26" t="s">
+      <c r="I12" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="26" t="s">
+      <c r="J12" s="25" t="s">
         <v>63</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2619,42 +2640,48 @@
       <c r="L12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="27"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="25"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="1">
+      <c r="N12" s="28"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="27"/>
+    </row>
+    <row r="13" s="9" customFormat="1" spans="1:16">
+      <c r="A13" s="9">
         <v>57010</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="9">
         <v>57010</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="9">
         <v>10</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="1">
+      <c r="F13" s="9"/>
+      <c r="G13" s="9">
         <v>1</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="9">
         <v>9999</v>
       </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
       <c r="K13" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="O13" s="24"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="27"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2708,16 +2735,16 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
       <c r="K15" s="23" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="O15" s="30"/>
-      <c r="P15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="32"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2735,23 +2762,23 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="29" t="s">
+      <c r="I16" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="29" t="s">
+      <c r="J16" s="30" t="s">
         <v>74</v>
       </c>
       <c r="K16" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="O16" s="30"/>
-      <c r="P16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="32"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
@@ -2769,23 +2796,23 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="29" t="s">
+      <c r="J17" s="30" t="s">
         <v>74</v>
       </c>
       <c r="K17" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="O17" s="30"/>
-      <c r="P17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="32"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
@@ -2809,8 +2836,8 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
       <c r="K18" s="23" t="b">
         <v>0</v>
       </c>
@@ -2826,7 +2853,7 @@
       <c r="O18" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="P18" s="33"/>
+      <c r="P18" s="34"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -2844,7 +2871,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="32">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2853,13 +2880,13 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
       <c r="K19" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="O19" s="30"/>
-      <c r="P19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="32"/>
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
@@ -2877,14 +2904,14 @@
       <c r="E20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="34"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="35" t="s">
+      <c r="I20" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="36" t="s">
         <v>44</v>
       </c>
       <c r="K20" s="23" t="b">
@@ -2893,10 +2920,10 @@
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="34"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="35"/>
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
@@ -2914,15 +2941,15 @@
       <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="34"/>
+      <c r="F21" s="35"/>
       <c r="G21" s="12">
         <v>3</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="35" t="s">
+      <c r="I21" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="36" t="s">
         <v>44</v>
       </c>
       <c r="K21" s="23" t="b">
@@ -2931,10 +2958,10 @@
       <c r="L21" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="34"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="35"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
@@ -2945,7 +2972,7 @@
       <c r="B22" s="14">
         <v>57019</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="12">
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
@@ -2954,17 +2981,17 @@
       <c r="E22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="39">
         <v>46106</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="14"/>
-      <c r="I22" s="35" t="s">
+      <c r="I22" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="J22" s="36" t="s">
         <v>44</v>
       </c>
       <c r="K22" s="23" t="b">
@@ -2973,45 +3000,45 @@
       <c r="L22" s="12">
         <v>1</v>
       </c>
-      <c r="O22" s="39" t="s">
+      <c r="O22" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="P22" s="40"/>
-    </row>
-    <row r="23" s="14" customFormat="1" spans="1:18">
-      <c r="A23" s="12">
+      <c r="P22" s="41"/>
+    </row>
+    <row r="23" s="9" customFormat="1" spans="1:18">
+      <c r="A23" s="42">
         <v>57020</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="9">
         <v>57020</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="42">
         <v>20</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="43">
         <v>46106</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="9">
         <v>1</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="9">
         <v>9999</v>
       </c>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="1" t="b">
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="44" t="b">
         <v>1</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="42">
         <v>1</v>
       </c>
-      <c r="P23" s="40"/>
+      <c r="P23" s="27"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -1186,7 +1186,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1232,12 +1232,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1569,7 +1563,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1593,16 +1587,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1611,89 +1605,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1761,9 +1755,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1781,6 +1772,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1817,9 +1811,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2378,13 +2369,13 @@
       <c r="H5" s="1">
         <v>9999</v>
       </c>
-      <c r="K5" s="23" t="b">
-        <v>0</v>
+      <c r="K5" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="24"/>
+      <c r="O5" s="23"/>
     </row>
     <row r="6" s="9" customFormat="1" spans="1:16">
       <c r="A6" s="9">
@@ -2407,10 +2398,10 @@
         <v>2</v>
       </c>
       <c r="H6" s="9"/>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="24" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="9" t="b">
@@ -2421,8 +2412,8 @@
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="27"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="26"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2446,13 +2437,13 @@
       <c r="H7" s="1">
         <v>9999</v>
       </c>
-      <c r="K7" s="23" t="b">
-        <v>0</v>
+      <c r="K7" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="24"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="8" s="9" customFormat="1" spans="1:16">
       <c r="A8" s="9">
@@ -2477,8 +2468,8 @@
       <c r="H8" s="9">
         <v>9999</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
       <c r="K8" s="9" t="b">
         <v>1</v>
       </c>
@@ -2487,8 +2478,8 @@
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="27"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="26"/>
     </row>
     <row r="9" s="9" customFormat="1" spans="1:16">
       <c r="A9" s="9">
@@ -2513,8 +2504,8 @@
       <c r="H9" s="9">
         <v>9999</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
       <c r="K9" s="9" t="b">
         <v>1</v>
       </c>
@@ -2523,8 +2514,8 @@
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="27"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="26"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2542,14 +2533,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="26"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="24" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2558,12 +2549,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="28" t="s">
+      <c r="M10" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="28"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="26"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2581,16 +2572,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="26">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="24" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2599,12 +2590,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="28" t="s">
+      <c r="M11" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="28"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="26"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2622,16 +2613,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="26">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="24" t="s">
         <v>63</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2640,12 +2631,12 @@
       <c r="L12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="28" t="s">
+      <c r="M12" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="28"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="26"/>
     </row>
     <row r="13" s="9" customFormat="1" spans="1:16">
       <c r="A13" s="9">
@@ -2670,8 +2661,8 @@
       <c r="H13" s="9">
         <v>9999</v>
       </c>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
       <c r="K13" s="9" t="b">
         <v>1</v>
       </c>
@@ -2680,8 +2671,8 @@
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="27"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="26"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2705,13 +2696,13 @@
       <c r="H14" s="1">
         <v>9999</v>
       </c>
-      <c r="K14" s="23" t="b">
-        <v>0</v>
+      <c r="K14" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="24"/>
+      <c r="O14" s="23"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2735,9 +2726,9 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="23" t="b">
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="30" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
@@ -2768,13 +2759,13 @@
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="30" t="s">
+      <c r="I16" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="30" t="s">
+      <c r="J16" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="23" t="b">
+      <c r="K16" s="30" t="b">
         <v>0</v>
       </c>
       <c r="O16" s="31"/>
@@ -2802,13 +2793,13 @@
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="30" t="s">
+      <c r="I17" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="30" t="s">
+      <c r="J17" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="K17" s="23" t="b">
+      <c r="K17" s="30" t="b">
         <v>0</v>
       </c>
       <c r="O17" s="31"/>
@@ -2838,8 +2829,8 @@
       </c>
       <c r="I18" s="33"/>
       <c r="J18" s="33"/>
-      <c r="K18" s="23" t="b">
-        <v>0</v>
+      <c r="K18" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
         <v>77</v>
@@ -2850,7 +2841,7 @@
       <c r="N18" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="O18" s="24" t="s">
+      <c r="O18" s="23" t="s">
         <v>80</v>
       </c>
       <c r="P18" s="34"/>
@@ -2880,9 +2871,9 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="23" t="b">
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="30" t="b">
         <v>0</v>
       </c>
       <c r="O19" s="31"/>
@@ -2914,7 +2905,7 @@
       <c r="J20" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="K20" s="23" t="b">
+      <c r="K20" s="30" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="12">
@@ -2952,7 +2943,7 @@
       <c r="J21" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="23" t="b">
+      <c r="K21" s="30" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="12">
@@ -2994,7 +2985,7 @@
       <c r="J22" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="23" t="b">
+      <c r="K22" s="30" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="12">
@@ -3030,15 +3021,15 @@
       <c r="H23" s="9">
         <v>9999</v>
       </c>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="44" t="b">
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L23" s="42">
         <v>1</v>
       </c>
-      <c r="P23" s="27"/>
+      <c r="P23" s="26"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -635,12 +635,56 @@
         </r>
       </text>
     </comment>
+    <comment ref="E24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+不绑定手机后才可以参加活动</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表DailyRewards的ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="110">
   <si>
     <t>序列ID</t>
   </si>
@@ -807,7 +851,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>1280000000_10_1_1</t>
+    <t>70000000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-7号开</t>
@@ -822,7 +866,7 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>8280000000_10_2_2</t>
+    <t>480000000_10_2_2</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-21号开</t>
@@ -837,7 +881,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>3890000000_10_3_2</t>
+    <t>200000000_10_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -873,16 +917,19 @@
     <t>活跃&amp;付费-成长基金(常驻)</t>
   </si>
   <si>
+    <t>1_5</t>
+  </si>
+  <si>
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
   </si>
   <si>
-    <t>1022501_10_1022502_20_1022503_20_1010302_5</t>
-  </si>
-  <si>
-    <t>16766400_39.92_4.99</t>
-  </si>
-  <si>
-    <t>1_google499|2_ios499</t>
+    <t>1022501_50_1022502_10</t>
+  </si>
+  <si>
+    <t>4123000_149.94_24.99</t>
+  </si>
+  <si>
+    <t>1_google2499|2_ios2499</t>
   </si>
   <si>
     <t>活跃-收集拼图</t>
@@ -904,6 +951,12 @@
   </si>
   <si>
     <t>活动-财富轮盘-常驻</t>
+  </si>
+  <si>
+    <t>绑定手机活动-没绑定可以参与</t>
+  </si>
+  <si>
+    <t>bindPhone(1)</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -2160,7 +2213,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2819,7 +2872,7 @@
         <v>76</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>
@@ -2833,16 +2886,16 @@
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O18" s="23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P18" s="34"/>
     </row>
@@ -2857,7 +2910,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2890,7 +2943,7 @@
         <v>17</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>39</v>
@@ -2900,7 +2953,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J20" s="36" t="s">
         <v>44</v>
@@ -2927,7 +2980,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>39</v>
@@ -2938,7 +2991,7 @@
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J21" s="36" t="s">
         <v>44</v>
@@ -2967,7 +3020,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>39</v>
@@ -2980,7 +3033,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J22" s="36" t="s">
         <v>44</v>
@@ -2992,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P22" s="41"/>
     </row>
@@ -3007,7 +3060,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E23" s="42" t="s">
         <v>39</v>
@@ -3030,6 +3083,37 @@
         <v>1</v>
       </c>
       <c r="P23" s="26"/>
+    </row>
+    <row r="24" s="9" customFormat="1" spans="1:18">
+      <c r="A24" s="9">
+        <v>57021</v>
+      </c>
+      <c r="B24" s="9">
+        <v>57021</v>
+      </c>
+      <c r="C24" s="9">
+        <v>21</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="9">
+        <v>1</v>
+      </c>
+      <c r="H24" s="9">
+        <v>9999</v>
+      </c>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="26"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3079,10 +3163,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3090,7 +3174,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3098,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3106,7 +3190,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3114,7 +3198,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3122,7 +3206,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3130,7 +3214,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3138,7 +3222,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3146,7 +3230,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3154,7 +3238,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3162,7 +3246,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3170,7 +3254,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3178,7 +3262,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3186,7 +3270,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3194,7 +3278,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3202,7 +3286,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3210,7 +3294,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3218,7 +3302,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3226,7 +3310,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -684,7 +684,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="108">
   <si>
     <t>序列ID</t>
   </si>
@@ -951,12 +951,6 @@
   </si>
   <si>
     <t>活动-财富轮盘-常驻</t>
-  </si>
-  <si>
-    <t>绑定手机活动-没绑定可以参与</t>
-  </si>
-  <si>
-    <t>bindPhone(1)</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -3085,32 +3079,10 @@
       <c r="P23" s="26"/>
     </row>
     <row r="24" s="9" customFormat="1" spans="1:18">
-      <c r="A24" s="9">
-        <v>57021</v>
-      </c>
-      <c r="B24" s="9">
-        <v>57021</v>
-      </c>
-      <c r="C24" s="9">
-        <v>21</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="9">
-        <v>1</v>
-      </c>
-      <c r="H24" s="9">
-        <v>9999</v>
-      </c>
+      <c r="E24" s="9"/>
       <c r="I24" s="24"/>
       <c r="J24" s="24"/>
-      <c r="K24" s="9" t="b">
-        <v>1</v>
-      </c>
+      <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="O24" s="25"/>
       <c r="P24" s="26"/>
@@ -3163,10 +3135,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3174,7 +3146,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3182,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3190,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3198,7 +3170,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3206,7 +3178,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3214,7 +3186,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3222,7 +3194,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3230,7 +3202,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3238,7 +3210,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3246,7 +3218,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3254,7 +3226,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3262,7 +3234,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3270,7 +3242,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3278,7 +3250,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3286,7 +3258,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3294,7 +3266,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3310,7 +3282,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -684,7 +684,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
   <si>
     <t>序列ID</t>
   </si>
@@ -915,9 +915,6 @@
   </si>
   <si>
     <t>活跃&amp;付费-成长基金(常驻)</t>
-  </si>
-  <si>
-    <t>1_5</t>
   </si>
   <si>
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
@@ -2866,7 +2863,7 @@
         <v>76</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="G18" s="11">
         <v>1</v>
@@ -2880,16 +2877,16 @@
         <v>1</v>
       </c>
       <c r="L18" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="N18" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="O18" s="23" t="s">
         <v>80</v>
-      </c>
-      <c r="O18" s="23" t="s">
-        <v>81</v>
       </c>
       <c r="P18" s="34"/>
     </row>
@@ -2904,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -2937,7 +2934,7 @@
         <v>17</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>39</v>
@@ -2947,7 +2944,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J20" s="36" t="s">
         <v>44</v>
@@ -2974,7 +2971,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>39</v>
@@ -2985,7 +2982,7 @@
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J21" s="36" t="s">
         <v>44</v>
@@ -3014,7 +3011,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>39</v>
@@ -3027,7 +3024,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J22" s="36" t="s">
         <v>44</v>
@@ -3039,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P22" s="41"/>
     </row>
@@ -3054,7 +3051,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" s="42" t="s">
         <v>39</v>
@@ -3135,10 +3132,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3146,7 +3143,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3154,7 +3151,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3162,7 +3159,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3170,7 +3167,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3178,7 +3175,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3186,7 +3183,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3194,7 +3191,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3202,7 +3199,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3210,7 +3207,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3218,7 +3215,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3226,7 +3223,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3234,7 +3231,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3242,7 +3239,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3250,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3258,7 +3255,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3266,7 +3263,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3274,7 +3271,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3282,7 +3279,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -923,7 +923,7 @@
     <t>1022501_50_1022502_10</t>
   </si>
   <si>
-    <t>4123000_149.94_24.99</t>
+    <t>4123000_149_24.99</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -1175,12 +1175,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -1219,12 +1219,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -635,7 +635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0">
+    <comment ref="L24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -653,11 +653,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-不绑定手机后才可以参加活动</t>
+配置表-GrowthFund.xlsx中的ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="L24" authorId="0">
+    <comment ref="N24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -675,7 +675,29 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-对应配置表DailyRewards的ID</t>
+获得道具数量_购买原价_实际购买价格</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+渠道ID_商品ID|……</t>
         </r>
       </text>
     </comment>
@@ -684,7 +706,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="108">
   <si>
     <t>序列ID</t>
   </si>
@@ -851,7 +873,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>70000000_10_1_1</t>
+    <t>60000000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-7号开</t>
@@ -881,7 +903,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>200000000_10_3_2</t>
+    <t>180000000_10_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -923,7 +945,7 @@
     <t>1022501_50_1022502_10</t>
   </si>
   <si>
-    <t>4123000_149_24.99</t>
+    <t>37078000_1249.5_24.99</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
@@ -948,6 +970,9 @@
   </si>
   <si>
     <t>活动-财富轮盘-常驻</t>
+  </si>
+  <si>
+    <t>活跃&amp;付费-成长基金(常驻)2</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1219,18 +1244,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1264,6 +1289,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1607,7 +1638,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1631,16 +1662,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1649,89 +1680,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1792,19 +1823,34 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1813,12 +1859,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1830,6 +1879,9 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1839,10 +1891,13 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2204,7 +2259,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2312,13 +2367,13 @@
       <c r="L2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="22" t="s">
         <v>22</v>
       </c>
       <c r="P2" s="19" t="s">
@@ -2360,13 +2415,13 @@
       <c r="L3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="25" t="s">
         <v>36</v>
       </c>
       <c r="P3" s="19" t="s">
@@ -2386,8 +2441,8 @@
       <c r="J4" s="17"/>
       <c r="K4" s="16"/>
       <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="18"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="24"/>
       <c r="O4" s="18"/>
       <c r="P4" s="19"/>
     </row>
@@ -2419,7 +2474,9 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="23"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="27"/>
     </row>
     <row r="6" s="9" customFormat="1" spans="1:16">
       <c r="A6" s="9">
@@ -2442,10 +2499,10 @@
         <v>2</v>
       </c>
       <c r="H6" s="9"/>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="28" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="9" t="b">
@@ -2454,10 +2511,10 @@
       <c r="L6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="26"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="31"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2487,7 +2544,9 @@
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="23"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="27"/>
     </row>
     <row r="8" s="9" customFormat="1" spans="1:16">
       <c r="A8" s="9">
@@ -2512,18 +2571,18 @@
       <c r="H8" s="9">
         <v>9999</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
       <c r="K8" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="26"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="31"/>
     </row>
     <row r="9" s="9" customFormat="1" spans="1:16">
       <c r="A9" s="9">
@@ -2548,18 +2607,18 @@
       <c r="H9" s="9">
         <v>9999</v>
       </c>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
       <c r="K9" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="26"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="31"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2577,14 +2636,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="31"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="28" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2593,12 +2652,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="27" t="s">
+      <c r="M10" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="27"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="26"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="31"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2616,16 +2675,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="31">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="28" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2634,12 +2693,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="26"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="31"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2657,16 +2716,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="31">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="28" t="s">
         <v>63</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2675,12 +2734,12 @@
       <c r="L12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="27"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="26"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="31"/>
     </row>
     <row r="13" s="9" customFormat="1" spans="1:16">
       <c r="A13" s="9">
@@ -2705,18 +2764,18 @@
       <c r="H13" s="9">
         <v>9999</v>
       </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
       <c r="K13" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="26"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="31"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2746,7 +2805,9 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="23"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="27"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2770,16 +2831,18 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="30" t="b">
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="35" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="O15" s="31"/>
-      <c r="P15" s="32"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="37"/>
+      <c r="P15" s="38"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2797,23 +2860,25 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="38">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="29" t="s">
+      <c r="I16" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="29" t="s">
+      <c r="J16" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="30" t="b">
+      <c r="K16" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="O16" s="31"/>
-      <c r="P16" s="32"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="37"/>
+      <c r="P16" s="38"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
@@ -2831,23 +2896,25 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="38">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="29" t="s">
+      <c r="J17" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="K17" s="30" t="b">
+      <c r="K17" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="O17" s="31"/>
-      <c r="P17" s="32"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="38"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
@@ -2871,24 +2938,24 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="9" t="b">
-        <v>1</v>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="35" t="b">
+        <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="O18" s="23" t="s">
+      <c r="O18" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="P18" s="34"/>
+      <c r="P18" s="41"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -2906,7 +2973,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="38">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2915,13 +2982,15 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="30" t="b">
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="O19" s="31"/>
-      <c r="P19" s="32"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="37"/>
+      <c r="P19" s="38"/>
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
@@ -2939,26 +3008,26 @@
       <c r="E20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="35"/>
+      <c r="F20" s="42"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="36" t="s">
+      <c r="I20" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="J20" s="36" t="s">
+      <c r="J20" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="K20" s="30" t="b">
+      <c r="K20" s="35" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="35"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="42"/>
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
@@ -2976,27 +3045,27 @@
       <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="35"/>
+      <c r="F21" s="42"/>
       <c r="G21" s="12">
         <v>3</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="36" t="s">
+      <c r="I21" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="30" t="b">
+      <c r="K21" s="35" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="35"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="42"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
@@ -3016,47 +3085,49 @@
       <c r="E22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="46">
         <v>46106</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="14"/>
-      <c r="I22" s="36" t="s">
+      <c r="I22" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="J22" s="36" t="s">
+      <c r="J22" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="30" t="b">
+      <c r="K22" s="35" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="12">
         <v>1</v>
       </c>
-      <c r="O22" s="40" t="s">
+      <c r="M22" s="47"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="P22" s="41"/>
+      <c r="P22" s="49"/>
     </row>
     <row r="23" s="9" customFormat="1" spans="1:18">
-      <c r="A23" s="42">
+      <c r="A23" s="50">
         <v>57020</v>
       </c>
       <c r="B23" s="9">
         <v>57020</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="50">
         <v>20</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="43">
+      <c r="F23" s="51">
         <v>46106</v>
       </c>
       <c r="G23" s="9">
@@ -3065,24 +3136,62 @@
       <c r="H23" s="9">
         <v>9999</v>
       </c>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
       <c r="K23" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L23" s="42">
+      <c r="L23" s="50">
         <v>1</v>
       </c>
-      <c r="P23" s="26"/>
-    </row>
-    <row r="24" s="9" customFormat="1" spans="1:18">
-      <c r="E24" s="9"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="26"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="P23" s="31"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:18">
+      <c r="A24" s="11">
+        <v>57021</v>
+      </c>
+      <c r="B24" s="11">
+        <v>57015</v>
+      </c>
+      <c r="C24" s="11">
+        <v>15</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="11">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="O24" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="P24" s="41"/>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3132,10 +3241,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3143,7 +3252,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3151,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3159,7 +3268,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3167,7 +3276,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3175,7 +3284,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3183,7 +3292,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3191,7 +3300,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3199,7 +3308,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3207,7 +3316,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3215,7 +3324,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3223,7 +3332,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3231,7 +3340,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3239,7 +3348,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3247,7 +3356,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3255,7 +3364,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3263,7 +3372,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3279,7 +3388,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
   <si>
     <t>序列ID</t>
   </si>
@@ -904,6 +904,9 @@
   </si>
   <si>
     <t>活动-财富轮盘-常驻</t>
+  </si>
+  <si>
+    <t>活动-充值活动：福利-常驻</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1175,12 +1178,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2160,7 +2163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -3030,6 +3033,32 @@
         <v>1</v>
       </c>
       <c r="P23" s="26"/>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="42">
+        <v>57021</v>
+      </c>
+      <c r="B24" s="9">
+        <v>57021</v>
+      </c>
+      <c r="C24" s="1">
+        <v>21</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>9999</v>
+      </c>
+      <c r="K24" s="30" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3079,10 +3108,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3090,7 +3119,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3098,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3106,7 +3135,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3114,7 +3143,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3122,7 +3151,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3130,7 +3159,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3138,7 +3167,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3146,7 +3175,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3154,7 +3183,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3162,7 +3191,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3170,7 +3199,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3178,7 +3207,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3186,7 +3215,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3194,7 +3223,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3202,7 +3231,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3210,7 +3239,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3226,7 +3255,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
   <si>
     <t>序列ID</t>
   </si>
@@ -904,9 +904,6 @@
   </si>
   <si>
     <t>活动-财富轮盘-常驻</t>
-  </si>
-  <si>
-    <t>活动-充值活动：福利-常驻</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1178,12 +1175,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2163,7 +2160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -3033,32 +3030,6 @@
         <v>1</v>
       </c>
       <c r="P23" s="26"/>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="42">
-        <v>57021</v>
-      </c>
-      <c r="B24" s="9">
-        <v>57021</v>
-      </c>
-      <c r="C24" s="1">
-        <v>21</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1">
-        <v>9999</v>
-      </c>
-      <c r="K24" s="30" t="b">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3108,10 +3079,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3119,7 +3090,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3127,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3135,7 +3106,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3143,7 +3114,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3151,7 +3122,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3159,7 +3130,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3167,7 +3138,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3175,7 +3146,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3183,7 +3154,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3191,7 +3162,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3199,7 +3170,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3207,7 +3178,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3215,7 +3186,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3223,7 +3194,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3231,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3239,7 +3210,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3255,7 +3226,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -706,7 +706,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="109">
   <si>
     <t>序列ID</t>
   </si>
@@ -973,6 +973,9 @@
   </si>
   <si>
     <t>活跃&amp;付费-成长基金(常驻)2</t>
+  </si>
+  <si>
+    <t>活动-充值活动：福利-常驻</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1255,7 +1258,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1301,12 +1304,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1638,7 +1635,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1662,16 +1659,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1680,89 +1677,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1841,16 +1838,13 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1867,7 +1861,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1879,7 +1873,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1891,13 +1885,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2511,10 +2502,10 @@
       <c r="L6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="31"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="30"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2579,10 +2570,10 @@
       <c r="L8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="31"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="30"/>
     </row>
     <row r="9" s="9" customFormat="1" spans="1:16">
       <c r="A9" s="9">
@@ -2615,10 +2606,10 @@
       <c r="L9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="31"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2636,7 +2627,7 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="31"/>
+      <c r="F10" s="30"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
@@ -2652,12 +2643,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="32" t="s">
+      <c r="M10" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="32"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="30"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2675,7 +2666,7 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
@@ -2693,12 +2684,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="32" t="s">
+      <c r="M11" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="32"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="30"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2716,7 +2707,7 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
@@ -2734,12 +2725,12 @@
       <c r="L12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="32"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="30"/>
     </row>
     <row r="13" s="9" customFormat="1" spans="1:16">
       <c r="A13" s="9">
@@ -2772,10 +2763,10 @@
       <c r="L13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="31"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="30"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2831,18 +2822,18 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="35" t="b">
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="38"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="37"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2860,25 +2851,25 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="37">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="34" t="s">
+      <c r="J16" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="35" t="b">
+      <c r="K16" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="38"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="37"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
@@ -2896,25 +2887,25 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="37">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="34" t="s">
+      <c r="I17" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="34" t="s">
+      <c r="J17" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="K17" s="35" t="b">
+      <c r="K17" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="38"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="37"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
@@ -2938,24 +2929,24 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="35" t="b">
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M18" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="N18" s="40" t="s">
+      <c r="N18" s="39" t="s">
         <v>79</v>
       </c>
       <c r="O18" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="P18" s="41"/>
+      <c r="P18" s="40"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -2973,7 +2964,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="37">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2982,15 +2973,15 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="35" t="b">
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="38"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="37"/>
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
@@ -3008,26 +2999,26 @@
       <c r="E20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="42"/>
+      <c r="F20" s="41"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="J20" s="43" t="s">
+      <c r="J20" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K20" s="35" t="b">
+      <c r="K20" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="42"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="41"/>
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
@@ -3045,27 +3036,27 @@
       <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="42"/>
+      <c r="F21" s="41"/>
       <c r="G21" s="12">
         <v>3</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="J21" s="43" t="s">
+      <c r="J21" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="35" t="b">
+      <c r="K21" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="42"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="41"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
@@ -3085,49 +3076,49 @@
       <c r="E22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="45">
         <v>46106</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="14"/>
-      <c r="I22" s="43" t="s">
+      <c r="I22" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="J22" s="43" t="s">
+      <c r="J22" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="35" t="b">
+      <c r="K22" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="12">
         <v>1</v>
       </c>
-      <c r="M22" s="47"/>
-      <c r="N22" s="47"/>
-      <c r="O22" s="48" t="s">
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="P22" s="49"/>
+      <c r="P22" s="47"/>
     </row>
     <row r="23" s="9" customFormat="1" spans="1:18">
-      <c r="A23" s="50">
+      <c r="A23" s="48">
         <v>57020</v>
       </c>
       <c r="B23" s="9">
         <v>57020</v>
       </c>
-      <c r="C23" s="50">
+      <c r="C23" s="48">
         <v>20</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="49">
         <v>46106</v>
       </c>
       <c r="G23" s="9">
@@ -3141,12 +3132,12 @@
       <c r="K23" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L23" s="50">
+      <c r="L23" s="48">
         <v>1</v>
       </c>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="P23" s="31"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="P23" s="30"/>
     </row>
     <row r="24" s="11" customFormat="1" spans="1:18">
       <c r="A24" s="11">
@@ -3170,28 +3161,62 @@
       <c r="H24" s="1">
         <v>9999</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
       <c r="K24" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L24" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="M24" s="40" t="s">
+      <c r="M24" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="N24" s="40" t="s">
+      <c r="N24" s="39" t="s">
         <v>79</v>
       </c>
       <c r="O24" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="P24" s="41"/>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
+      <c r="P24" s="40"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:18">
+      <c r="A25" s="48">
+        <v>57022</v>
+      </c>
+      <c r="B25" s="9">
+        <v>57021</v>
+      </c>
+      <c r="C25" s="1">
+        <v>21</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3241,10 +3266,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3252,7 +3277,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3260,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3268,7 +3293,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3276,7 +3301,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3284,7 +3309,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3292,7 +3317,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3300,7 +3325,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3308,7 +3333,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3316,7 +3341,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3324,7 +3349,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3332,7 +3357,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3340,7 +3365,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3348,7 +3373,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3356,7 +3381,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3364,7 +3389,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3372,7 +3397,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3388,7 +3413,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -706,7 +706,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
   <si>
     <t>序列ID</t>
   </si>
@@ -975,7 +975,14 @@
     <t>活跃&amp;付费-成长基金(常驻)2</t>
   </si>
   <si>
-    <t>活动-充值活动：福利-常驻</t>
+    <t>活动-充值活动：福利（常驻）时段开</t>
+  </si>
+  <si>
+    <t>2026/3/11 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_2001_2002_2003
+</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1759,7 +1766,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1901,6 +1908,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3180,7 +3190,7 @@
       </c>
       <c r="P24" s="40"/>
     </row>
-    <row r="25" customFormat="1" spans="1:18">
+    <row r="25" customFormat="1" ht="115.5" spans="1:18">
       <c r="A25" s="48">
         <v>57022</v>
       </c>
@@ -3200,16 +3210,18 @@
       <c r="G25" s="1">
         <v>1</v>
       </c>
-      <c r="H25" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
+      <c r="H25" s="1"/>
+      <c r="I25" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K25" s="9" t="b">
         <v>1</v>
+      </c>
+      <c r="L25" s="50" t="s">
+        <v>91</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -3266,10 +3278,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3277,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3285,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3293,7 +3305,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3301,7 +3313,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3309,7 +3321,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3317,7 +3329,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3325,7 +3337,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3333,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3341,7 +3353,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3349,7 +3361,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3357,7 +3369,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3365,7 +3377,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3373,7 +3385,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3381,7 +3393,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3389,7 +3401,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3397,7 +3409,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3413,7 +3425,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="110">
   <si>
     <t>序列ID</t>
   </si>
@@ -907,6 +907,12 @@
   </si>
   <si>
     <t>活动-充值活动：福利-常驻</t>
+  </si>
+  <si>
+    <t>2026/03/11 00:00:00</t>
+  </si>
+  <si>
+    <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1178,12 +1184,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3051,13 +3057,20 @@
         <v>39</v>
       </c>
       <c r="G24" s="1">
+        <v>2</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H24" s="1">
-        <v>9999</v>
-      </c>
-      <c r="K24" s="30" t="b">
-        <v>0</v>
+      <c r="L24" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3108,10 +3121,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3119,7 +3132,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3127,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3135,7 +3148,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3143,7 +3156,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3151,7 +3164,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3159,7 +3172,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3167,7 +3180,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3175,7 +3188,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3183,7 +3196,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3191,7 +3204,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3199,7 +3212,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3207,7 +3220,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3215,7 +3228,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3223,7 +3236,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3231,7 +3244,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3239,7 +3252,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3255,7 +3268,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -981,8 +981,7 @@
     <t>2026/3/11 00:00:00</t>
   </si>
   <si>
-    <t xml:space="preserve">1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_2001_2002_2003
-</t>
+    <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1254,12 +1253,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1766,7 +1765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1908,9 +1907,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3190,7 +3186,7 @@
       </c>
       <c r="P24" s="40"/>
     </row>
-    <row r="25" customFormat="1" ht="115.5" spans="1:18">
+    <row r="25" customFormat="1" spans="1:18">
       <c r="A25" s="48">
         <v>57022</v>
       </c>
@@ -3208,7 +3204,7 @@
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="42" t="s">
@@ -3220,7 +3216,7 @@
       <c r="K25" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L25" s="50" t="s">
+      <c r="L25" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M25" s="1"/>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -978,7 +978,7 @@
     <t>活动-充值活动：福利（常驻）时段开</t>
   </si>
   <si>
-    <t>2026/3/11 00:00:00</t>
+    <t>2026/03/11 00:00:00</t>
   </si>
   <si>
     <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
@@ -1253,12 +1253,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -978,7 +978,7 @@
     <t>活动-充值活动：福利（常驻）时段开</t>
   </si>
   <si>
-    <t>2026/03/11 00:00:00</t>
+    <t>2026/03/17 00:00:00</t>
   </si>
   <si>
     <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -3213,8 +3213,8 @@
       <c r="J25" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K25" s="9" t="b">
-        <v>1</v>
+      <c r="K25" s="34" t="b">
+        <v>0</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>91</v>

--- a/slots/resources/sample/ActivityConfig.xlsx
+++ b/slots/resources/sample/ActivityConfig.xlsx
@@ -635,12 +635,78 @@
         </r>
       </text>
     </comment>
+    <comment ref="L24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置表-GrowthFund.xlsx中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+获得道具数量_购买原价_实际购买价格</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+渠道ID_商品ID|……</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
   <si>
     <t>序列ID</t>
   </si>
@@ -807,7 +873,7 @@
     <t>101_102_103_104_105_106_107_108_109_110_111_112</t>
   </si>
   <si>
-    <t>1280000000_10_1_1</t>
+    <t>60000000_10_1_1</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-7号开</t>
@@ -822,7 +888,7 @@
     <t>201_202_203_204_205_206_207_208_209_210_211_212</t>
   </si>
   <si>
-    <t>8280000000_10_2_2</t>
+    <t>480000000_10_2_2</t>
   </si>
   <si>
     <t>付费-官方派奖(常驻)-21号开</t>
@@ -837,7 +903,7 @@
     <t>301_302_303_304_305_306_307_308_309_310_311_312</t>
   </si>
   <si>
-    <t>3890000000_10_3_2</t>
+    <t>180000000_10_3_2</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -876,13 +942,13 @@
     <t>1_2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18_19_20_101_102_103_104_105_106_107_108_109_110_111_112_113_114_115_116_117_118_119_120</t>
   </si>
   <si>
-    <t>1022501_10_1022502_20_1022503_20_1010302_5</t>
-  </si>
-  <si>
-    <t>16766400_39.92_4.99</t>
-  </si>
-  <si>
-    <t>1_google499|2_ios499</t>
+    <t>1022501_50_1022502_10</t>
+  </si>
+  <si>
+    <t>37078000_1249.5_24.99</t>
+  </si>
+  <si>
+    <t>1_google2499|2_ios2499</t>
   </si>
   <si>
     <t>活跃-收集拼图</t>
@@ -906,10 +972,13 @@
     <t>活动-财富轮盘-常驻</t>
   </si>
   <si>
-    <t>活动-充值活动：福利-常驻</t>
-  </si>
-  <si>
-    <t>2026/03/11 00:00:00</t>
+    <t>活跃&amp;付费-成长基金(常驻)2</t>
+  </si>
+  <si>
+    <t>活动-充值活动：福利（常驻）时段开</t>
+  </si>
+  <si>
+    <t>2026/03/17 00:00:00</t>
   </si>
   <si>
     <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
@@ -1184,12 +1253,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1234,13 +1303,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1696,7 +1765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1757,13 +1826,25 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1778,12 +1859,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1795,6 +1879,9 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1804,7 +1891,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2169,7 +2256,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2277,13 +2364,13 @@
       <c r="L2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="22" t="s">
         <v>22</v>
       </c>
       <c r="P2" s="19" t="s">
@@ -2325,13 +2412,13 @@
       <c r="L3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="25" t="s">
         <v>36</v>
       </c>
       <c r="P3" s="19" t="s">
@@ -2351,8 +2438,8 @@
       <c r="J4" s="17"/>
       <c r="K4" s="16"/>
       <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="18"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="24"/>
       <c r="O4" s="18"/>
       <c r="P4" s="19"/>
     </row>
@@ -2384,7 +2471,9 @@
       <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="23"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="27"/>
     </row>
     <row r="6" s="9" customFormat="1" spans="1:16">
       <c r="A6" s="9">
@@ -2407,10 +2496,10 @@
         <v>2</v>
       </c>
       <c r="H6" s="9"/>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="28" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="9" t="b">
@@ -2419,10 +2508,10 @@
       <c r="L6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="30"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
@@ -2452,7 +2541,9 @@
       <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="23"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="27"/>
     </row>
     <row r="8" s="9" customFormat="1" spans="1:16">
       <c r="A8" s="9">
@@ -2477,18 +2568,18 @@
       <c r="H8" s="9">
         <v>9999</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
       <c r="K8" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="30"/>
     </row>
     <row r="9" s="9" customFormat="1" spans="1:16">
       <c r="A9" s="9">
@@ -2513,18 +2604,18 @@
       <c r="H9" s="9">
         <v>9999</v>
       </c>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
       <c r="K9" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
     </row>
     <row r="10" s="9" customFormat="1" spans="1:16">
       <c r="A10" s="9">
@@ -2542,14 +2633,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="30"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="28" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="b">
@@ -2558,12 +2649,12 @@
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="27" t="s">
+      <c r="M10" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="27"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="26"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="30"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2581,16 +2672,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="30">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="28" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="9" t="b">
@@ -2599,12 +2690,12 @@
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="26"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="30"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2622,16 +2713,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="30">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="28" t="s">
         <v>63</v>
       </c>
       <c r="K12" s="9" t="b">
@@ -2640,12 +2731,12 @@
       <c r="L12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="27"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="26"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="30"/>
     </row>
     <row r="13" s="9" customFormat="1" spans="1:16">
       <c r="A13" s="9">
@@ -2670,18 +2761,18 @@
       <c r="H13" s="9">
         <v>9999</v>
       </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
       <c r="K13" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="30"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
@@ -2711,7 +2802,9 @@
       <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="23"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="27"/>
     </row>
     <row r="15" s="10" customFormat="1" spans="1:16">
       <c r="A15" s="10">
@@ -2735,16 +2828,18 @@
       <c r="H15" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="30" t="b">
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="O15" s="31"/>
-      <c r="P15" s="32"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="37"/>
     </row>
     <row r="16" s="10" customFormat="1" spans="1:16">
       <c r="A16" s="10">
@@ -2762,23 +2857,25 @@
       <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="37">
         <v>46101</v>
       </c>
       <c r="G16" s="10">
         <v>2</v>
       </c>
-      <c r="I16" s="29" t="s">
+      <c r="I16" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="29" t="s">
+      <c r="J16" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="30" t="b">
+      <c r="K16" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="O16" s="31"/>
-      <c r="P16" s="32"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="37"/>
     </row>
     <row r="17" s="10" customFormat="1" spans="1:18">
       <c r="A17" s="10">
@@ -2796,23 +2893,25 @@
       <c r="E17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="37">
         <v>46102</v>
       </c>
       <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="29" t="s">
+      <c r="J17" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="K17" s="30" t="b">
+      <c r="K17" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="O17" s="31"/>
-      <c r="P17" s="32"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="37"/>
     </row>
     <row r="18" s="11" customFormat="1" spans="1:18">
       <c r="A18" s="11">
@@ -2836,24 +2935,24 @@
       <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="9" t="b">
-        <v>1</v>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="34" t="b">
+        <v>0</v>
       </c>
       <c r="L18" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="N18" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="O18" s="23" t="s">
+      <c r="O18" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="P18" s="34"/>
+      <c r="P18" s="40"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -2871,7 +2970,7 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="37">
         <v>46103</v>
       </c>
       <c r="G19" s="10">
@@ -2880,13 +2979,15 @@
       <c r="H19" s="10">
         <v>90</v>
       </c>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="30" t="b">
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="O19" s="31"/>
-      <c r="P19" s="32"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="37"/>
     </row>
     <row r="20" s="12" customFormat="1" spans="1:18">
       <c r="A20" s="12">
@@ -2904,26 +3005,26 @@
       <c r="E20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="35"/>
+      <c r="F20" s="41"/>
       <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="36" t="s">
+      <c r="I20" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="J20" s="36" t="s">
+      <c r="J20" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K20" s="30" t="b">
+      <c r="K20" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="35"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="41"/>
     </row>
     <row r="21" s="13" customFormat="1" spans="1:18">
       <c r="A21" s="12">
@@ -2941,27 +3042,27 @@
       <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="35"/>
+      <c r="F21" s="41"/>
       <c r="G21" s="12">
         <v>3</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="36" t="s">
+      <c r="I21" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="30" t="b">
+      <c r="K21" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="35"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="41"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
     </row>
@@ -2981,47 +3082,49 @@
       <c r="E22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="45">
         <v>46106</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="14"/>
-      <c r="I22" s="36" t="s">
+      <c r="I22" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="J22" s="36" t="s">
+      <c r="J22" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="30" t="b">
+      <c r="K22" s="34" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="12">
         <v>1</v>
       </c>
-      <c r="O22" s="40" t="s">
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="P22" s="41"/>
+      <c r="P22" s="47"/>
     </row>
     <row r="23" s="9" customFormat="1" spans="1:18">
-      <c r="A23" s="42">
+      <c r="A23" s="48">
         <v>57020</v>
       </c>
       <c r="B23" s="9">
         <v>57020</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="48">
         <v>20</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="43">
+      <c r="F23" s="49">
         <v>46106</v>
       </c>
       <c r="G23" s="9">
@@ -3030,48 +3133,98 @@
       <c r="H23" s="9">
         <v>9999</v>
       </c>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
       <c r="K23" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L23" s="42">
+      <c r="L23" s="48">
         <v>1</v>
       </c>
-      <c r="P23" s="26"/>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="42">
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="P23" s="30"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:18">
+      <c r="A24" s="11">
         <v>57021</v>
       </c>
-      <c r="B24" s="9">
-        <v>57021</v>
-      </c>
-      <c r="C24" s="1">
-        <v>21</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="B24" s="11">
+        <v>57015</v>
+      </c>
+      <c r="C24" s="11">
+        <v>15</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>44</v>
-      </c>
+      <c r="E24" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="11">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
       <c r="K24" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="O24" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="P24" s="40"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:18">
+      <c r="A25" s="48">
+        <v>57022</v>
+      </c>
+      <c r="B25" s="9">
+        <v>57021</v>
+      </c>
+      <c r="C25" s="1">
+        <v>21</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="42" t="s">
         <v>90</v>
       </c>
+      <c r="J25" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K25" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3121,10 +3274,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3132,7 +3285,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3140,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3148,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3156,7 +3309,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3164,7 +3317,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3172,7 +3325,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3180,7 +3333,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3188,7 +3341,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3196,7 +3349,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3204,7 +3357,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3212,7 +3365,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3220,7 +3373,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3228,7 +3381,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3236,7 +3389,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3244,7 +3397,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3252,7 +3405,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3268,7 +3421,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">
